--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>12-09-2026</t>
+          <t>14-09-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,7 +503,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>12-09-2026</t>
+          <t>14-09-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -540,7 +540,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>12-09-2026</t>
+          <t>14-09-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -577,7 +577,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>12-09-2026</t>
+          <t>14-09-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -614,7 +614,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>12-09-2026</t>
+          <t>14-09-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -651,7 +651,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>12-09-2026</t>
+          <t>14-09-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -688,7 +688,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>12-09-2026</t>
+          <t>14-09-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -725,7 +725,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>12-09-2026</t>
+          <t>14-09-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -762,7 +762,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>12-09-2026</t>
+          <t>14-09-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -799,7 +799,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>12-09-2026</t>
+          <t>14-09-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -836,7 +836,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>12-09-2026</t>
+          <t>14-09-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>14-09-2026</t>
+          <t>15-09-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,7 +503,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>14-09-2026</t>
+          <t>15-09-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -540,7 +540,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>14-09-2026</t>
+          <t>15-09-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -577,7 +577,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>14-09-2026</t>
+          <t>15-09-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -614,7 +614,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>14-09-2026</t>
+          <t>15-09-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -651,7 +651,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>14-09-2026</t>
+          <t>15-09-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -688,7 +688,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>14-09-2026</t>
+          <t>15-09-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -725,7 +725,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>14-09-2026</t>
+          <t>15-09-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -762,7 +762,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>14-09-2026</t>
+          <t>15-09-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -799,7 +799,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>14-09-2026</t>
+          <t>15-09-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -836,7 +836,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>14-09-2026</t>
+          <t>15-09-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -471,23 +471,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>287.2</v>
+        <v>413.05</v>
       </c>
       <c r="D2" t="n">
-        <v>286.53</v>
+        <v>406.64</v>
       </c>
       <c r="E2" t="n">
-        <v>282.4</v>
+        <v>397.28</v>
       </c>
       <c r="F2" t="n">
-        <v>278.29</v>
+        <v>399.95</v>
       </c>
       <c r="G2" t="n">
-        <v>3.2</v>
+        <v>3.27</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -512,19 +512,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>116.75</v>
+        <v>116.11</v>
       </c>
       <c r="D3" t="n">
-        <v>115.92</v>
+        <v>116.02</v>
       </c>
       <c r="E3" t="n">
-        <v>112.74</v>
+        <v>112.98</v>
       </c>
       <c r="F3" t="n">
-        <v>112.41</v>
+        <v>112.38</v>
       </c>
       <c r="G3" t="n">
-        <v>3.86</v>
+        <v>3.32</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>419</v>
+        <v>5636.5</v>
       </c>
       <c r="D4" t="n">
-        <v>406.12</v>
+        <v>5581.28</v>
       </c>
       <c r="E4" t="n">
-        <v>396.63</v>
+        <v>5417.98</v>
       </c>
       <c r="F4" t="n">
-        <v>400</v>
+        <v>5396.71</v>
       </c>
       <c r="G4" t="n">
-        <v>4.75</v>
+        <v>4.44</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -586,19 +586,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>562.9</v>
+        <v>552.55</v>
       </c>
       <c r="D5" t="n">
-        <v>516.4400000000001</v>
+        <v>517.77</v>
       </c>
       <c r="E5" t="n">
-        <v>523.9299999999999</v>
+        <v>524.12</v>
       </c>
       <c r="F5" t="n">
-        <v>523.49</v>
+        <v>523.53</v>
       </c>
       <c r="G5" t="n">
-        <v>7.53</v>
+        <v>5.54</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -623,19 +623,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>489.8</v>
+        <v>488.45</v>
       </c>
       <c r="D6" t="n">
-        <v>474.22</v>
+        <v>475.47</v>
       </c>
       <c r="E6" t="n">
-        <v>460.37</v>
+        <v>461.64</v>
       </c>
       <c r="F6" t="n">
-        <v>454.35</v>
+        <v>454.74</v>
       </c>
       <c r="G6" t="n">
-        <v>7.8</v>
+        <v>7.41</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -660,19 +660,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1797.3</v>
+        <v>1783.4</v>
       </c>
       <c r="D7" t="n">
-        <v>1754.97</v>
+        <v>1761.03</v>
       </c>
       <c r="E7" t="n">
-        <v>1683.04</v>
+        <v>1686.89</v>
       </c>
       <c r="F7" t="n">
-        <v>1651.94</v>
+        <v>1652.03</v>
       </c>
       <c r="G7" t="n">
-        <v>8.800000000000001</v>
+        <v>7.95</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -693,23 +693,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2153.5</v>
+        <v>1613.5</v>
       </c>
       <c r="D8" t="n">
-        <v>2105.99</v>
+        <v>1602.98</v>
       </c>
       <c r="E8" t="n">
-        <v>1990.35</v>
+        <v>1581.4</v>
       </c>
       <c r="F8" t="n">
-        <v>1950.67</v>
+        <v>1490.24</v>
       </c>
       <c r="G8" t="n">
-        <v>10.4</v>
+        <v>8.27</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -730,23 +730,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>323.5</v>
+        <v>2120.5</v>
       </c>
       <c r="D9" t="n">
-        <v>320.52</v>
+        <v>2112.2</v>
       </c>
       <c r="E9" t="n">
-        <v>308.6</v>
+        <v>1996.81</v>
       </c>
       <c r="F9" t="n">
-        <v>274</v>
+        <v>1952.63</v>
       </c>
       <c r="G9" t="n">
-        <v>18.06</v>
+        <v>8.6</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -771,19 +771,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1026.5</v>
+        <v>996.7</v>
       </c>
       <c r="D10" t="n">
-        <v>968.03</v>
+        <v>972.3200000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>951.5700000000001</v>
+        <v>952.4400000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>850.11</v>
+        <v>850.5</v>
       </c>
       <c r="G10" t="n">
-        <v>20.75</v>
+        <v>17.19</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -808,19 +808,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3276</v>
+        <v>3202.4</v>
       </c>
       <c r="D11" t="n">
-        <v>3078.68</v>
+        <v>3097.57</v>
       </c>
       <c r="E11" t="n">
-        <v>2949.59</v>
+        <v>2959.31</v>
       </c>
       <c r="F11" t="n">
-        <v>2671.75</v>
+        <v>2677.36</v>
       </c>
       <c r="G11" t="n">
-        <v>22.62</v>
+        <v>19.61</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>431</v>
+        <v>422.05</v>
       </c>
       <c r="D12" t="n">
-        <v>421.2</v>
+        <v>421.56</v>
       </c>
       <c r="E12" t="n">
-        <v>414.85</v>
+        <v>415.56</v>
       </c>
       <c r="F12" t="n">
-        <v>338.03</v>
+        <v>338.69</v>
       </c>
       <c r="G12" t="n">
-        <v>27.5</v>
+        <v>24.61</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>413.05</v>
+        <v>409.8</v>
       </c>
       <c r="D2" t="n">
-        <v>406.64</v>
+        <v>406.53</v>
       </c>
       <c r="E2" t="n">
-        <v>397.28</v>
+        <v>397.21</v>
       </c>
       <c r="F2" t="n">
-        <v>399.95</v>
+        <v>399.94</v>
       </c>
       <c r="G2" t="n">
-        <v>3.27</v>
+        <v>2.47</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>116.11</v>
+        <v>542</v>
       </c>
       <c r="D3" t="n">
-        <v>116.02</v>
+        <v>517.41</v>
       </c>
       <c r="E3" t="n">
-        <v>112.98</v>
+        <v>523.91</v>
       </c>
       <c r="F3" t="n">
-        <v>112.38</v>
+        <v>523.47</v>
       </c>
       <c r="G3" t="n">
-        <v>3.32</v>
+        <v>3.54</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5636.5</v>
+        <v>485.6</v>
       </c>
       <c r="D4" t="n">
-        <v>5581.28</v>
+        <v>475.37</v>
       </c>
       <c r="E4" t="n">
-        <v>5417.98</v>
+        <v>461.58</v>
       </c>
       <c r="F4" t="n">
-        <v>5396.71</v>
+        <v>454.73</v>
       </c>
       <c r="G4" t="n">
-        <v>4.44</v>
+        <v>6.79</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>552.55</v>
+        <v>2119.3</v>
       </c>
       <c r="D5" t="n">
-        <v>517.77</v>
+        <v>2112.16</v>
       </c>
       <c r="E5" t="n">
-        <v>524.12</v>
+        <v>1996.79</v>
       </c>
       <c r="F5" t="n">
-        <v>523.53</v>
+        <v>1952.63</v>
       </c>
       <c r="G5" t="n">
-        <v>5.54</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>488.45</v>
+        <v>990.8</v>
       </c>
       <c r="D6" t="n">
-        <v>475.47</v>
+        <v>972.12</v>
       </c>
       <c r="E6" t="n">
-        <v>461.64</v>
+        <v>952.3200000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>454.74</v>
+        <v>850.47</v>
       </c>
       <c r="G6" t="n">
-        <v>7.41</v>
+        <v>16.5</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -656,23 +656,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1783.4</v>
+        <v>3173.5</v>
       </c>
       <c r="D7" t="n">
-        <v>1761.03</v>
+        <v>3096.61</v>
       </c>
       <c r="E7" t="n">
-        <v>1686.89</v>
+        <v>2958.73</v>
       </c>
       <c r="F7" t="n">
-        <v>1652.03</v>
+        <v>2677.22</v>
       </c>
       <c r="G7" t="n">
-        <v>7.95</v>
+        <v>18.54</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -680,191 +680,6 @@
         </is>
       </c>
       <c r="I7" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>15-09-2026</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>TECHM</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>1613.5</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1602.98</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1581.4</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1490.24</v>
-      </c>
-      <c r="G8" t="n">
-        <v>8.27</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>15-09-2026</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>APLAPOLLO</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>2120.5</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2112.2</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1996.81</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1952.63</v>
-      </c>
-      <c r="G9" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>15-09-2026</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>MOTILALOFS</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>996.7</v>
-      </c>
-      <c r="D10" t="n">
-        <v>972.3200000000001</v>
-      </c>
-      <c r="E10" t="n">
-        <v>952.4400000000001</v>
-      </c>
-      <c r="F10" t="n">
-        <v>850.5</v>
-      </c>
-      <c r="G10" t="n">
-        <v>17.19</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>15-09-2026</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>3202.4</v>
-      </c>
-      <c r="D11" t="n">
-        <v>3097.57</v>
-      </c>
-      <c r="E11" t="n">
-        <v>2959.31</v>
-      </c>
-      <c r="F11" t="n">
-        <v>2677.36</v>
-      </c>
-      <c r="G11" t="n">
-        <v>19.61</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>15-09-2026</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>BHEL</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>422.05</v>
-      </c>
-      <c r="D12" t="n">
-        <v>421.56</v>
-      </c>
-      <c r="E12" t="n">
-        <v>415.56</v>
-      </c>
-      <c r="F12" t="n">
-        <v>338.69</v>
-      </c>
-      <c r="G12" t="n">
-        <v>24.61</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>15-09-2026</t>
+          <t>16-09-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -478,13 +478,13 @@
         <v>409.8</v>
       </c>
       <c r="D2" t="n">
-        <v>406.53</v>
+        <v>407.23</v>
       </c>
       <c r="E2" t="n">
-        <v>397.21</v>
+        <v>397.97</v>
       </c>
       <c r="F2" t="n">
-        <v>399.94</v>
+        <v>399.91</v>
       </c>
       <c r="G2" t="n">
         <v>2.47</v>
@@ -503,28 +503,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>15-09-2026</t>
+          <t>16-09-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>542</v>
+        <v>485.6</v>
       </c>
       <c r="D3" t="n">
-        <v>517.41</v>
+        <v>476.73</v>
       </c>
       <c r="E3" t="n">
-        <v>523.91</v>
+        <v>462.94</v>
       </c>
       <c r="F3" t="n">
-        <v>523.47</v>
+        <v>455.15</v>
       </c>
       <c r="G3" t="n">
-        <v>3.54</v>
+        <v>6.69</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -540,28 +540,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>15-09-2026</t>
+          <t>16-09-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>485.6</v>
+        <v>3173.5</v>
       </c>
       <c r="D4" t="n">
-        <v>475.37</v>
+        <v>3116.69</v>
       </c>
       <c r="E4" t="n">
-        <v>461.58</v>
+        <v>2971.52</v>
       </c>
       <c r="F4" t="n">
-        <v>454.73</v>
+        <v>2683.55</v>
       </c>
       <c r="G4" t="n">
-        <v>6.79</v>
+        <v>18.26</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -569,117 +569,6 @@
         </is>
       </c>
       <c r="I4" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>15-09-2026</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>APLAPOLLO</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>2119.3</v>
-      </c>
-      <c r="D5" t="n">
-        <v>2112.16</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1996.79</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1952.63</v>
-      </c>
-      <c r="G5" t="n">
-        <v>8.539999999999999</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>15-09-2026</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>MOTILALOFS</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>990.8</v>
-      </c>
-      <c r="D6" t="n">
-        <v>972.12</v>
-      </c>
-      <c r="E6" t="n">
-        <v>952.3200000000001</v>
-      </c>
-      <c r="F6" t="n">
-        <v>850.47</v>
-      </c>
-      <c r="G6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>15-09-2026</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>3173.5</v>
-      </c>
-      <c r="D7" t="n">
-        <v>3096.61</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2958.73</v>
-      </c>
-      <c r="F7" t="n">
-        <v>2677.22</v>
-      </c>
-      <c r="G7" t="n">
-        <v>18.54</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>409.8</v>
+        <v>412.85</v>
       </c>
       <c r="D2" t="n">
-        <v>407.23</v>
+        <v>407.66</v>
       </c>
       <c r="E2" t="n">
-        <v>397.97</v>
+        <v>398.84</v>
       </c>
       <c r="F2" t="n">
-        <v>399.91</v>
+        <v>399.83</v>
       </c>
       <c r="G2" t="n">
-        <v>2.47</v>
+        <v>3.26</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>485.6</v>
+        <v>541.5</v>
       </c>
       <c r="D3" t="n">
-        <v>476.73</v>
+        <v>517.4</v>
       </c>
       <c r="E3" t="n">
-        <v>462.94</v>
+        <v>523.9</v>
       </c>
       <c r="F3" t="n">
-        <v>455.15</v>
+        <v>523.47</v>
       </c>
       <c r="G3" t="n">
-        <v>6.69</v>
+        <v>3.44</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3173.5</v>
+        <v>116.95</v>
       </c>
       <c r="D4" t="n">
-        <v>3116.69</v>
+        <v>116.18</v>
       </c>
       <c r="E4" t="n">
-        <v>2971.52</v>
+        <v>113.53</v>
       </c>
       <c r="F4" t="n">
-        <v>2683.55</v>
+        <v>112.33</v>
       </c>
       <c r="G4" t="n">
-        <v>18.26</v>
+        <v>4.11</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -569,6 +569,80 @@
         </is>
       </c>
       <c r="I4" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>16-09-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>483.3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>478.07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>464.01</v>
+      </c>
+      <c r="F5" t="n">
+        <v>455.53</v>
+      </c>
+      <c r="G5" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>16-09-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>981.9</v>
+      </c>
+      <c r="D6" t="n">
+        <v>971.83</v>
+      </c>
+      <c r="E6" t="n">
+        <v>952.14</v>
+      </c>
+      <c r="F6" t="n">
+        <v>850.4299999999999</v>
+      </c>
+      <c r="G6" t="n">
+        <v>15.46</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,23 +471,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>412.85</v>
+        <v>543</v>
       </c>
       <c r="D2" t="n">
-        <v>407.66</v>
+        <v>518.55</v>
       </c>
       <c r="E2" t="n">
-        <v>398.84</v>
+        <v>524.01</v>
       </c>
       <c r="F2" t="n">
-        <v>399.83</v>
+        <v>523.49</v>
       </c>
       <c r="G2" t="n">
-        <v>3.26</v>
+        <v>3.73</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>541.5</v>
+        <v>415</v>
       </c>
       <c r="D3" t="n">
-        <v>517.4</v>
+        <v>407.73</v>
       </c>
       <c r="E3" t="n">
-        <v>523.9</v>
+        <v>398.88</v>
       </c>
       <c r="F3" t="n">
-        <v>523.47</v>
+        <v>399.84</v>
       </c>
       <c r="G3" t="n">
-        <v>3.44</v>
+        <v>3.79</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -549,10 +549,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>116.95</v>
+        <v>116.8</v>
       </c>
       <c r="D4" t="n">
-        <v>116.18</v>
+        <v>116.17</v>
       </c>
       <c r="E4" t="n">
         <v>113.53</v>
@@ -561,7 +561,7 @@
         <v>112.33</v>
       </c>
       <c r="G4" t="n">
-        <v>4.11</v>
+        <v>3.98</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -586,19 +586,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>483.3</v>
+        <v>487.6</v>
       </c>
       <c r="D5" t="n">
-        <v>478.07</v>
+        <v>478.22</v>
       </c>
       <c r="E5" t="n">
-        <v>464.01</v>
+        <v>464.1</v>
       </c>
       <c r="F5" t="n">
-        <v>455.53</v>
+        <v>455.55</v>
       </c>
       <c r="G5" t="n">
-        <v>6.1</v>
+        <v>7.04</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,30 +619,104 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>POLICYBZR</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1827.1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1765.36</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1690.87</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1651.99</v>
+      </c>
+      <c r="G6" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>16-09-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>MOTILALOFS</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>981.9</v>
-      </c>
-      <c r="D6" t="n">
-        <v>971.83</v>
-      </c>
-      <c r="E6" t="n">
-        <v>952.14</v>
-      </c>
-      <c r="F6" t="n">
-        <v>850.4299999999999</v>
-      </c>
-      <c r="G6" t="n">
-        <v>15.46</v>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="C7" t="n">
+        <v>976.5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>975.97</v>
+      </c>
+      <c r="E7" t="n">
+        <v>952.83</v>
+      </c>
+      <c r="F7" t="n">
+        <v>850.59</v>
+      </c>
+      <c r="G7" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>16-09-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3211.2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3137.32</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2981.04</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2689.42</v>
+      </c>
+      <c r="G8" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>16-09-2026</t>
+          <t>17-09-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -478,16 +478,16 @@
         <v>543</v>
       </c>
       <c r="D2" t="n">
-        <v>518.55</v>
+        <v>520.59</v>
       </c>
       <c r="E2" t="n">
-        <v>524.01</v>
+        <v>524.61</v>
       </c>
       <c r="F2" t="n">
-        <v>523.49</v>
+        <v>523.61</v>
       </c>
       <c r="G2" t="n">
-        <v>3.73</v>
+        <v>3.7</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -503,7 +503,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>16-09-2026</t>
+          <t>17-09-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -540,7 +540,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>16-09-2026</t>
+          <t>17-09-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -577,7 +577,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>16-09-2026</t>
+          <t>17-09-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -614,7 +614,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>16-09-2026</t>
+          <t>17-09-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -626,13 +626,13 @@
         <v>1827.1</v>
       </c>
       <c r="D6" t="n">
-        <v>1765.36</v>
+        <v>1772.03</v>
       </c>
       <c r="E6" t="n">
-        <v>1690.87</v>
+        <v>1694.65</v>
       </c>
       <c r="F6" t="n">
-        <v>1651.99</v>
+        <v>1651.93</v>
       </c>
       <c r="G6" t="n">
         <v>10.6</v>
@@ -651,28 +651,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>16-09-2026</t>
+          <t>17-09-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>976.5</v>
+        <v>3211.2</v>
       </c>
       <c r="D7" t="n">
-        <v>975.97</v>
+        <v>3137.32</v>
       </c>
       <c r="E7" t="n">
-        <v>952.83</v>
+        <v>2981.04</v>
       </c>
       <c r="F7" t="n">
-        <v>850.59</v>
+        <v>2689.42</v>
       </c>
       <c r="G7" t="n">
-        <v>14.8</v>
+        <v>19.4</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -680,43 +680,6 @@
         </is>
       </c>
       <c r="I7" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>16-09-2026</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>3211.2</v>
-      </c>
-      <c r="D8" t="n">
-        <v>3137.32</v>
-      </c>
-      <c r="E8" t="n">
-        <v>2981.04</v>
-      </c>
-      <c r="F8" t="n">
-        <v>2689.42</v>
-      </c>
-      <c r="G8" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,23 +471,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>543</v>
+        <v>413.25</v>
       </c>
       <c r="D2" t="n">
-        <v>520.59</v>
+        <v>408.37</v>
       </c>
       <c r="E2" t="n">
-        <v>524.61</v>
+        <v>399.62</v>
       </c>
       <c r="F2" t="n">
-        <v>523.61</v>
+        <v>399.77</v>
       </c>
       <c r="G2" t="n">
-        <v>3.7</v>
+        <v>3.37</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>415</v>
+        <v>545.75</v>
       </c>
       <c r="D3" t="n">
-        <v>407.73</v>
+        <v>522.05</v>
       </c>
       <c r="E3" t="n">
-        <v>398.88</v>
+        <v>525.12</v>
       </c>
       <c r="F3" t="n">
-        <v>399.84</v>
+        <v>523.64</v>
       </c>
       <c r="G3" t="n">
-        <v>3.79</v>
+        <v>4.22</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -549,19 +549,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>116.8</v>
+        <v>117.39</v>
       </c>
       <c r="D4" t="n">
-        <v>116.17</v>
+        <v>116.28</v>
       </c>
       <c r="E4" t="n">
-        <v>113.53</v>
+        <v>113.81</v>
       </c>
       <c r="F4" t="n">
-        <v>112.33</v>
+        <v>112.31</v>
       </c>
       <c r="G4" t="n">
-        <v>3.98</v>
+        <v>4.53</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>487.6</v>
+        <v>2137.8</v>
       </c>
       <c r="D5" t="n">
-        <v>478.22</v>
+        <v>2126.75</v>
       </c>
       <c r="E5" t="n">
-        <v>464.1</v>
+        <v>2010.3</v>
       </c>
       <c r="F5" t="n">
-        <v>455.55</v>
+        <v>1956.88</v>
       </c>
       <c r="G5" t="n">
-        <v>7.04</v>
+        <v>9.25</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1827.1</v>
+        <v>993.5</v>
       </c>
       <c r="D6" t="n">
-        <v>1772.03</v>
+        <v>984.84</v>
       </c>
       <c r="E6" t="n">
-        <v>1694.65</v>
+        <v>956.1900000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>1651.93</v>
+        <v>851.21</v>
       </c>
       <c r="G6" t="n">
-        <v>10.6</v>
+        <v>16.72</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -656,30 +656,67 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>324.45</v>
+      </c>
+      <c r="D7" t="n">
+        <v>322.01</v>
+      </c>
+      <c r="E7" t="n">
+        <v>311.38</v>
+      </c>
+      <c r="F7" t="n">
+        <v>274.35</v>
+      </c>
+      <c r="G7" t="n">
+        <v>18.26</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>17-09-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>MCX</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>3211.2</v>
-      </c>
-      <c r="D7" t="n">
-        <v>3137.32</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2981.04</v>
-      </c>
-      <c r="F7" t="n">
-        <v>2689.42</v>
-      </c>
-      <c r="G7" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="C8" t="n">
+        <v>3282.8</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3158.96</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2991.12</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2695.64</v>
+      </c>
+      <c r="G8" t="n">
+        <v>21.78</v>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -471,23 +471,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>413.25</v>
+        <v>116.47</v>
       </c>
       <c r="D2" t="n">
-        <v>408.37</v>
+        <v>116.25</v>
       </c>
       <c r="E2" t="n">
-        <v>399.62</v>
+        <v>113.79</v>
       </c>
       <c r="F2" t="n">
-        <v>399.77</v>
+        <v>112.3</v>
       </c>
       <c r="G2" t="n">
-        <v>3.37</v>
+        <v>3.71</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>545.75</v>
+        <v>416.5</v>
       </c>
       <c r="D3" t="n">
-        <v>522.05</v>
+        <v>408.48</v>
       </c>
       <c r="E3" t="n">
-        <v>525.12</v>
+        <v>399.68</v>
       </c>
       <c r="F3" t="n">
-        <v>523.64</v>
+        <v>399.79</v>
       </c>
       <c r="G3" t="n">
-        <v>4.22</v>
+        <v>4.18</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>117.39</v>
+        <v>545.9</v>
       </c>
       <c r="D4" t="n">
-        <v>116.28</v>
+        <v>522.05</v>
       </c>
       <c r="E4" t="n">
-        <v>113.81</v>
+        <v>525.13</v>
       </c>
       <c r="F4" t="n">
-        <v>112.31</v>
+        <v>523.64</v>
       </c>
       <c r="G4" t="n">
-        <v>4.53</v>
+        <v>4.25</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -586,19 +586,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2137.8</v>
+        <v>2148.5</v>
       </c>
       <c r="D5" t="n">
-        <v>2126.75</v>
+        <v>2133.19</v>
       </c>
       <c r="E5" t="n">
-        <v>2010.3</v>
+        <v>2017.34</v>
       </c>
       <c r="F5" t="n">
-        <v>1956.88</v>
+        <v>1958.9</v>
       </c>
       <c r="G5" t="n">
-        <v>9.25</v>
+        <v>9.68</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -623,19 +623,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>993.5</v>
+        <v>988.7</v>
       </c>
       <c r="D6" t="n">
-        <v>984.84</v>
+        <v>984.6799999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>956.1900000000001</v>
+        <v>956.1</v>
       </c>
       <c r="F6" t="n">
-        <v>851.21</v>
+        <v>851.1900000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>16.72</v>
+        <v>16.16</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -660,19 +660,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>324.45</v>
+        <v>322.35</v>
       </c>
       <c r="D7" t="n">
-        <v>322.01</v>
+        <v>321.94</v>
       </c>
       <c r="E7" t="n">
-        <v>311.38</v>
+        <v>311.34</v>
       </c>
       <c r="F7" t="n">
-        <v>274.35</v>
+        <v>274.34</v>
       </c>
       <c r="G7" t="n">
-        <v>18.26</v>
+        <v>17.5</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -697,19 +697,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3282.8</v>
+        <v>3265.2</v>
       </c>
       <c r="D8" t="n">
-        <v>3158.96</v>
+        <v>3158.38</v>
       </c>
       <c r="E8" t="n">
-        <v>2991.12</v>
+        <v>2990.77</v>
       </c>
       <c r="F8" t="n">
-        <v>2695.64</v>
+        <v>2695.55</v>
       </c>
       <c r="G8" t="n">
-        <v>21.78</v>
+        <v>21.13</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>17-09-2026</t>
+          <t>18-09-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,7 +503,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>17-09-2026</t>
+          <t>18-09-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -540,28 +540,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>17-09-2026</t>
+          <t>18-09-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>545.9</v>
+        <v>322.35</v>
       </c>
       <c r="D4" t="n">
-        <v>522.05</v>
+        <v>321.94</v>
       </c>
       <c r="E4" t="n">
-        <v>525.13</v>
+        <v>311.34</v>
       </c>
       <c r="F4" t="n">
-        <v>523.64</v>
+        <v>274.34</v>
       </c>
       <c r="G4" t="n">
-        <v>4.25</v>
+        <v>17.5</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -569,154 +569,6 @@
         </is>
       </c>
       <c r="I4" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>17-09-2026</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>APLAPOLLO</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>2148.5</v>
-      </c>
-      <c r="D5" t="n">
-        <v>2133.19</v>
-      </c>
-      <c r="E5" t="n">
-        <v>2017.34</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1958.9</v>
-      </c>
-      <c r="G5" t="n">
-        <v>9.68</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>17-09-2026</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>MOTILALOFS</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>988.7</v>
-      </c>
-      <c r="D6" t="n">
-        <v>984.6799999999999</v>
-      </c>
-      <c r="E6" t="n">
-        <v>956.1</v>
-      </c>
-      <c r="F6" t="n">
-        <v>851.1900000000001</v>
-      </c>
-      <c r="G6" t="n">
-        <v>16.16</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>17-09-2026</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>ETERNAL</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>322.35</v>
-      </c>
-      <c r="D7" t="n">
-        <v>321.94</v>
-      </c>
-      <c r="E7" t="n">
-        <v>311.34</v>
-      </c>
-      <c r="F7" t="n">
-        <v>274.34</v>
-      </c>
-      <c r="G7" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>17-09-2026</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>3265.2</v>
-      </c>
-      <c r="D8" t="n">
-        <v>3158.38</v>
-      </c>
-      <c r="E8" t="n">
-        <v>2990.77</v>
-      </c>
-      <c r="F8" t="n">
-        <v>2695.55</v>
-      </c>
-      <c r="G8" t="n">
-        <v>21.13</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>116.47</v>
+        <v>117.05</v>
       </c>
       <c r="D2" t="n">
-        <v>116.25</v>
+        <v>116.32</v>
       </c>
       <c r="E2" t="n">
-        <v>113.79</v>
+        <v>114.02</v>
       </c>
       <c r="F2" t="n">
-        <v>112.3</v>
+        <v>112.31</v>
       </c>
       <c r="G2" t="n">
-        <v>3.71</v>
+        <v>4.22</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -512,19 +512,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>416.5</v>
+        <v>417.2</v>
       </c>
       <c r="D3" t="n">
-        <v>408.48</v>
+        <v>409.36</v>
       </c>
       <c r="E3" t="n">
-        <v>399.68</v>
+        <v>400.49</v>
       </c>
       <c r="F3" t="n">
-        <v>399.79</v>
+        <v>399.73</v>
       </c>
       <c r="G3" t="n">
-        <v>4.18</v>
+        <v>4.37</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,30 +545,215 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>547.5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>522.1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>525.16</v>
+      </c>
+      <c r="F4" t="n">
+        <v>523.65</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>18-09-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>737.05</v>
+      </c>
+      <c r="D5" t="n">
+        <v>723.03</v>
+      </c>
+      <c r="E5" t="n">
+        <v>728.0599999999999</v>
+      </c>
+      <c r="F5" t="n">
+        <v>686.03</v>
+      </c>
+      <c r="G5" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>18-09-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2184.4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2134.39</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2018.06</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1959.08</v>
+      </c>
+      <c r="G6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>18-09-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1000.5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>985.0700000000001</v>
+      </c>
+      <c r="E7" t="n">
+        <v>956.33</v>
+      </c>
+      <c r="F7" t="n">
+        <v>851.25</v>
+      </c>
+      <c r="G7" t="n">
+        <v>17.53</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>18-09-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>ETERNAL</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>322.35</v>
-      </c>
-      <c r="D4" t="n">
-        <v>321.94</v>
-      </c>
-      <c r="E4" t="n">
-        <v>311.34</v>
-      </c>
-      <c r="F4" t="n">
-        <v>274.34</v>
-      </c>
-      <c r="G4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="C8" t="n">
+        <v>328.4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>322.34</v>
+      </c>
+      <c r="E8" t="n">
+        <v>312.06</v>
+      </c>
+      <c r="F8" t="n">
+        <v>274.48</v>
+      </c>
+      <c r="G8" t="n">
+        <v>19.65</v>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>18-09-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>3267.7</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3158.46</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2990.82</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2695.57</v>
+      </c>
+      <c r="G9" t="n">
+        <v>21.22</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,23 +471,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>117.05</v>
+        <v>412.5</v>
       </c>
       <c r="D2" t="n">
-        <v>116.32</v>
+        <v>409.2</v>
       </c>
       <c r="E2" t="n">
-        <v>114.02</v>
+        <v>400.39</v>
       </c>
       <c r="F2" t="n">
-        <v>112.31</v>
+        <v>399.71</v>
       </c>
       <c r="G2" t="n">
-        <v>4.22</v>
+        <v>3.2</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>417.2</v>
+        <v>117.27</v>
       </c>
       <c r="D3" t="n">
-        <v>409.36</v>
+        <v>116.33</v>
       </c>
       <c r="E3" t="n">
-        <v>400.49</v>
+        <v>114.03</v>
       </c>
       <c r="F3" t="n">
-        <v>399.73</v>
+        <v>112.31</v>
       </c>
       <c r="G3" t="n">
-        <v>4.37</v>
+        <v>4.42</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -549,19 +549,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>547.5</v>
+        <v>548.15</v>
       </c>
       <c r="D4" t="n">
-        <v>522.1</v>
+        <v>524.02</v>
       </c>
       <c r="E4" t="n">
-        <v>525.16</v>
+        <v>525.63</v>
       </c>
       <c r="F4" t="n">
-        <v>523.65</v>
+        <v>523.7</v>
       </c>
       <c r="G4" t="n">
-        <v>4.55</v>
+        <v>4.67</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>737.05</v>
+        <v>292.6</v>
       </c>
       <c r="D5" t="n">
-        <v>723.03</v>
+        <v>287.58</v>
       </c>
       <c r="E5" t="n">
-        <v>728.0599999999999</v>
+        <v>283.63</v>
       </c>
       <c r="F5" t="n">
-        <v>686.03</v>
+        <v>278.82</v>
       </c>
       <c r="G5" t="n">
-        <v>7.44</v>
+        <v>4.94</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2184.4</v>
+        <v>11282</v>
       </c>
       <c r="D6" t="n">
-        <v>2134.39</v>
+        <v>11275.37</v>
       </c>
       <c r="E6" t="n">
-        <v>2018.06</v>
+        <v>11096.88</v>
       </c>
       <c r="F6" t="n">
-        <v>1959.08</v>
+        <v>10586.22</v>
       </c>
       <c r="G6" t="n">
-        <v>11.5</v>
+        <v>6.57</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -656,23 +656,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1000.5</v>
+        <v>732.75</v>
       </c>
       <c r="D7" t="n">
-        <v>985.0700000000001</v>
+        <v>722.89</v>
       </c>
       <c r="E7" t="n">
-        <v>956.33</v>
+        <v>727.97</v>
       </c>
       <c r="F7" t="n">
-        <v>851.25</v>
+        <v>686.01</v>
       </c>
       <c r="G7" t="n">
-        <v>17.53</v>
+        <v>6.81</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -693,23 +693,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>328.4</v>
+        <v>2208.8</v>
       </c>
       <c r="D8" t="n">
-        <v>322.34</v>
+        <v>2201.01</v>
       </c>
       <c r="E8" t="n">
-        <v>312.06</v>
+        <v>2134.01</v>
       </c>
       <c r="F8" t="n">
-        <v>274.48</v>
+        <v>2051.99</v>
       </c>
       <c r="G8" t="n">
-        <v>19.65</v>
+        <v>7.64</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -730,30 +730,141 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2270.1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2137.24</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2019.77</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1959.51</v>
+      </c>
+      <c r="G9" t="n">
+        <v>15.85</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>18-09-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1010</v>
+      </c>
+      <c r="D10" t="n">
+        <v>985.39</v>
+      </c>
+      <c r="E10" t="n">
+        <v>956.52</v>
+      </c>
+      <c r="F10" t="n">
+        <v>851.29</v>
+      </c>
+      <c r="G10" t="n">
+        <v>18.64</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>18-09-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>326.85</v>
+      </c>
+      <c r="D11" t="n">
+        <v>322.48</v>
+      </c>
+      <c r="E11" t="n">
+        <v>312.65</v>
+      </c>
+      <c r="F11" t="n">
+        <v>274.58</v>
+      </c>
+      <c r="G11" t="n">
+        <v>19.03</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>18-09-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>MCX</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>3267.7</v>
-      </c>
-      <c r="D9" t="n">
-        <v>3158.46</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2990.82</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2695.57</v>
-      </c>
-      <c r="G9" t="n">
-        <v>21.22</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
+      <c r="C12" t="n">
+        <v>3260</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3158.2</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2990.66</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2695.53</v>
+      </c>
+      <c r="G12" t="n">
+        <v>20.94</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,28 +466,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>18-09-2026</t>
+          <t>19-09-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>412.5</v>
+        <v>117.27</v>
       </c>
       <c r="D2" t="n">
-        <v>409.2</v>
+        <v>116.33</v>
       </c>
       <c r="E2" t="n">
-        <v>400.39</v>
+        <v>114.03</v>
       </c>
       <c r="F2" t="n">
-        <v>399.71</v>
+        <v>112.31</v>
       </c>
       <c r="G2" t="n">
-        <v>3.2</v>
+        <v>4.42</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -503,28 +503,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>18-09-2026</t>
+          <t>19-09-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>117.27</v>
+        <v>548.15</v>
       </c>
       <c r="D3" t="n">
-        <v>116.33</v>
+        <v>524.02</v>
       </c>
       <c r="E3" t="n">
-        <v>114.03</v>
+        <v>525.63</v>
       </c>
       <c r="F3" t="n">
-        <v>112.31</v>
+        <v>523.7</v>
       </c>
       <c r="G3" t="n">
-        <v>4.42</v>
+        <v>4.67</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -540,28 +540,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>18-09-2026</t>
+          <t>19-09-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>548.15</v>
+        <v>11282</v>
       </c>
       <c r="D4" t="n">
-        <v>524.02</v>
+        <v>11275.37</v>
       </c>
       <c r="E4" t="n">
-        <v>525.63</v>
+        <v>11096.88</v>
       </c>
       <c r="F4" t="n">
-        <v>523.7</v>
+        <v>10586.22</v>
       </c>
       <c r="G4" t="n">
-        <v>4.67</v>
+        <v>6.57</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -577,28 +577,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>18-09-2026</t>
+          <t>19-09-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>292.6</v>
+        <v>732.75</v>
       </c>
       <c r="D5" t="n">
-        <v>287.58</v>
+        <v>722.89</v>
       </c>
       <c r="E5" t="n">
-        <v>283.63</v>
+        <v>727.97</v>
       </c>
       <c r="F5" t="n">
-        <v>278.82</v>
+        <v>686.01</v>
       </c>
       <c r="G5" t="n">
-        <v>4.94</v>
+        <v>6.81</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -614,28 +614,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>18-09-2026</t>
+          <t>19-09-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>11282</v>
+        <v>2270.1</v>
       </c>
       <c r="D6" t="n">
-        <v>11275.37</v>
+        <v>2137.24</v>
       </c>
       <c r="E6" t="n">
-        <v>11096.88</v>
+        <v>2019.77</v>
       </c>
       <c r="F6" t="n">
-        <v>10586.22</v>
+        <v>1959.51</v>
       </c>
       <c r="G6" t="n">
-        <v>6.57</v>
+        <v>15.85</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -651,28 +651,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>18-09-2026</t>
+          <t>19-09-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>732.75</v>
+        <v>326.85</v>
       </c>
       <c r="D7" t="n">
-        <v>722.89</v>
+        <v>322.48</v>
       </c>
       <c r="E7" t="n">
-        <v>727.97</v>
+        <v>312.65</v>
       </c>
       <c r="F7" t="n">
-        <v>686.01</v>
+        <v>274.58</v>
       </c>
       <c r="G7" t="n">
-        <v>6.81</v>
+        <v>19.03</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -688,28 +688,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>18-09-2026</t>
+          <t>19-09-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2208.8</v>
+        <v>3260</v>
       </c>
       <c r="D8" t="n">
-        <v>2201.01</v>
+        <v>3158.2</v>
       </c>
       <c r="E8" t="n">
-        <v>2134.01</v>
+        <v>2990.66</v>
       </c>
       <c r="F8" t="n">
-        <v>2051.99</v>
+        <v>2695.53</v>
       </c>
       <c r="G8" t="n">
-        <v>7.64</v>
+        <v>20.94</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -717,154 +717,6 @@
         </is>
       </c>
       <c r="I8" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>18-09-2026</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>APLAPOLLO</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>2270.1</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2137.24</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2019.77</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1959.51</v>
-      </c>
-      <c r="G9" t="n">
-        <v>15.85</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>18-09-2026</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>MOTILALOFS</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>1010</v>
-      </c>
-      <c r="D10" t="n">
-        <v>985.39</v>
-      </c>
-      <c r="E10" t="n">
-        <v>956.52</v>
-      </c>
-      <c r="F10" t="n">
-        <v>851.29</v>
-      </c>
-      <c r="G10" t="n">
-        <v>18.64</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>18-09-2026</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>ETERNAL</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>326.85</v>
-      </c>
-      <c r="D11" t="n">
-        <v>322.48</v>
-      </c>
-      <c r="E11" t="n">
-        <v>312.65</v>
-      </c>
-      <c r="F11" t="n">
-        <v>274.58</v>
-      </c>
-      <c r="G11" t="n">
-        <v>19.03</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>18-09-2026</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>3260</v>
-      </c>
-      <c r="D12" t="n">
-        <v>3158.2</v>
-      </c>
-      <c r="E12" t="n">
-        <v>2990.66</v>
-      </c>
-      <c r="F12" t="n">
-        <v>2695.53</v>
-      </c>
-      <c r="G12" t="n">
-        <v>20.94</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,23 +471,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>117.27</v>
+        <v>412.5</v>
       </c>
       <c r="D2" t="n">
-        <v>116.33</v>
+        <v>409.2</v>
       </c>
       <c r="E2" t="n">
-        <v>114.03</v>
+        <v>400.39</v>
       </c>
       <c r="F2" t="n">
-        <v>112.31</v>
+        <v>399.71</v>
       </c>
       <c r="G2" t="n">
-        <v>4.42</v>
+        <v>3.2</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>548.15</v>
+        <v>117.27</v>
       </c>
       <c r="D3" t="n">
-        <v>524.02</v>
+        <v>116.33</v>
       </c>
       <c r="E3" t="n">
-        <v>525.63</v>
+        <v>114.03</v>
       </c>
       <c r="F3" t="n">
-        <v>523.7</v>
+        <v>112.31</v>
       </c>
       <c r="G3" t="n">
-        <v>4.67</v>
+        <v>4.42</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11282</v>
+        <v>548.15</v>
       </c>
       <c r="D4" t="n">
-        <v>11275.37</v>
+        <v>524.02</v>
       </c>
       <c r="E4" t="n">
-        <v>11096.88</v>
+        <v>525.63</v>
       </c>
       <c r="F4" t="n">
-        <v>10586.22</v>
+        <v>523.7</v>
       </c>
       <c r="G4" t="n">
-        <v>6.57</v>
+        <v>4.67</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>732.75</v>
+        <v>292.6</v>
       </c>
       <c r="D5" t="n">
-        <v>722.89</v>
+        <v>287.58</v>
       </c>
       <c r="E5" t="n">
-        <v>727.97</v>
+        <v>283.63</v>
       </c>
       <c r="F5" t="n">
-        <v>686.01</v>
+        <v>278.82</v>
       </c>
       <c r="G5" t="n">
-        <v>6.81</v>
+        <v>4.94</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2270.1</v>
+        <v>11282</v>
       </c>
       <c r="D6" t="n">
-        <v>2137.24</v>
+        <v>11275.37</v>
       </c>
       <c r="E6" t="n">
-        <v>2019.77</v>
+        <v>11096.88</v>
       </c>
       <c r="F6" t="n">
-        <v>1959.51</v>
+        <v>10586.22</v>
       </c>
       <c r="G6" t="n">
-        <v>15.85</v>
+        <v>6.57</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -656,23 +656,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>326.85</v>
+        <v>732.75</v>
       </c>
       <c r="D7" t="n">
-        <v>322.48</v>
+        <v>722.89</v>
       </c>
       <c r="E7" t="n">
-        <v>312.65</v>
+        <v>727.97</v>
       </c>
       <c r="F7" t="n">
-        <v>274.58</v>
+        <v>686.01</v>
       </c>
       <c r="G7" t="n">
-        <v>19.03</v>
+        <v>6.81</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -693,30 +693,178 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>HYUNDAI</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2208.8</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2201.01</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2134.01</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2051.99</v>
+      </c>
+      <c r="G8" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>19-09-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2270.1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2137.24</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2019.77</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1959.51</v>
+      </c>
+      <c r="G9" t="n">
+        <v>15.85</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>19-09-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1010</v>
+      </c>
+      <c r="D10" t="n">
+        <v>985.39</v>
+      </c>
+      <c r="E10" t="n">
+        <v>956.52</v>
+      </c>
+      <c r="F10" t="n">
+        <v>851.29</v>
+      </c>
+      <c r="G10" t="n">
+        <v>18.64</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>19-09-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>326.85</v>
+      </c>
+      <c r="D11" t="n">
+        <v>322.48</v>
+      </c>
+      <c r="E11" t="n">
+        <v>312.65</v>
+      </c>
+      <c r="F11" t="n">
+        <v>274.58</v>
+      </c>
+      <c r="G11" t="n">
+        <v>19.03</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>19-09-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>MCX</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C12" t="n">
         <v>3260</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D12" t="n">
         <v>3158.2</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E12" t="n">
         <v>2990.66</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F12" t="n">
         <v>2695.53</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G12" t="n">
         <v>20.94</v>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,28 +466,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>19-09-2026</t>
+          <t>21-09-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>412.5</v>
+        <v>117.27</v>
       </c>
       <c r="D2" t="n">
-        <v>409.2</v>
+        <v>116.33</v>
       </c>
       <c r="E2" t="n">
-        <v>400.39</v>
+        <v>114.03</v>
       </c>
       <c r="F2" t="n">
-        <v>399.71</v>
+        <v>112.31</v>
       </c>
       <c r="G2" t="n">
-        <v>3.2</v>
+        <v>4.42</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -503,28 +503,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>19-09-2026</t>
+          <t>21-09-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>117.27</v>
+        <v>548.15</v>
       </c>
       <c r="D3" t="n">
-        <v>116.33</v>
+        <v>524.02</v>
       </c>
       <c r="E3" t="n">
-        <v>114.03</v>
+        <v>525.63</v>
       </c>
       <c r="F3" t="n">
-        <v>112.31</v>
+        <v>523.7</v>
       </c>
       <c r="G3" t="n">
-        <v>4.42</v>
+        <v>4.67</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -540,28 +540,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>19-09-2026</t>
+          <t>21-09-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>548.15</v>
+        <v>11217</v>
       </c>
       <c r="D4" t="n">
-        <v>524.02</v>
+        <v>11210.4</v>
       </c>
       <c r="E4" t="n">
-        <v>525.63</v>
+        <v>11032.95</v>
       </c>
       <c r="F4" t="n">
-        <v>523.7</v>
+        <v>10525.23</v>
       </c>
       <c r="G4" t="n">
-        <v>4.67</v>
+        <v>6.57</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -577,28 +577,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>19-09-2026</t>
+          <t>21-09-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>292.6</v>
+        <v>732.75</v>
       </c>
       <c r="D5" t="n">
-        <v>287.58</v>
+        <v>722.89</v>
       </c>
       <c r="E5" t="n">
-        <v>283.63</v>
+        <v>727.97</v>
       </c>
       <c r="F5" t="n">
-        <v>278.82</v>
+        <v>686.01</v>
       </c>
       <c r="G5" t="n">
-        <v>4.94</v>
+        <v>6.81</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -614,28 +614,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>19-09-2026</t>
+          <t>21-09-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>11282</v>
+        <v>2208.8</v>
       </c>
       <c r="D6" t="n">
-        <v>11275.37</v>
+        <v>2201.01</v>
       </c>
       <c r="E6" t="n">
-        <v>11096.88</v>
+        <v>2134.01</v>
       </c>
       <c r="F6" t="n">
-        <v>10586.22</v>
+        <v>2051.99</v>
       </c>
       <c r="G6" t="n">
-        <v>6.57</v>
+        <v>7.64</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -651,28 +651,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>19-09-2026</t>
+          <t>21-09-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>732.75</v>
+        <v>2270.1</v>
       </c>
       <c r="D7" t="n">
-        <v>722.89</v>
+        <v>2137.24</v>
       </c>
       <c r="E7" t="n">
-        <v>727.97</v>
+        <v>2019.77</v>
       </c>
       <c r="F7" t="n">
-        <v>686.01</v>
+        <v>1959.51</v>
       </c>
       <c r="G7" t="n">
-        <v>6.81</v>
+        <v>15.85</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -688,28 +688,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>19-09-2026</t>
+          <t>21-09-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2208.8</v>
+        <v>326.85</v>
       </c>
       <c r="D8" t="n">
-        <v>2201.01</v>
+        <v>322.48</v>
       </c>
       <c r="E8" t="n">
-        <v>2134.01</v>
+        <v>312.65</v>
       </c>
       <c r="F8" t="n">
-        <v>2051.99</v>
+        <v>274.58</v>
       </c>
       <c r="G8" t="n">
-        <v>7.64</v>
+        <v>19.03</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -725,28 +725,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>19-09-2026</t>
+          <t>21-09-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2270.1</v>
+        <v>3260</v>
       </c>
       <c r="D9" t="n">
-        <v>2137.24</v>
+        <v>3158.2</v>
       </c>
       <c r="E9" t="n">
-        <v>2019.77</v>
+        <v>2990.66</v>
       </c>
       <c r="F9" t="n">
-        <v>1959.51</v>
+        <v>2695.53</v>
       </c>
       <c r="G9" t="n">
-        <v>15.85</v>
+        <v>20.94</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -754,117 +754,6 @@
         </is>
       </c>
       <c r="I9" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>19-09-2026</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>MOTILALOFS</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>1010</v>
-      </c>
-      <c r="D10" t="n">
-        <v>985.39</v>
-      </c>
-      <c r="E10" t="n">
-        <v>956.52</v>
-      </c>
-      <c r="F10" t="n">
-        <v>851.29</v>
-      </c>
-      <c r="G10" t="n">
-        <v>18.64</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>19-09-2026</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>ETERNAL</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>326.85</v>
-      </c>
-      <c r="D11" t="n">
-        <v>322.48</v>
-      </c>
-      <c r="E11" t="n">
-        <v>312.65</v>
-      </c>
-      <c r="F11" t="n">
-        <v>274.58</v>
-      </c>
-      <c r="G11" t="n">
-        <v>19.03</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>19-09-2026</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>3260</v>
-      </c>
-      <c r="D12" t="n">
-        <v>3158.2</v>
-      </c>
-      <c r="E12" t="n">
-        <v>2990.66</v>
-      </c>
-      <c r="F12" t="n">
-        <v>2695.53</v>
-      </c>
-      <c r="G12" t="n">
-        <v>20.94</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,23 +471,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>117.27</v>
+        <v>288.3</v>
       </c>
       <c r="D2" t="n">
-        <v>116.33</v>
+        <v>287.85</v>
       </c>
       <c r="E2" t="n">
-        <v>114.03</v>
+        <v>283.82</v>
       </c>
       <c r="F2" t="n">
-        <v>112.31</v>
+        <v>278.87</v>
       </c>
       <c r="G2" t="n">
-        <v>4.42</v>
+        <v>3.38</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>548.15</v>
+        <v>117.4</v>
       </c>
       <c r="D3" t="n">
-        <v>524.02</v>
+        <v>116.46</v>
       </c>
       <c r="E3" t="n">
-        <v>525.63</v>
+        <v>114.25</v>
       </c>
       <c r="F3" t="n">
-        <v>523.7</v>
+        <v>112.31</v>
       </c>
       <c r="G3" t="n">
-        <v>4.67</v>
+        <v>4.53</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11217</v>
+        <v>418.4</v>
       </c>
       <c r="D4" t="n">
-        <v>11210.4</v>
+        <v>410.03</v>
       </c>
       <c r="E4" t="n">
-        <v>11032.95</v>
+        <v>401.08</v>
       </c>
       <c r="F4" t="n">
-        <v>10525.23</v>
+        <v>399.67</v>
       </c>
       <c r="G4" t="n">
-        <v>6.57</v>
+        <v>4.69</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>732.75</v>
+        <v>566.7</v>
       </c>
       <c r="D5" t="n">
-        <v>722.89</v>
+        <v>526.4400000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>727.97</v>
+        <v>526.1900000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>686.01</v>
+        <v>523.84</v>
       </c>
       <c r="G5" t="n">
-        <v>6.81</v>
+        <v>8.18</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2208.8</v>
+        <v>11400</v>
       </c>
       <c r="D6" t="n">
-        <v>2201.01</v>
+        <v>11217.13</v>
       </c>
       <c r="E6" t="n">
-        <v>2134.01</v>
+        <v>11049.09</v>
       </c>
       <c r="F6" t="n">
-        <v>2051.99</v>
+        <v>10527.13</v>
       </c>
       <c r="G6" t="n">
-        <v>7.64</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -656,23 +656,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2270.1</v>
+        <v>747.45</v>
       </c>
       <c r="D7" t="n">
-        <v>2137.24</v>
+        <v>723.51</v>
       </c>
       <c r="E7" t="n">
-        <v>2019.77</v>
+        <v>728.15</v>
       </c>
       <c r="F7" t="n">
-        <v>1959.51</v>
+        <v>686.12</v>
       </c>
       <c r="G7" t="n">
-        <v>15.85</v>
+        <v>8.94</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -693,23 +693,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>326.85</v>
+        <v>2191.8</v>
       </c>
       <c r="D8" t="n">
-        <v>322.48</v>
+        <v>2144.89</v>
       </c>
       <c r="E8" t="n">
-        <v>312.65</v>
+        <v>2027.03</v>
       </c>
       <c r="F8" t="n">
-        <v>274.58</v>
+        <v>1961.74</v>
       </c>
       <c r="G8" t="n">
-        <v>19.03</v>
+        <v>11.73</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -730,30 +730,104 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1009.2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>990.03</v>
+      </c>
+      <c r="E9" t="n">
+        <v>957.12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>851.77</v>
+      </c>
+      <c r="G9" t="n">
+        <v>18.48</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>21-09-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>330.55</v>
+      </c>
+      <c r="D10" t="n">
+        <v>323.16</v>
+      </c>
+      <c r="E10" t="n">
+        <v>313.56</v>
+      </c>
+      <c r="F10" t="n">
+        <v>274.76</v>
+      </c>
+      <c r="G10" t="n">
+        <v>20.31</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>21-09-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>MCX</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>3260</v>
-      </c>
-      <c r="D9" t="n">
-        <v>3158.2</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2990.66</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2695.53</v>
-      </c>
-      <c r="G9" t="n">
-        <v>20.94</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
+      <c r="C11" t="n">
+        <v>3253.2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3178.93</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3000.45</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2701.68</v>
+      </c>
+      <c r="G11" t="n">
+        <v>20.41</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,23 +471,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>288.3</v>
+        <v>414.8</v>
       </c>
       <c r="D2" t="n">
-        <v>287.85</v>
+        <v>409.91</v>
       </c>
       <c r="E2" t="n">
-        <v>283.82</v>
+        <v>401.01</v>
       </c>
       <c r="F2" t="n">
-        <v>278.87</v>
+        <v>399.65</v>
       </c>
       <c r="G2" t="n">
-        <v>3.38</v>
+        <v>3.79</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -512,19 +512,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>117.4</v>
+        <v>118</v>
       </c>
       <c r="D3" t="n">
-        <v>116.46</v>
+        <v>116.48</v>
       </c>
       <c r="E3" t="n">
-        <v>114.25</v>
+        <v>114.26</v>
       </c>
       <c r="F3" t="n">
-        <v>112.31</v>
+        <v>112.32</v>
       </c>
       <c r="G3" t="n">
-        <v>4.53</v>
+        <v>5.06</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>418.4</v>
+        <v>11409</v>
       </c>
       <c r="D4" t="n">
-        <v>410.03</v>
+        <v>11202.16</v>
       </c>
       <c r="E4" t="n">
-        <v>401.08</v>
+        <v>11054.4</v>
       </c>
       <c r="F4" t="n">
-        <v>399.67</v>
+        <v>10527.31</v>
       </c>
       <c r="G4" t="n">
-        <v>4.69</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -586,19 +586,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>566.7</v>
+        <v>568</v>
       </c>
       <c r="D5" t="n">
-        <v>526.4400000000001</v>
+        <v>528.34</v>
       </c>
       <c r="E5" t="n">
-        <v>526.1900000000001</v>
+        <v>526.3200000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>523.84</v>
+        <v>523.89</v>
       </c>
       <c r="G5" t="n">
-        <v>8.18</v>
+        <v>8.42</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>11400</v>
+        <v>745</v>
       </c>
       <c r="D6" t="n">
-        <v>11217.13</v>
+        <v>723.4299999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>11049.09</v>
+        <v>728.1</v>
       </c>
       <c r="F6" t="n">
-        <v>10527.13</v>
+        <v>686.1</v>
       </c>
       <c r="G6" t="n">
-        <v>8.289999999999999</v>
+        <v>8.58</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -656,23 +656,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>747.45</v>
+        <v>2181.1</v>
       </c>
       <c r="D7" t="n">
-        <v>723.51</v>
+        <v>2149.07</v>
       </c>
       <c r="E7" t="n">
-        <v>728.15</v>
+        <v>2033.35</v>
       </c>
       <c r="F7" t="n">
-        <v>686.12</v>
+        <v>1963.6</v>
       </c>
       <c r="G7" t="n">
-        <v>8.94</v>
+        <v>11.08</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -693,23 +693,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2191.8</v>
+        <v>995</v>
       </c>
       <c r="D8" t="n">
-        <v>2144.89</v>
+        <v>993.11</v>
       </c>
       <c r="E8" t="n">
-        <v>2027.03</v>
+        <v>956.95</v>
       </c>
       <c r="F8" t="n">
-        <v>1961.74</v>
+        <v>852.09</v>
       </c>
       <c r="G8" t="n">
-        <v>11.73</v>
+        <v>16.77</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -730,23 +730,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1009.2</v>
+        <v>3209</v>
       </c>
       <c r="D9" t="n">
-        <v>990.03</v>
+        <v>3194.54</v>
       </c>
       <c r="E9" t="n">
-        <v>957.12</v>
+        <v>3009.36</v>
       </c>
       <c r="F9" t="n">
-        <v>851.77</v>
+        <v>2707.69</v>
       </c>
       <c r="G9" t="n">
-        <v>18.48</v>
+        <v>18.51</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -771,19 +771,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>330.55</v>
+        <v>335.9</v>
       </c>
       <c r="D10" t="n">
-        <v>323.16</v>
+        <v>323.34</v>
       </c>
       <c r="E10" t="n">
-        <v>313.56</v>
+        <v>313.66</v>
       </c>
       <c r="F10" t="n">
-        <v>274.76</v>
+        <v>274.78</v>
       </c>
       <c r="G10" t="n">
-        <v>20.31</v>
+        <v>22.24</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -791,43 +791,6 @@
         </is>
       </c>
       <c r="I10" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>21-09-2026</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>3253.2</v>
-      </c>
-      <c r="D11" t="n">
-        <v>3178.93</v>
-      </c>
-      <c r="E11" t="n">
-        <v>3000.45</v>
-      </c>
-      <c r="F11" t="n">
-        <v>2701.68</v>
-      </c>
-      <c r="G11" t="n">
-        <v>20.41</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>21-09-2026</t>
+          <t>22-09-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>414.8</v>
+        <v>414</v>
       </c>
       <c r="D2" t="n">
-        <v>409.91</v>
+        <v>409.89</v>
       </c>
       <c r="E2" t="n">
-        <v>401.01</v>
+        <v>400.99</v>
       </c>
       <c r="F2" t="n">
         <v>399.65</v>
       </c>
       <c r="G2" t="n">
-        <v>3.79</v>
+        <v>3.59</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -503,7 +503,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>21-09-2026</t>
+          <t>22-09-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -512,19 +512,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>118</v>
+        <v>117.55</v>
       </c>
       <c r="D3" t="n">
-        <v>116.48</v>
+        <v>116.46</v>
       </c>
       <c r="E3" t="n">
-        <v>114.26</v>
+        <v>114.25</v>
       </c>
       <c r="F3" t="n">
-        <v>112.32</v>
+        <v>112.31</v>
       </c>
       <c r="G3" t="n">
-        <v>5.06</v>
+        <v>4.66</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -540,7 +540,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>21-09-2026</t>
+          <t>22-09-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -549,19 +549,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11409</v>
+        <v>11323</v>
       </c>
       <c r="D4" t="n">
-        <v>11202.16</v>
+        <v>11199.29</v>
       </c>
       <c r="E4" t="n">
-        <v>11054.4</v>
+        <v>11052.68</v>
       </c>
       <c r="F4" t="n">
-        <v>10527.31</v>
+        <v>10526.88</v>
       </c>
       <c r="G4" t="n">
-        <v>8.380000000000001</v>
+        <v>7.56</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -577,28 +577,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>21-09-2026</t>
+          <t>22-09-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>568</v>
+        <v>741.9</v>
       </c>
       <c r="D5" t="n">
-        <v>528.34</v>
+        <v>723.33</v>
       </c>
       <c r="E5" t="n">
-        <v>526.3200000000001</v>
+        <v>728.04</v>
       </c>
       <c r="F5" t="n">
-        <v>523.89</v>
+        <v>686.09</v>
       </c>
       <c r="G5" t="n">
-        <v>8.42</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -614,28 +614,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>21-09-2026</t>
+          <t>22-09-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>745</v>
+        <v>573</v>
       </c>
       <c r="D6" t="n">
-        <v>723.4299999999999</v>
+        <v>528.5</v>
       </c>
       <c r="E6" t="n">
-        <v>728.1</v>
+        <v>526.42</v>
       </c>
       <c r="F6" t="n">
-        <v>686.1</v>
+        <v>523.92</v>
       </c>
       <c r="G6" t="n">
-        <v>8.58</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>21-09-2026</t>
+          <t>22-09-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -660,19 +660,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2181.1</v>
+        <v>2178.5</v>
       </c>
       <c r="D7" t="n">
-        <v>2149.07</v>
+        <v>2148.99</v>
       </c>
       <c r="E7" t="n">
-        <v>2033.35</v>
+        <v>2033.3</v>
       </c>
       <c r="F7" t="n">
-        <v>1963.6</v>
+        <v>1963.58</v>
       </c>
       <c r="G7" t="n">
-        <v>11.08</v>
+        <v>10.95</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>21-09-2026</t>
+          <t>22-09-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -697,19 +697,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>995</v>
+        <v>1020.8</v>
       </c>
       <c r="D8" t="n">
-        <v>993.11</v>
+        <v>993.97</v>
       </c>
       <c r="E8" t="n">
-        <v>956.95</v>
+        <v>957.47</v>
       </c>
       <c r="F8" t="n">
-        <v>852.09</v>
+        <v>852.22</v>
       </c>
       <c r="G8" t="n">
-        <v>16.77</v>
+        <v>19.78</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>21-09-2026</t>
+          <t>22-09-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3209</v>
+        <v>3269</v>
       </c>
       <c r="D9" t="n">
-        <v>3194.54</v>
+        <v>3196.54</v>
       </c>
       <c r="E9" t="n">
-        <v>3009.36</v>
+        <v>3010.56</v>
       </c>
       <c r="F9" t="n">
-        <v>2707.69</v>
+        <v>2707.99</v>
       </c>
       <c r="G9" t="n">
-        <v>18.51</v>
+        <v>20.72</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>21-09-2026</t>
+          <t>22-09-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -771,19 +771,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>335.9</v>
+        <v>336.95</v>
       </c>
       <c r="D10" t="n">
-        <v>323.34</v>
+        <v>323.38</v>
       </c>
       <c r="E10" t="n">
-        <v>313.66</v>
+        <v>313.68</v>
       </c>
       <c r="F10" t="n">
-        <v>274.78</v>
+        <v>274.79</v>
       </c>
       <c r="G10" t="n">
-        <v>22.24</v>
+        <v>22.62</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>414</v>
+        <v>412.65</v>
       </c>
       <c r="D2" t="n">
-        <v>409.89</v>
+        <v>410.57</v>
       </c>
       <c r="E2" t="n">
-        <v>400.99</v>
+        <v>401.7</v>
       </c>
       <c r="F2" t="n">
-        <v>399.65</v>
+        <v>399.56</v>
       </c>
       <c r="G2" t="n">
-        <v>3.59</v>
+        <v>3.28</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -512,19 +512,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>117.55</v>
+        <v>117</v>
       </c>
       <c r="D3" t="n">
-        <v>116.46</v>
+        <v>116.58</v>
       </c>
       <c r="E3" t="n">
-        <v>114.25</v>
+        <v>114.5</v>
       </c>
       <c r="F3" t="n">
         <v>112.31</v>
       </c>
       <c r="G3" t="n">
-        <v>4.66</v>
+        <v>4.18</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11323</v>
+        <v>736.25</v>
       </c>
       <c r="D4" t="n">
-        <v>11199.29</v>
+        <v>723.84</v>
       </c>
       <c r="E4" t="n">
-        <v>11052.68</v>
+        <v>728.16</v>
       </c>
       <c r="F4" t="n">
-        <v>10526.88</v>
+        <v>686.15</v>
       </c>
       <c r="G4" t="n">
-        <v>7.56</v>
+        <v>7.3</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>741.9</v>
+        <v>565</v>
       </c>
       <c r="D5" t="n">
-        <v>723.33</v>
+        <v>530.77</v>
       </c>
       <c r="E5" t="n">
-        <v>728.04</v>
+        <v>526.84</v>
       </c>
       <c r="F5" t="n">
-        <v>686.09</v>
+        <v>524.0599999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>8.130000000000001</v>
+        <v>7.81</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>573</v>
+        <v>1805</v>
       </c>
       <c r="D6" t="n">
-        <v>528.5</v>
+        <v>1795.75</v>
       </c>
       <c r="E6" t="n">
-        <v>526.42</v>
+        <v>1715.08</v>
       </c>
       <c r="F6" t="n">
-        <v>523.92</v>
+        <v>1650.21</v>
       </c>
       <c r="G6" t="n">
-        <v>9.369999999999999</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -660,19 +660,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2178.5</v>
+        <v>2195</v>
       </c>
       <c r="D7" t="n">
-        <v>2148.99</v>
+        <v>2155.41</v>
       </c>
       <c r="E7" t="n">
-        <v>2033.3</v>
+        <v>2041.41</v>
       </c>
       <c r="F7" t="n">
-        <v>1963.58</v>
+        <v>1965.75</v>
       </c>
       <c r="G7" t="n">
-        <v>10.95</v>
+        <v>11.66</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -697,19 +697,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1020.8</v>
+        <v>1007</v>
       </c>
       <c r="D8" t="n">
-        <v>993.97</v>
+        <v>997.08</v>
       </c>
       <c r="E8" t="n">
-        <v>957.47</v>
+        <v>957.75</v>
       </c>
       <c r="F8" t="n">
-        <v>852.22</v>
+        <v>852.74</v>
       </c>
       <c r="G8" t="n">
-        <v>19.78</v>
+        <v>18.09</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3269</v>
+        <v>3262.6</v>
       </c>
       <c r="D9" t="n">
-        <v>3196.54</v>
+        <v>3207.03</v>
       </c>
       <c r="E9" t="n">
-        <v>3010.56</v>
+        <v>3016.93</v>
       </c>
       <c r="F9" t="n">
-        <v>2707.99</v>
+        <v>2713.68</v>
       </c>
       <c r="G9" t="n">
-        <v>20.72</v>
+        <v>20.23</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -771,19 +771,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>336.95</v>
+        <v>342</v>
       </c>
       <c r="D10" t="n">
-        <v>323.38</v>
+        <v>324.14</v>
       </c>
       <c r="E10" t="n">
-        <v>313.68</v>
+        <v>314.78</v>
       </c>
       <c r="F10" t="n">
-        <v>274.79</v>
+        <v>275.03</v>
       </c>
       <c r="G10" t="n">
-        <v>22.62</v>
+        <v>24.35</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>22-09-2026</t>
+          <t>23-09-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,7 +503,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>22-09-2026</t>
+          <t>23-09-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -540,28 +540,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>22-09-2026</t>
+          <t>23-09-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>736.25</v>
+        <v>565</v>
       </c>
       <c r="D4" t="n">
-        <v>723.84</v>
+        <v>530.77</v>
       </c>
       <c r="E4" t="n">
-        <v>728.16</v>
+        <v>526.84</v>
       </c>
       <c r="F4" t="n">
-        <v>686.15</v>
+        <v>524.0599999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>7.3</v>
+        <v>7.81</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -577,28 +577,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>22-09-2026</t>
+          <t>23-09-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>565</v>
+        <v>3262.6</v>
       </c>
       <c r="D5" t="n">
-        <v>530.77</v>
+        <v>3207.03</v>
       </c>
       <c r="E5" t="n">
-        <v>526.84</v>
+        <v>3016.93</v>
       </c>
       <c r="F5" t="n">
-        <v>524.0599999999999</v>
+        <v>2713.68</v>
       </c>
       <c r="G5" t="n">
-        <v>7.81</v>
+        <v>20.23</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -614,28 +614,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>22-09-2026</t>
+          <t>23-09-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1805</v>
+        <v>342</v>
       </c>
       <c r="D6" t="n">
-        <v>1795.75</v>
+        <v>324.14</v>
       </c>
       <c r="E6" t="n">
-        <v>1715.08</v>
+        <v>314.78</v>
       </c>
       <c r="F6" t="n">
-        <v>1650.21</v>
+        <v>275.03</v>
       </c>
       <c r="G6" t="n">
-        <v>9.380000000000001</v>
+        <v>24.35</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -643,154 +643,6 @@
         </is>
       </c>
       <c r="I6" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>22-09-2026</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>APLAPOLLO</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>2195</v>
-      </c>
-      <c r="D7" t="n">
-        <v>2155.41</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2041.41</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1965.75</v>
-      </c>
-      <c r="G7" t="n">
-        <v>11.66</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>22-09-2026</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>MOTILALOFS</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>1007</v>
-      </c>
-      <c r="D8" t="n">
-        <v>997.08</v>
-      </c>
-      <c r="E8" t="n">
-        <v>957.75</v>
-      </c>
-      <c r="F8" t="n">
-        <v>852.74</v>
-      </c>
-      <c r="G8" t="n">
-        <v>18.09</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>22-09-2026</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>3262.6</v>
-      </c>
-      <c r="D9" t="n">
-        <v>3207.03</v>
-      </c>
-      <c r="E9" t="n">
-        <v>3016.93</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2713.68</v>
-      </c>
-      <c r="G9" t="n">
-        <v>20.23</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>22-09-2026</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>ETERNAL</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>342</v>
-      </c>
-      <c r="D10" t="n">
-        <v>324.14</v>
-      </c>
-      <c r="E10" t="n">
-        <v>314.78</v>
-      </c>
-      <c r="F10" t="n">
-        <v>275.03</v>
-      </c>
-      <c r="G10" t="n">
-        <v>24.35</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>412.65</v>
+        <v>415.75</v>
       </c>
       <c r="D2" t="n">
-        <v>410.57</v>
+        <v>411.41</v>
       </c>
       <c r="E2" t="n">
-        <v>401.7</v>
+        <v>402.46</v>
       </c>
       <c r="F2" t="n">
-        <v>399.56</v>
+        <v>399.51</v>
       </c>
       <c r="G2" t="n">
-        <v>3.28</v>
+        <v>4.06</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -512,19 +512,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>117</v>
+        <v>117.81</v>
       </c>
       <c r="D3" t="n">
-        <v>116.58</v>
+        <v>116.54</v>
       </c>
       <c r="E3" t="n">
-        <v>114.5</v>
+        <v>114.74</v>
       </c>
       <c r="F3" t="n">
-        <v>112.31</v>
+        <v>112.34</v>
       </c>
       <c r="G3" t="n">
-        <v>4.18</v>
+        <v>4.87</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>565</v>
+        <v>11355</v>
       </c>
       <c r="D4" t="n">
-        <v>530.77</v>
+        <v>11186.97</v>
       </c>
       <c r="E4" t="n">
-        <v>526.84</v>
+        <v>11087.29</v>
       </c>
       <c r="F4" t="n">
-        <v>524.0599999999999</v>
+        <v>10531.26</v>
       </c>
       <c r="G4" t="n">
-        <v>7.81</v>
+        <v>7.82</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3262.6</v>
+        <v>741.55</v>
       </c>
       <c r="D5" t="n">
-        <v>3207.03</v>
+        <v>724.01</v>
       </c>
       <c r="E5" t="n">
-        <v>3016.93</v>
+        <v>728.26</v>
       </c>
       <c r="F5" t="n">
-        <v>2713.68</v>
+        <v>686.17</v>
       </c>
       <c r="G5" t="n">
-        <v>20.23</v>
+        <v>8.07</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,30 +619,215 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>572.5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>533.25</v>
+      </c>
+      <c r="E6" t="n">
+        <v>527.51</v>
+      </c>
+      <c r="F6" t="n">
+        <v>524.36</v>
+      </c>
+      <c r="G6" t="n">
+        <v>9.18</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>23-09-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>POLICYBZR</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1825.5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1796.43</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1715.49</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1650.31</v>
+      </c>
+      <c r="G7" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>23-09-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2183.7</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2155.03</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2041.18</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1965.69</v>
+      </c>
+      <c r="G8" t="n">
+        <v>11.09</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>23-09-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>3274</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3217.4</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3024.7</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2719.9</v>
+      </c>
+      <c r="G9" t="n">
+        <v>20.37</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>23-09-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1050.7</v>
+      </c>
+      <c r="D10" t="n">
+        <v>998.54</v>
+      </c>
+      <c r="E10" t="n">
+        <v>958.63</v>
+      </c>
+      <c r="F10" t="n">
+        <v>852.96</v>
+      </c>
+      <c r="G10" t="n">
+        <v>23.18</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>23-09-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>ETERNAL</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>342</v>
-      </c>
-      <c r="D6" t="n">
-        <v>324.14</v>
-      </c>
-      <c r="E6" t="n">
-        <v>314.78</v>
-      </c>
-      <c r="F6" t="n">
-        <v>275.03</v>
-      </c>
-      <c r="G6" t="n">
-        <v>24.35</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="C11" t="n">
+        <v>342.95</v>
+      </c>
+      <c r="D11" t="n">
+        <v>325.1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>315.74</v>
+      </c>
+      <c r="F11" t="n">
+        <v>275.32</v>
+      </c>
+      <c r="G11" t="n">
+        <v>24.56</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>415.75</v>
+        <v>413.25</v>
       </c>
       <c r="D2" t="n">
-        <v>411.41</v>
+        <v>411.33</v>
       </c>
       <c r="E2" t="n">
-        <v>402.46</v>
+        <v>402.41</v>
       </c>
       <c r="F2" t="n">
-        <v>399.51</v>
+        <v>399.5</v>
       </c>
       <c r="G2" t="n">
-        <v>4.06</v>
+        <v>3.44</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -512,19 +512,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>117.81</v>
+        <v>118.3</v>
       </c>
       <c r="D3" t="n">
-        <v>116.54</v>
+        <v>116.55</v>
       </c>
       <c r="E3" t="n">
-        <v>114.74</v>
+        <v>114.75</v>
       </c>
       <c r="F3" t="n">
         <v>112.34</v>
       </c>
       <c r="G3" t="n">
-        <v>4.87</v>
+        <v>5.31</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11355</v>
+        <v>743.7</v>
       </c>
       <c r="D4" t="n">
-        <v>11186.97</v>
+        <v>724.49</v>
       </c>
       <c r="E4" t="n">
-        <v>11087.29</v>
+        <v>728.17</v>
       </c>
       <c r="F4" t="n">
-        <v>10531.26</v>
+        <v>686.29</v>
       </c>
       <c r="G4" t="n">
-        <v>7.82</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>741.55</v>
+        <v>11449</v>
       </c>
       <c r="D5" t="n">
-        <v>724.01</v>
+        <v>11190.1</v>
       </c>
       <c r="E5" t="n">
-        <v>728.26</v>
+        <v>11089.17</v>
       </c>
       <c r="F5" t="n">
-        <v>686.17</v>
+        <v>10531.73</v>
       </c>
       <c r="G5" t="n">
-        <v>8.07</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -656,23 +656,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1825.5</v>
+        <v>2195</v>
       </c>
       <c r="D7" t="n">
-        <v>1796.43</v>
+        <v>2162.26</v>
       </c>
       <c r="E7" t="n">
-        <v>1715.49</v>
+        <v>2049.1</v>
       </c>
       <c r="F7" t="n">
-        <v>1650.31</v>
+        <v>1968.08</v>
       </c>
       <c r="G7" t="n">
-        <v>10.62</v>
+        <v>11.53</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -693,23 +693,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2183.7</v>
+        <v>1886.3</v>
       </c>
       <c r="D8" t="n">
-        <v>2155.03</v>
+        <v>1800.66</v>
       </c>
       <c r="E8" t="n">
-        <v>2041.18</v>
+        <v>1720.59</v>
       </c>
       <c r="F8" t="n">
-        <v>1965.69</v>
+        <v>1650.17</v>
       </c>
       <c r="G8" t="n">
-        <v>11.09</v>
+        <v>14.31</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -730,23 +730,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3274</v>
+        <v>1042.5</v>
       </c>
       <c r="D9" t="n">
-        <v>3217.4</v>
+        <v>1001.8</v>
       </c>
       <c r="E9" t="n">
-        <v>3024.7</v>
+        <v>959.25</v>
       </c>
       <c r="F9" t="n">
-        <v>2719.9</v>
+        <v>853.76</v>
       </c>
       <c r="G9" t="n">
-        <v>20.37</v>
+        <v>22.11</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -767,23 +767,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1050.7</v>
+        <v>3374</v>
       </c>
       <c r="D10" t="n">
-        <v>998.54</v>
+        <v>3220.73</v>
       </c>
       <c r="E10" t="n">
-        <v>958.63</v>
+        <v>3026.7</v>
       </c>
       <c r="F10" t="n">
-        <v>852.96</v>
+        <v>2720.4</v>
       </c>
       <c r="G10" t="n">
-        <v>23.18</v>
+        <v>24.03</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -808,10 +808,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>342.95</v>
+        <v>342.65</v>
       </c>
       <c r="D11" t="n">
-        <v>325.1</v>
+        <v>325.09</v>
       </c>
       <c r="E11" t="n">
         <v>315.74</v>
@@ -820,7 +820,7 @@
         <v>275.32</v>
       </c>
       <c r="G11" t="n">
-        <v>24.56</v>
+        <v>24.46</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,28 +466,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>23-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>413.25</v>
+        <v>118.3</v>
       </c>
       <c r="D2" t="n">
-        <v>411.33</v>
+        <v>116.55</v>
       </c>
       <c r="E2" t="n">
-        <v>402.41</v>
+        <v>114.75</v>
       </c>
       <c r="F2" t="n">
-        <v>399.5</v>
+        <v>112.34</v>
       </c>
       <c r="G2" t="n">
-        <v>3.44</v>
+        <v>5.31</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -503,28 +503,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>23-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>118.3</v>
+        <v>743.7</v>
       </c>
       <c r="D3" t="n">
-        <v>116.55</v>
+        <v>724.49</v>
       </c>
       <c r="E3" t="n">
-        <v>114.75</v>
+        <v>728.17</v>
       </c>
       <c r="F3" t="n">
-        <v>112.34</v>
+        <v>686.29</v>
       </c>
       <c r="G3" t="n">
-        <v>5.31</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -540,28 +540,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>23-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>743.7</v>
+        <v>572.5</v>
       </c>
       <c r="D4" t="n">
-        <v>724.49</v>
+        <v>533.25</v>
       </c>
       <c r="E4" t="n">
-        <v>728.17</v>
+        <v>527.51</v>
       </c>
       <c r="F4" t="n">
-        <v>686.29</v>
+        <v>524.36</v>
       </c>
       <c r="G4" t="n">
-        <v>8.369999999999999</v>
+        <v>9.18</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -577,28 +577,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>23-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>11449</v>
+        <v>1886.3</v>
       </c>
       <c r="D5" t="n">
-        <v>11190.1</v>
+        <v>1800.66</v>
       </c>
       <c r="E5" t="n">
-        <v>11089.17</v>
+        <v>1720.59</v>
       </c>
       <c r="F5" t="n">
-        <v>10531.73</v>
+        <v>1650.17</v>
       </c>
       <c r="G5" t="n">
-        <v>8.710000000000001</v>
+        <v>14.31</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -614,28 +614,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>23-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>572.5</v>
+        <v>3374</v>
       </c>
       <c r="D6" t="n">
-        <v>533.25</v>
+        <v>3220.73</v>
       </c>
       <c r="E6" t="n">
-        <v>527.51</v>
+        <v>3026.7</v>
       </c>
       <c r="F6" t="n">
-        <v>524.36</v>
+        <v>2720.4</v>
       </c>
       <c r="G6" t="n">
-        <v>9.18</v>
+        <v>24.03</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -651,28 +651,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>23-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2195</v>
+        <v>342.65</v>
       </c>
       <c r="D7" t="n">
-        <v>2162.26</v>
+        <v>325.09</v>
       </c>
       <c r="E7" t="n">
-        <v>2049.1</v>
+        <v>315.74</v>
       </c>
       <c r="F7" t="n">
-        <v>1968.08</v>
+        <v>275.32</v>
       </c>
       <c r="G7" t="n">
-        <v>11.53</v>
+        <v>24.46</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -680,154 +680,6 @@
         </is>
       </c>
       <c r="I7" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>23-09-2026</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>POLICYBZR</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>1886.3</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1800.66</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1720.59</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1650.17</v>
-      </c>
-      <c r="G8" t="n">
-        <v>14.31</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>23-09-2026</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>MOTILALOFS</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>1042.5</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1001.8</v>
-      </c>
-      <c r="E9" t="n">
-        <v>959.25</v>
-      </c>
-      <c r="F9" t="n">
-        <v>853.76</v>
-      </c>
-      <c r="G9" t="n">
-        <v>22.11</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>23-09-2026</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>3374</v>
-      </c>
-      <c r="D10" t="n">
-        <v>3220.73</v>
-      </c>
-      <c r="E10" t="n">
-        <v>3026.7</v>
-      </c>
-      <c r="F10" t="n">
-        <v>2720.4</v>
-      </c>
-      <c r="G10" t="n">
-        <v>24.03</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>23-09-2026</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>ETERNAL</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>342.65</v>
-      </c>
-      <c r="D11" t="n">
-        <v>325.09</v>
-      </c>
-      <c r="E11" t="n">
-        <v>315.74</v>
-      </c>
-      <c r="F11" t="n">
-        <v>275.32</v>
-      </c>
-      <c r="G11" t="n">
-        <v>24.46</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>118.3</v>
+        <v>117.61</v>
       </c>
       <c r="D2" t="n">
         <v>116.55</v>
       </c>
       <c r="E2" t="n">
-        <v>114.75</v>
+        <v>115</v>
       </c>
       <c r="F2" t="n">
-        <v>112.34</v>
+        <v>112.35</v>
       </c>
       <c r="G2" t="n">
-        <v>5.31</v>
+        <v>4.68</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>743.7</v>
+        <v>11189</v>
       </c>
       <c r="D3" t="n">
-        <v>724.49</v>
+        <v>11181.43</v>
       </c>
       <c r="E3" t="n">
-        <v>728.17</v>
+        <v>11083.97</v>
       </c>
       <c r="F3" t="n">
-        <v>686.29</v>
+        <v>10530.43</v>
       </c>
       <c r="G3" t="n">
-        <v>8.369999999999999</v>
+        <v>6.25</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -549,19 +549,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>572.5</v>
+        <v>570.25</v>
       </c>
       <c r="D4" t="n">
-        <v>533.25</v>
+        <v>535.86</v>
       </c>
       <c r="E4" t="n">
-        <v>527.51</v>
+        <v>528.1900000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>524.36</v>
+        <v>524.6</v>
       </c>
       <c r="G4" t="n">
-        <v>9.18</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1886.3</v>
+        <v>2189.8</v>
       </c>
       <c r="D5" t="n">
-        <v>1800.66</v>
+        <v>2162.09</v>
       </c>
       <c r="E5" t="n">
-        <v>1720.59</v>
+        <v>2049</v>
       </c>
       <c r="F5" t="n">
-        <v>1650.17</v>
+        <v>1968.05</v>
       </c>
       <c r="G5" t="n">
-        <v>14.31</v>
+        <v>11.27</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3374</v>
+        <v>1038.3</v>
       </c>
       <c r="D6" t="n">
-        <v>3220.73</v>
+        <v>1001.66</v>
       </c>
       <c r="E6" t="n">
-        <v>3026.7</v>
+        <v>959.17</v>
       </c>
       <c r="F6" t="n">
-        <v>2720.4</v>
+        <v>853.74</v>
       </c>
       <c r="G6" t="n">
-        <v>24.03</v>
+        <v>21.62</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -660,19 +660,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>342.65</v>
+        <v>341.05</v>
       </c>
       <c r="D7" t="n">
-        <v>325.09</v>
+        <v>325.86</v>
       </c>
       <c r="E7" t="n">
-        <v>315.74</v>
+        <v>316.83</v>
       </c>
       <c r="F7" t="n">
-        <v>275.32</v>
+        <v>275.57</v>
       </c>
       <c r="G7" t="n">
-        <v>24.46</v>
+        <v>23.76</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -680,6 +680,43 @@
         </is>
       </c>
       <c r="I7" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>24-09-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3422.2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3236.05</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3038.97</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2727.18</v>
+      </c>
+      <c r="G8" t="n">
+        <v>25.49</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>117.61</v>
+        <v>117.12</v>
       </c>
       <c r="D2" t="n">
-        <v>116.55</v>
+        <v>116.54</v>
       </c>
       <c r="E2" t="n">
-        <v>115</v>
+        <v>114.99</v>
       </c>
       <c r="F2" t="n">
         <v>112.35</v>
       </c>
       <c r="G2" t="n">
-        <v>4.68</v>
+        <v>4.24</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11189</v>
+        <v>564.25</v>
       </c>
       <c r="D3" t="n">
-        <v>11181.43</v>
+        <v>535.66</v>
       </c>
       <c r="E3" t="n">
-        <v>11083.97</v>
+        <v>528.0700000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>10530.43</v>
+        <v>524.5700000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>6.25</v>
+        <v>7.56</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>570.25</v>
+        <v>2184.8</v>
       </c>
       <c r="D4" t="n">
-        <v>535.86</v>
+        <v>2166.54</v>
       </c>
       <c r="E4" t="n">
-        <v>528.1900000000001</v>
+        <v>2057.09</v>
       </c>
       <c r="F4" t="n">
-        <v>524.6</v>
+        <v>1970.33</v>
       </c>
       <c r="G4" t="n">
-        <v>8.699999999999999</v>
+        <v>10.88</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2189.8</v>
+        <v>1022</v>
       </c>
       <c r="D5" t="n">
-        <v>2162.09</v>
+        <v>1005.95</v>
       </c>
       <c r="E5" t="n">
-        <v>2049</v>
+        <v>960.59</v>
       </c>
       <c r="F5" t="n">
-        <v>1968.05</v>
+        <v>854.66</v>
       </c>
       <c r="G5" t="n">
-        <v>11.27</v>
+        <v>19.58</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1038.3</v>
+        <v>335.5</v>
       </c>
       <c r="D6" t="n">
-        <v>1001.66</v>
+        <v>325.68</v>
       </c>
       <c r="E6" t="n">
-        <v>959.17</v>
+        <v>316.72</v>
       </c>
       <c r="F6" t="n">
-        <v>853.74</v>
+        <v>275.54</v>
       </c>
       <c r="G6" t="n">
-        <v>21.62</v>
+        <v>21.76</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -643,80 +643,6 @@
         </is>
       </c>
       <c r="I6" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>24-09-2026</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>ETERNAL</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>341.05</v>
-      </c>
-      <c r="D7" t="n">
-        <v>325.86</v>
-      </c>
-      <c r="E7" t="n">
-        <v>316.83</v>
-      </c>
-      <c r="F7" t="n">
-        <v>275.57</v>
-      </c>
-      <c r="G7" t="n">
-        <v>23.76</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>24-09-2026</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>3422.2</v>
-      </c>
-      <c r="D8" t="n">
-        <v>3236.05</v>
-      </c>
-      <c r="E8" t="n">
-        <v>3038.97</v>
-      </c>
-      <c r="F8" t="n">
-        <v>2727.18</v>
-      </c>
-      <c r="G8" t="n">
-        <v>25.49</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>25-09-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,7 +503,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>25-09-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -540,7 +540,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>25-09-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -577,28 +577,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>25-09-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1022</v>
+        <v>335.5</v>
       </c>
       <c r="D5" t="n">
-        <v>1005.95</v>
+        <v>325.68</v>
       </c>
       <c r="E5" t="n">
-        <v>960.59</v>
+        <v>316.72</v>
       </c>
       <c r="F5" t="n">
-        <v>854.66</v>
+        <v>275.54</v>
       </c>
       <c r="G5" t="n">
-        <v>19.58</v>
+        <v>21.76</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -606,43 +606,6 @@
         </is>
       </c>
       <c r="I5" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>24-09-2026</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>ETERNAL</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>335.5</v>
-      </c>
-      <c r="D6" t="n">
-        <v>325.68</v>
-      </c>
-      <c r="E6" t="n">
-        <v>316.72</v>
-      </c>
-      <c r="F6" t="n">
-        <v>275.54</v>
-      </c>
-      <c r="G6" t="n">
-        <v>21.76</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>117.12</v>
+        <v>116.89</v>
       </c>
       <c r="D2" t="n">
-        <v>116.54</v>
+        <v>116.5</v>
       </c>
       <c r="E2" t="n">
-        <v>114.99</v>
+        <v>115.21</v>
       </c>
       <c r="F2" t="n">
-        <v>112.35</v>
+        <v>112.37</v>
       </c>
       <c r="G2" t="n">
-        <v>4.24</v>
+        <v>4.03</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -512,19 +512,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>564.25</v>
+        <v>561.85</v>
       </c>
       <c r="D3" t="n">
-        <v>535.66</v>
+        <v>538.04</v>
       </c>
       <c r="E3" t="n">
-        <v>528.0700000000001</v>
+        <v>528.53</v>
       </c>
       <c r="F3" t="n">
-        <v>524.5700000000001</v>
+        <v>524.77</v>
       </c>
       <c r="G3" t="n">
-        <v>7.56</v>
+        <v>7.07</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -549,19 +549,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2184.8</v>
+        <v>2198.7</v>
       </c>
       <c r="D4" t="n">
-        <v>2166.54</v>
+        <v>2170.65</v>
       </c>
       <c r="E4" t="n">
-        <v>2057.09</v>
+        <v>2065.29</v>
       </c>
       <c r="F4" t="n">
-        <v>1970.33</v>
+        <v>1972.68</v>
       </c>
       <c r="G4" t="n">
-        <v>10.88</v>
+        <v>11.46</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -586,19 +586,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>335.5</v>
+        <v>333.2</v>
       </c>
       <c r="D5" t="n">
-        <v>325.68</v>
+        <v>326.17</v>
       </c>
       <c r="E5" t="n">
-        <v>316.72</v>
+        <v>317.65</v>
       </c>
       <c r="F5" t="n">
-        <v>275.54</v>
+        <v>275.79</v>
       </c>
       <c r="G5" t="n">
-        <v>21.76</v>
+        <v>20.82</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -606,6 +606,43 @@
         </is>
       </c>
       <c r="I5" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>25-09-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1033.5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1006.33</v>
+      </c>
+      <c r="E6" t="n">
+        <v>960.8200000000001</v>
+      </c>
+      <c r="F6" t="n">
+        <v>854.71</v>
+      </c>
+      <c r="G6" t="n">
+        <v>20.92</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -475,10 +475,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>116.89</v>
+        <v>116.6</v>
       </c>
       <c r="D2" t="n">
-        <v>116.5</v>
+        <v>116.49</v>
       </c>
       <c r="E2" t="n">
         <v>115.21</v>
@@ -487,7 +487,7 @@
         <v>112.37</v>
       </c>
       <c r="G2" t="n">
-        <v>4.03</v>
+        <v>3.77</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -512,19 +512,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>561.85</v>
+        <v>566</v>
       </c>
       <c r="D3" t="n">
-        <v>538.04</v>
+        <v>538.1799999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>528.53</v>
+        <v>528.61</v>
       </c>
       <c r="F3" t="n">
-        <v>524.77</v>
+        <v>524.8</v>
       </c>
       <c r="G3" t="n">
-        <v>7.07</v>
+        <v>7.85</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -549,19 +549,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2198.7</v>
+        <v>2214.7</v>
       </c>
       <c r="D4" t="n">
-        <v>2170.65</v>
+        <v>2171.19</v>
       </c>
       <c r="E4" t="n">
-        <v>2065.29</v>
+        <v>2065.61</v>
       </c>
       <c r="F4" t="n">
-        <v>1972.68</v>
+        <v>1972.76</v>
       </c>
       <c r="G4" t="n">
-        <v>11.46</v>
+        <v>12.26</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>333.2</v>
+        <v>1029</v>
       </c>
       <c r="D5" t="n">
-        <v>326.17</v>
+        <v>1010.12</v>
       </c>
       <c r="E5" t="n">
-        <v>317.65</v>
+        <v>961.83</v>
       </c>
       <c r="F5" t="n">
-        <v>275.79</v>
+        <v>855.67</v>
       </c>
       <c r="G5" t="n">
-        <v>20.82</v>
+        <v>20.26</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1033.5</v>
+        <v>335</v>
       </c>
       <c r="D6" t="n">
-        <v>1006.33</v>
+        <v>326.23</v>
       </c>
       <c r="E6" t="n">
-        <v>960.8200000000001</v>
+        <v>317.68</v>
       </c>
       <c r="F6" t="n">
-        <v>854.71</v>
+        <v>275.8</v>
       </c>
       <c r="G6" t="n">
-        <v>20.92</v>
+        <v>21.47</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>25-09-2026</t>
+          <t>26-09-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,7 +503,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>25-09-2026</t>
+          <t>26-09-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -540,7 +540,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>25-09-2026</t>
+          <t>26-09-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -577,28 +577,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>25-09-2026</t>
+          <t>26-09-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1029</v>
+        <v>335</v>
       </c>
       <c r="D5" t="n">
-        <v>1010.12</v>
+        <v>326.23</v>
       </c>
       <c r="E5" t="n">
-        <v>961.83</v>
+        <v>317.68</v>
       </c>
       <c r="F5" t="n">
-        <v>855.67</v>
+        <v>275.8</v>
       </c>
       <c r="G5" t="n">
-        <v>20.26</v>
+        <v>21.47</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -606,43 +606,6 @@
         </is>
       </c>
       <c r="I5" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>25-09-2026</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>ETERNAL</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>335</v>
-      </c>
-      <c r="D6" t="n">
-        <v>326.23</v>
-      </c>
-      <c r="E6" t="n">
-        <v>317.68</v>
-      </c>
-      <c r="F6" t="n">
-        <v>275.8</v>
-      </c>
-      <c r="G6" t="n">
-        <v>21.47</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -582,30 +582,67 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1029</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1010.12</v>
+      </c>
+      <c r="E5" t="n">
+        <v>961.83</v>
+      </c>
+      <c r="F5" t="n">
+        <v>855.67</v>
+      </c>
+      <c r="G5" t="n">
+        <v>20.26</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>26-09-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>ETERNAL</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C6" t="n">
         <v>335</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D6" t="n">
         <v>326.23</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E6" t="n">
         <v>317.68</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F6" t="n">
         <v>275.8</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G6" t="n">
         <v>21.47</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>26-09-2026</t>
+          <t>28-09-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,7 +503,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>26-09-2026</t>
+          <t>28-09-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -540,7 +540,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>26-09-2026</t>
+          <t>28-09-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -577,7 +577,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>26-09-2026</t>
+          <t>28-09-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -614,7 +614,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>26-09-2026</t>
+          <t>28-09-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -471,23 +471,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>116.6</v>
+        <v>290.9</v>
       </c>
       <c r="D2" t="n">
-        <v>116.49</v>
+        <v>288.86</v>
       </c>
       <c r="E2" t="n">
-        <v>115.21</v>
+        <v>284.85</v>
       </c>
       <c r="F2" t="n">
-        <v>112.37</v>
+        <v>279.32</v>
       </c>
       <c r="G2" t="n">
-        <v>3.77</v>
+        <v>4.14</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -512,19 +512,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>566</v>
+        <v>572.85</v>
       </c>
       <c r="D3" t="n">
-        <v>538.1799999999999</v>
+        <v>541</v>
       </c>
       <c r="E3" t="n">
-        <v>528.61</v>
+        <v>529.24</v>
       </c>
       <c r="F3" t="n">
-        <v>524.8</v>
+        <v>525.04</v>
       </c>
       <c r="G3" t="n">
-        <v>7.85</v>
+        <v>9.1</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -549,19 +549,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2214.7</v>
+        <v>2183</v>
       </c>
       <c r="D4" t="n">
-        <v>2171.19</v>
+        <v>2174.84</v>
       </c>
       <c r="E4" t="n">
-        <v>2065.61</v>
+        <v>2073.12</v>
       </c>
       <c r="F4" t="n">
-        <v>1972.76</v>
+        <v>1975.09</v>
       </c>
       <c r="G4" t="n">
-        <v>12.26</v>
+        <v>10.53</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -586,19 +586,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1029</v>
+        <v>1016.5</v>
       </c>
       <c r="D5" t="n">
-        <v>1010.12</v>
+        <v>1012.17</v>
       </c>
       <c r="E5" t="n">
-        <v>961.83</v>
+        <v>962.7</v>
       </c>
       <c r="F5" t="n">
-        <v>855.67</v>
+        <v>856.63</v>
       </c>
       <c r="G5" t="n">
-        <v>20.26</v>
+        <v>18.66</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -623,19 +623,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>335</v>
+        <v>329.15</v>
       </c>
       <c r="D6" t="n">
-        <v>326.23</v>
+        <v>326.6</v>
       </c>
       <c r="E6" t="n">
-        <v>317.68</v>
+        <v>318.53</v>
       </c>
       <c r="F6" t="n">
-        <v>275.8</v>
+        <v>275.99</v>
       </c>
       <c r="G6" t="n">
-        <v>21.47</v>
+        <v>19.26</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>290.9</v>
+        <v>289.85</v>
       </c>
       <c r="D2" t="n">
-        <v>288.86</v>
+        <v>288.83</v>
       </c>
       <c r="E2" t="n">
-        <v>284.85</v>
+        <v>284.83</v>
       </c>
       <c r="F2" t="n">
         <v>279.32</v>
       </c>
       <c r="G2" t="n">
-        <v>4.14</v>
+        <v>3.77</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -512,19 +512,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>572.85</v>
+        <v>564.15</v>
       </c>
       <c r="D3" t="n">
-        <v>541</v>
+        <v>540.71</v>
       </c>
       <c r="E3" t="n">
-        <v>529.24</v>
+        <v>529.0599999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>525.04</v>
+        <v>525</v>
       </c>
       <c r="G3" t="n">
-        <v>9.1</v>
+        <v>7.46</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -549,19 +549,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2183</v>
+        <v>2197</v>
       </c>
       <c r="D4" t="n">
-        <v>2174.84</v>
+        <v>2175.31</v>
       </c>
       <c r="E4" t="n">
-        <v>2073.12</v>
+        <v>2073.4</v>
       </c>
       <c r="F4" t="n">
-        <v>1975.09</v>
+        <v>1975.16</v>
       </c>
       <c r="G4" t="n">
-        <v>10.53</v>
+        <v>11.23</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1016.5</v>
+        <v>330.95</v>
       </c>
       <c r="D5" t="n">
-        <v>1012.17</v>
+        <v>326.66</v>
       </c>
       <c r="E5" t="n">
-        <v>962.7</v>
+        <v>318.56</v>
       </c>
       <c r="F5" t="n">
-        <v>856.63</v>
+        <v>276</v>
       </c>
       <c r="G5" t="n">
-        <v>18.66</v>
+        <v>19.91</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -606,43 +606,6 @@
         </is>
       </c>
       <c r="I5" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>28-09-2026</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>ETERNAL</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>329.15</v>
-      </c>
-      <c r="D6" t="n">
-        <v>326.6</v>
-      </c>
-      <c r="E6" t="n">
-        <v>318.53</v>
-      </c>
-      <c r="F6" t="n">
-        <v>275.99</v>
-      </c>
-      <c r="G6" t="n">
-        <v>19.26</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>28-09-2026</t>
+          <t>29-09-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,7 +503,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>28-09-2026</t>
+          <t>29-09-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -540,28 +540,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>28-09-2026</t>
+          <t>29-09-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2197</v>
+        <v>330.95</v>
       </c>
       <c r="D4" t="n">
-        <v>2175.31</v>
+        <v>326.66</v>
       </c>
       <c r="E4" t="n">
-        <v>2073.4</v>
+        <v>318.56</v>
       </c>
       <c r="F4" t="n">
-        <v>1975.16</v>
+        <v>276</v>
       </c>
       <c r="G4" t="n">
-        <v>11.23</v>
+        <v>19.91</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -569,43 +569,6 @@
         </is>
       </c>
       <c r="I4" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>28-09-2026</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>ETERNAL</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>330.95</v>
-      </c>
-      <c r="D5" t="n">
-        <v>326.66</v>
-      </c>
-      <c r="E5" t="n">
-        <v>318.56</v>
-      </c>
-      <c r="F5" t="n">
-        <v>276</v>
-      </c>
-      <c r="G5" t="n">
-        <v>19.91</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,23 +471,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>289.85</v>
+        <v>559.3</v>
       </c>
       <c r="D2" t="n">
-        <v>288.83</v>
+        <v>543.05</v>
       </c>
       <c r="E2" t="n">
-        <v>284.83</v>
+        <v>529.49</v>
       </c>
       <c r="F2" t="n">
-        <v>279.32</v>
+        <v>525.1900000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>3.77</v>
+        <v>6.5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>564.15</v>
+        <v>2210.9</v>
       </c>
       <c r="D3" t="n">
-        <v>540.71</v>
+        <v>2175.77</v>
       </c>
       <c r="E3" t="n">
-        <v>529.0599999999999</v>
+        <v>2073.68</v>
       </c>
       <c r="F3" t="n">
-        <v>525</v>
+        <v>1975.23</v>
       </c>
       <c r="G3" t="n">
-        <v>7.46</v>
+        <v>11.93</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -532,43 +532,6 @@
         </is>
       </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>29-09-2026</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ETERNAL</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>330.95</v>
-      </c>
-      <c r="D4" t="n">
-        <v>326.66</v>
-      </c>
-      <c r="E4" t="n">
-        <v>318.56</v>
-      </c>
-      <c r="F4" t="n">
-        <v>276</v>
-      </c>
-      <c r="G4" t="n">
-        <v>19.91</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>559.3</v>
+        <v>548.5</v>
       </c>
       <c r="D2" t="n">
-        <v>543.05</v>
+        <v>542.6900000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>529.49</v>
+        <v>529.28</v>
       </c>
       <c r="F2" t="n">
-        <v>525.1900000000001</v>
+        <v>525.13</v>
       </c>
       <c r="G2" t="n">
-        <v>6.5</v>
+        <v>4.45</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -512,19 +512,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2210.9</v>
+        <v>2188.6</v>
       </c>
       <c r="D3" t="n">
-        <v>2175.77</v>
+        <v>2178.03</v>
       </c>
       <c r="E3" t="n">
-        <v>2073.68</v>
+        <v>2080.92</v>
       </c>
       <c r="F3" t="n">
-        <v>1975.23</v>
+        <v>1977.45</v>
       </c>
       <c r="G3" t="n">
-        <v>11.93</v>
+        <v>10.68</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -532,6 +532,43 @@
         </is>
       </c>
       <c r="I3" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>29-09-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>327.85</v>
+      </c>
+      <c r="D4" t="n">
+        <v>327.06</v>
+      </c>
+      <c r="E4" t="n">
+        <v>319.39</v>
+      </c>
+      <c r="F4" t="n">
+        <v>276.15</v>
+      </c>
+      <c r="G4" t="n">
+        <v>18.72</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,28 +466,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>29-09-2026</t>
+          <t>30-09-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>548.5</v>
+        <v>327.85</v>
       </c>
       <c r="D2" t="n">
-        <v>542.6900000000001</v>
+        <v>327.06</v>
       </c>
       <c r="E2" t="n">
-        <v>529.28</v>
+        <v>319.39</v>
       </c>
       <c r="F2" t="n">
-        <v>525.13</v>
+        <v>276.15</v>
       </c>
       <c r="G2" t="n">
-        <v>4.45</v>
+        <v>18.72</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -495,80 +495,6 @@
         </is>
       </c>
       <c r="I2" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>29-09-2026</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>APLAPOLLO</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>2188.6</v>
-      </c>
-      <c r="D3" t="n">
-        <v>2178.03</v>
-      </c>
-      <c r="E3" t="n">
-        <v>2080.92</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1977.45</v>
-      </c>
-      <c r="G3" t="n">
-        <v>10.68</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>29-09-2026</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ETERNAL</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>327.85</v>
-      </c>
-      <c r="D4" t="n">
-        <v>327.06</v>
-      </c>
-      <c r="E4" t="n">
-        <v>319.39</v>
-      </c>
-      <c r="F4" t="n">
-        <v>276.15</v>
-      </c>
-      <c r="G4" t="n">
-        <v>18.72</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,23 +471,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>BANDHANBNK</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>327.85</v>
+        <v>181.07</v>
       </c>
       <c r="D2" t="n">
-        <v>327.06</v>
+        <v>174.16</v>
       </c>
       <c r="E2" t="n">
-        <v>319.39</v>
+        <v>172.89</v>
       </c>
       <c r="F2" t="n">
-        <v>276.15</v>
+        <v>175.34</v>
       </c>
       <c r="G2" t="n">
-        <v>18.72</v>
+        <v>3.27</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -495,6 +495,43 @@
         </is>
       </c>
       <c r="I2" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>30-09-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2199</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2178.38</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2081.13</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1977.5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>181.07</v>
+        <v>178.23</v>
       </c>
       <c r="D2" t="n">
-        <v>174.16</v>
+        <v>174.06</v>
       </c>
       <c r="E2" t="n">
-        <v>172.89</v>
+        <v>172.83</v>
       </c>
       <c r="F2" t="n">
-        <v>175.34</v>
+        <v>175.33</v>
       </c>
       <c r="G2" t="n">
-        <v>3.27</v>
+        <v>1.65</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,30 +508,67 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>674</v>
+      </c>
+      <c r="D3" t="n">
+        <v>666.08</v>
+      </c>
+      <c r="E3" t="n">
+        <v>662.09</v>
+      </c>
+      <c r="F3" t="n">
+        <v>621.25</v>
+      </c>
+      <c r="G3" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>30-09-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>APLAPOLLO</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>2199</v>
-      </c>
-      <c r="D3" t="n">
-        <v>2178.38</v>
-      </c>
-      <c r="E3" t="n">
-        <v>2081.13</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1977.5</v>
-      </c>
-      <c r="G3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="C4" t="n">
+        <v>2190.1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2180.58</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2088.41</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1979.74</v>
+      </c>
+      <c r="G4" t="n">
+        <v>10.63</v>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,7 +503,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -532,43 +532,6 @@
         </is>
       </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>30-09-2026</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>APLAPOLLO</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>2190.1</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2180.58</v>
-      </c>
-      <c r="E4" t="n">
-        <v>2088.41</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1979.74</v>
-      </c>
-      <c r="G4" t="n">
-        <v>10.63</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>178.23</v>
+        <v>177.64</v>
       </c>
       <c r="D2" t="n">
-        <v>174.06</v>
+        <v>174.18</v>
       </c>
       <c r="E2" t="n">
-        <v>172.83</v>
+        <v>173.1</v>
       </c>
       <c r="F2" t="n">
-        <v>175.33</v>
+        <v>175.48</v>
       </c>
       <c r="G2" t="n">
-        <v>1.65</v>
+        <v>1.23</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -495,43 +495,6 @@
         </is>
       </c>
       <c r="I2" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>01-10-2026</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>DLF</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>674</v>
-      </c>
-      <c r="D3" t="n">
-        <v>666.08</v>
-      </c>
-      <c r="E3" t="n">
-        <v>662.09</v>
-      </c>
-      <c r="F3" t="n">
-        <v>621.25</v>
-      </c>
-      <c r="G3" t="n">
-        <v>8.49</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -471,23 +471,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BANDHANBNK</t>
+          <t>MANKIND</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>177.64</v>
+        <v>2535</v>
       </c>
       <c r="D2" t="n">
-        <v>174.18</v>
+        <v>2379.21</v>
       </c>
       <c r="E2" t="n">
-        <v>173.1</v>
+        <v>2411.79</v>
       </c>
       <c r="F2" t="n">
-        <v>175.48</v>
+        <v>2298.06</v>
       </c>
       <c r="G2" t="n">
-        <v>1.23</v>
+        <v>10.31</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -466,28 +466,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>01-10-2026</t>
+          <t>02-10-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MANKIND</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2535</v>
+        <v>2190.1</v>
       </c>
       <c r="D2" t="n">
-        <v>2379.21</v>
+        <v>2180.58</v>
       </c>
       <c r="E2" t="n">
-        <v>2411.79</v>
+        <v>2088.41</v>
       </c>
       <c r="F2" t="n">
-        <v>2298.06</v>
+        <v>1979.74</v>
       </c>
       <c r="G2" t="n">
-        <v>10.31</v>
+        <v>10.63</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -471,23 +471,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>MANKIND</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2190.1</v>
+        <v>2535</v>
       </c>
       <c r="D2" t="n">
-        <v>2180.58</v>
+        <v>2379.21</v>
       </c>
       <c r="E2" t="n">
-        <v>2088.41</v>
+        <v>2411.79</v>
       </c>
       <c r="F2" t="n">
-        <v>1979.74</v>
+        <v>2298.06</v>
       </c>
       <c r="G2" t="n">
-        <v>10.63</v>
+        <v>10.31</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>02-10-2026</t>
+          <t>03-10-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>03-10-2026</t>
+          <t>05-10-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,30 +471,104 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>289.3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>288.28</v>
+      </c>
+      <c r="E2" t="n">
+        <v>285.67</v>
+      </c>
+      <c r="F2" t="n">
+        <v>279.74</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>671.45</v>
+      </c>
+      <c r="D3" t="n">
+        <v>665.27</v>
+      </c>
+      <c r="E3" t="n">
+        <v>663.26</v>
+      </c>
+      <c r="F3" t="n">
+        <v>621.11</v>
+      </c>
+      <c r="G3" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>MANKIND</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>2535</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2379.21</v>
-      </c>
-      <c r="E2" t="n">
-        <v>2411.79</v>
-      </c>
-      <c r="F2" t="n">
-        <v>2298.06</v>
-      </c>
-      <c r="G2" t="n">
-        <v>10.31</v>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="C4" t="n">
+        <v>2514.8</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2383.57</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2411.94</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2300.1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>06-10-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>289.3</v>
+        <v>292.65</v>
       </c>
       <c r="D2" t="n">
-        <v>288.28</v>
+        <v>288.39</v>
       </c>
       <c r="E2" t="n">
-        <v>285.67</v>
+        <v>285.73</v>
       </c>
       <c r="F2" t="n">
-        <v>279.74</v>
+        <v>279.75</v>
       </c>
       <c r="G2" t="n">
-        <v>3.42</v>
+        <v>4.61</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -503,28 +503,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>06-10-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>MANKIND</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>671.45</v>
+        <v>2479.9</v>
       </c>
       <c r="D3" t="n">
-        <v>665.27</v>
+        <v>2391.55</v>
       </c>
       <c r="E3" t="n">
-        <v>663.26</v>
+        <v>2408.14</v>
       </c>
       <c r="F3" t="n">
-        <v>621.11</v>
+        <v>2303.73</v>
       </c>
       <c r="G3" t="n">
-        <v>8.1</v>
+        <v>7.65</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -540,28 +540,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>06-10-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MANKIND</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2514.8</v>
+        <v>674.1</v>
       </c>
       <c r="D4" t="n">
-        <v>2383.57</v>
+        <v>664</v>
       </c>
       <c r="E4" t="n">
-        <v>2411.94</v>
+        <v>663.66</v>
       </c>
       <c r="F4" t="n">
-        <v>2300.1</v>
+        <v>621.01</v>
       </c>
       <c r="G4" t="n">
-        <v>9.33</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -569,6 +569,43 @@
         </is>
       </c>
       <c r="I4" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>06-10-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1038.25</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1017.82</v>
+      </c>
+      <c r="E5" t="n">
+        <v>974.08</v>
+      </c>
+      <c r="F5" t="n">
+        <v>861.38</v>
+      </c>
+      <c r="G5" t="n">
+        <v>20.53</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>292.65</v>
+        <v>296.5</v>
       </c>
       <c r="D2" t="n">
-        <v>288.39</v>
+        <v>288.52</v>
       </c>
       <c r="E2" t="n">
-        <v>285.73</v>
+        <v>285.81</v>
       </c>
       <c r="F2" t="n">
-        <v>279.75</v>
+        <v>279.77</v>
       </c>
       <c r="G2" t="n">
-        <v>4.61</v>
+        <v>5.98</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MANKIND</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2479.9</v>
+        <v>668.6</v>
       </c>
       <c r="D3" t="n">
-        <v>2391.55</v>
+        <v>663.8200000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>2408.14</v>
+        <v>663.55</v>
       </c>
       <c r="F3" t="n">
-        <v>2303.73</v>
+        <v>620.99</v>
       </c>
       <c r="G3" t="n">
-        <v>7.65</v>
+        <v>7.67</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>MANKIND</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>674.1</v>
+        <v>2503.3</v>
       </c>
       <c r="D4" t="n">
-        <v>664</v>
+        <v>2392.33</v>
       </c>
       <c r="E4" t="n">
-        <v>663.66</v>
+        <v>2408.6</v>
       </c>
       <c r="F4" t="n">
-        <v>621.01</v>
+        <v>2303.85</v>
       </c>
       <c r="G4" t="n">
-        <v>8.550000000000001</v>
+        <v>8.66</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,30 +582,67 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>328.1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>325.81</v>
+      </c>
+      <c r="E5" t="n">
+        <v>322.21</v>
+      </c>
+      <c r="F5" t="n">
+        <v>276.94</v>
+      </c>
+      <c r="G5" t="n">
+        <v>18.47</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>06-10-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>MOTILALOFS</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>1038.25</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1017.82</v>
-      </c>
-      <c r="E5" t="n">
-        <v>974.08</v>
-      </c>
-      <c r="F5" t="n">
-        <v>861.38</v>
-      </c>
-      <c r="G5" t="n">
-        <v>20.53</v>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="C6" t="n">
+        <v>1059.7</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1018.54</v>
+      </c>
+      <c r="E6" t="n">
+        <v>974.51</v>
+      </c>
+      <c r="F6" t="n">
+        <v>861.49</v>
+      </c>
+      <c r="G6" t="n">
+        <v>23.01</v>
+      </c>
+      <c r="H6" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>296.5</v>
+        <v>297.5</v>
       </c>
       <c r="D2" t="n">
-        <v>288.52</v>
+        <v>288.35</v>
       </c>
       <c r="E2" t="n">
-        <v>285.81</v>
+        <v>286.17</v>
       </c>
       <c r="F2" t="n">
-        <v>279.77</v>
+        <v>279.9</v>
       </c>
       <c r="G2" t="n">
-        <v>5.98</v>
+        <v>6.29</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -512,19 +512,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>668.6</v>
+        <v>666.1</v>
       </c>
       <c r="D3" t="n">
-        <v>663.8200000000001</v>
+        <v>663.74</v>
       </c>
       <c r="E3" t="n">
-        <v>663.55</v>
+        <v>663.5</v>
       </c>
       <c r="F3" t="n">
-        <v>620.99</v>
+        <v>620.97</v>
       </c>
       <c r="G3" t="n">
-        <v>7.67</v>
+        <v>7.27</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -549,19 +549,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2503.3</v>
+        <v>2500</v>
       </c>
       <c r="D4" t="n">
-        <v>2392.33</v>
+        <v>2392.22</v>
       </c>
       <c r="E4" t="n">
-        <v>2408.6</v>
+        <v>2408.54</v>
       </c>
       <c r="F4" t="n">
-        <v>2303.85</v>
+        <v>2303.83</v>
       </c>
       <c r="G4" t="n">
-        <v>8.66</v>
+        <v>8.51</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -586,19 +586,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>328.1</v>
+        <v>329</v>
       </c>
       <c r="D5" t="n">
-        <v>325.81</v>
+        <v>325.84</v>
       </c>
       <c r="E5" t="n">
-        <v>322.21</v>
+        <v>322.23</v>
       </c>
       <c r="F5" t="n">
         <v>276.94</v>
       </c>
       <c r="G5" t="n">
-        <v>18.47</v>
+        <v>18.8</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -623,19 +623,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1059.7</v>
+        <v>1081.15</v>
       </c>
       <c r="D6" t="n">
-        <v>1018.54</v>
+        <v>1019.25</v>
       </c>
       <c r="E6" t="n">
-        <v>974.51</v>
+        <v>974.9400000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>861.49</v>
+        <v>861.6</v>
       </c>
       <c r="G6" t="n">
-        <v>23.01</v>
+        <v>25.48</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,28 +466,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>06-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>297.5</v>
+        <v>666.1</v>
       </c>
       <c r="D2" t="n">
-        <v>288.35</v>
+        <v>663.74</v>
       </c>
       <c r="E2" t="n">
-        <v>286.17</v>
+        <v>663.5</v>
       </c>
       <c r="F2" t="n">
-        <v>279.9</v>
+        <v>620.97</v>
       </c>
       <c r="G2" t="n">
-        <v>6.29</v>
+        <v>7.27</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -503,28 +503,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>06-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>666.1</v>
+        <v>329</v>
       </c>
       <c r="D3" t="n">
-        <v>663.74</v>
+        <v>325.84</v>
       </c>
       <c r="E3" t="n">
-        <v>663.5</v>
+        <v>322.23</v>
       </c>
       <c r="F3" t="n">
-        <v>620.97</v>
+        <v>276.94</v>
       </c>
       <c r="G3" t="n">
-        <v>7.27</v>
+        <v>18.8</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -540,28 +540,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>06-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MANKIND</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2500</v>
+        <v>1081.15</v>
       </c>
       <c r="D4" t="n">
-        <v>2392.22</v>
+        <v>1019.25</v>
       </c>
       <c r="E4" t="n">
-        <v>2408.54</v>
+        <v>974.9400000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>2303.83</v>
+        <v>861.6</v>
       </c>
       <c r="G4" t="n">
-        <v>8.51</v>
+        <v>25.48</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -569,80 +569,6 @@
         </is>
       </c>
       <c r="I4" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>06-10-2026</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>ETERNAL</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>329</v>
-      </c>
-      <c r="D5" t="n">
-        <v>325.84</v>
-      </c>
-      <c r="E5" t="n">
-        <v>322.23</v>
-      </c>
-      <c r="F5" t="n">
-        <v>276.94</v>
-      </c>
-      <c r="G5" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>06-10-2026</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>MOTILALOFS</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>1081.15</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1019.25</v>
-      </c>
-      <c r="E6" t="n">
-        <v>974.9400000000001</v>
-      </c>
-      <c r="F6" t="n">
-        <v>861.6</v>
-      </c>
-      <c r="G6" t="n">
-        <v>25.48</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -471,23 +471,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>666.1</v>
+        <v>295.95</v>
       </c>
       <c r="D2" t="n">
-        <v>663.74</v>
+        <v>288.3</v>
       </c>
       <c r="E2" t="n">
-        <v>663.5</v>
+        <v>286.14</v>
       </c>
       <c r="F2" t="n">
-        <v>620.97</v>
+        <v>279.89</v>
       </c>
       <c r="G2" t="n">
-        <v>7.27</v>
+        <v>5.74</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>MANKIND</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>329</v>
+        <v>2509.3</v>
       </c>
       <c r="D3" t="n">
-        <v>325.84</v>
+        <v>2392.53</v>
       </c>
       <c r="E3" t="n">
-        <v>322.23</v>
+        <v>2408.72</v>
       </c>
       <c r="F3" t="n">
-        <v>276.94</v>
+        <v>2303.88</v>
       </c>
       <c r="G3" t="n">
-        <v>18.8</v>
+        <v>8.92</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1081.15</v>
+        <v>331.4</v>
       </c>
       <c r="D4" t="n">
-        <v>1019.25</v>
+        <v>325.99</v>
       </c>
       <c r="E4" t="n">
-        <v>974.9400000000001</v>
+        <v>322.62</v>
       </c>
       <c r="F4" t="n">
-        <v>861.6</v>
+        <v>277.17</v>
       </c>
       <c r="G4" t="n">
-        <v>25.48</v>
+        <v>19.57</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>295.95</v>
+        <v>297</v>
       </c>
       <c r="D2" t="n">
-        <v>288.3</v>
+        <v>288.5</v>
       </c>
       <c r="E2" t="n">
-        <v>286.14</v>
+        <v>286.56</v>
       </c>
       <c r="F2" t="n">
-        <v>279.89</v>
+        <v>280.03</v>
       </c>
       <c r="G2" t="n">
-        <v>5.74</v>
+        <v>6.06</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -512,19 +512,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2509.3</v>
+        <v>2500</v>
       </c>
       <c r="D3" t="n">
-        <v>2392.53</v>
+        <v>2395.77</v>
       </c>
       <c r="E3" t="n">
-        <v>2408.72</v>
+        <v>2406.68</v>
       </c>
       <c r="F3" t="n">
-        <v>2303.88</v>
+        <v>2305.47</v>
       </c>
       <c r="G3" t="n">
-        <v>8.92</v>
+        <v>8.44</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -549,19 +549,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>331.4</v>
+        <v>328</v>
       </c>
       <c r="D4" t="n">
-        <v>325.99</v>
+        <v>325.87</v>
       </c>
       <c r="E4" t="n">
-        <v>322.62</v>
+        <v>322.55</v>
       </c>
       <c r="F4" t="n">
-        <v>277.17</v>
+        <v>277.15</v>
       </c>
       <c r="G4" t="n">
-        <v>19.57</v>
+        <v>18.35</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,28 +466,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>08-10-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>MANKIND</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>297</v>
+        <v>2500</v>
       </c>
       <c r="D2" t="n">
-        <v>288.5</v>
+        <v>2395.77</v>
       </c>
       <c r="E2" t="n">
-        <v>286.56</v>
+        <v>2406.68</v>
       </c>
       <c r="F2" t="n">
-        <v>280.03</v>
+        <v>2305.47</v>
       </c>
       <c r="G2" t="n">
-        <v>6.06</v>
+        <v>8.44</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -495,80 +495,6 @@
         </is>
       </c>
       <c r="I2" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>07-10-2026</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>MANKIND</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>2500</v>
-      </c>
-      <c r="D3" t="n">
-        <v>2395.77</v>
-      </c>
-      <c r="E3" t="n">
-        <v>2406.68</v>
-      </c>
-      <c r="F3" t="n">
-        <v>2305.47</v>
-      </c>
-      <c r="G3" t="n">
-        <v>8.44</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>07-10-2026</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ETERNAL</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>328</v>
-      </c>
-      <c r="D4" t="n">
-        <v>325.87</v>
-      </c>
-      <c r="E4" t="n">
-        <v>322.55</v>
-      </c>
-      <c r="F4" t="n">
-        <v>277.15</v>
-      </c>
-      <c r="G4" t="n">
-        <v>18.35</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -471,23 +471,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MANKIND</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2500</v>
+        <v>290.3</v>
       </c>
       <c r="D2" t="n">
-        <v>2395.77</v>
+        <v>288.28</v>
       </c>
       <c r="E2" t="n">
-        <v>2406.68</v>
+        <v>286.42</v>
       </c>
       <c r="F2" t="n">
-        <v>2305.47</v>
+        <v>280</v>
       </c>
       <c r="G2" t="n">
-        <v>8.44</v>
+        <v>3.68</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>290.3</v>
+        <v>288.5</v>
       </c>
       <c r="D2" t="n">
-        <v>288.28</v>
+        <v>288.48</v>
       </c>
       <c r="E2" t="n">
-        <v>286.42</v>
+        <v>286.78</v>
       </c>
       <c r="F2" t="n">
-        <v>280</v>
+        <v>280.11</v>
       </c>
       <c r="G2" t="n">
-        <v>3.68</v>
+        <v>3</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>08-10-2026</t>
+          <t>09-10-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>288.5</v>
+        <v>291.8</v>
       </c>
       <c r="D2" t="n">
-        <v>288.48</v>
+        <v>288.64</v>
       </c>
       <c r="E2" t="n">
-        <v>286.78</v>
+        <v>286.88</v>
       </c>
       <c r="F2" t="n">
-        <v>280.11</v>
+        <v>280.02</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>4.21</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>291.8</v>
+        <v>291.5</v>
       </c>
       <c r="D2" t="n">
-        <v>288.64</v>
+        <v>288.63</v>
       </c>
       <c r="E2" t="n">
-        <v>286.88</v>
+        <v>286.87</v>
       </c>
       <c r="F2" t="n">
         <v>280.02</v>
       </c>
       <c r="G2" t="n">
-        <v>4.21</v>
+        <v>4.1</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09-10-2026</t>
+          <t>10-10-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>291.5</v>
+        <v>289.2</v>
       </c>
       <c r="D2" t="n">
-        <v>288.63</v>
+        <v>288.57</v>
       </c>
       <c r="E2" t="n">
-        <v>286.87</v>
+        <v>287.08</v>
       </c>
       <c r="F2" t="n">
-        <v>280.02</v>
+        <v>280.14</v>
       </c>
       <c r="G2" t="n">
-        <v>4.1</v>
+        <v>3.23</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -495,6 +495,43 @@
         </is>
       </c>
       <c r="I2" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>12-10-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>441.4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>419.33</v>
+      </c>
+      <c r="E3" t="n">
+        <v>410.51</v>
+      </c>
+      <c r="F3" t="n">
+        <v>399.51</v>
+      </c>
+      <c r="G3" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>13-10-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,10 +475,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>289.2</v>
+        <v>289.55</v>
       </c>
       <c r="D2" t="n">
-        <v>288.57</v>
+        <v>288.58</v>
       </c>
       <c r="E2" t="n">
         <v>287.08</v>
@@ -487,7 +487,7 @@
         <v>280.14</v>
       </c>
       <c r="G2" t="n">
-        <v>3.23</v>
+        <v>3.36</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -503,7 +503,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>13-10-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -512,19 +512,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>441.4</v>
+        <v>442.1</v>
       </c>
       <c r="D3" t="n">
-        <v>419.33</v>
+        <v>419.35</v>
       </c>
       <c r="E3" t="n">
-        <v>410.51</v>
+        <v>410.52</v>
       </c>
       <c r="F3" t="n">
         <v>399.51</v>
       </c>
       <c r="G3" t="n">
-        <v>10.49</v>
+        <v>10.66</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -532,6 +532,43 @@
         </is>
       </c>
       <c r="I3" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>13-10-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>327.6</v>
+      </c>
+      <c r="D4" t="n">
+        <v>326.01</v>
+      </c>
+      <c r="E4" t="n">
+        <v>322.99</v>
+      </c>
+      <c r="F4" t="n">
+        <v>277.88</v>
+      </c>
+      <c r="G4" t="n">
+        <v>17.89</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>289.55</v>
+        <v>288.75</v>
       </c>
       <c r="D2" t="n">
-        <v>288.58</v>
+        <v>288.55</v>
       </c>
       <c r="E2" t="n">
-        <v>287.08</v>
+        <v>287.07</v>
       </c>
       <c r="F2" t="n">
         <v>280.14</v>
       </c>
       <c r="G2" t="n">
-        <v>3.36</v>
+        <v>3.08</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -512,19 +512,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>442.1</v>
+        <v>438.95</v>
       </c>
       <c r="D3" t="n">
-        <v>419.35</v>
+        <v>419.25</v>
       </c>
       <c r="E3" t="n">
-        <v>410.52</v>
+        <v>410.46</v>
       </c>
       <c r="F3" t="n">
-        <v>399.51</v>
+        <v>399.5</v>
       </c>
       <c r="G3" t="n">
-        <v>10.66</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -532,43 +532,6 @@
         </is>
       </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>13-10-2026</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ETERNAL</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>327.6</v>
-      </c>
-      <c r="D4" t="n">
-        <v>326.01</v>
-      </c>
-      <c r="E4" t="n">
-        <v>322.99</v>
-      </c>
-      <c r="F4" t="n">
-        <v>277.88</v>
-      </c>
-      <c r="G4" t="n">
-        <v>17.89</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>288.75</v>
+        <v>290</v>
       </c>
       <c r="D2" t="n">
-        <v>288.55</v>
+        <v>288.6</v>
       </c>
       <c r="E2" t="n">
-        <v>287.07</v>
+        <v>287.09</v>
       </c>
       <c r="F2" t="n">
         <v>280.14</v>
       </c>
       <c r="G2" t="n">
-        <v>3.08</v>
+        <v>3.52</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,30 +508,67 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2185</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2174.83</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2120.76</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1989.09</v>
+      </c>
+      <c r="G3" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>13-10-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>KOTAKBANK</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>438.95</v>
-      </c>
-      <c r="D3" t="n">
+      <c r="C4" t="n">
+        <v>439</v>
+      </c>
+      <c r="D4" t="n">
         <v>419.25</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E4" t="n">
         <v>410.46</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F4" t="n">
         <v>399.5</v>
       </c>
-      <c r="G3" t="n">
-        <v>9.880000000000001</v>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="G4" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,28 +466,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>13-10-2026</t>
+          <t>14-10-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>290</v>
+        <v>2185</v>
       </c>
       <c r="D2" t="n">
-        <v>288.6</v>
+        <v>2171.51</v>
       </c>
       <c r="E2" t="n">
-        <v>287.09</v>
+        <v>2127.66</v>
       </c>
       <c r="F2" t="n">
-        <v>280.14</v>
+        <v>1990.81</v>
       </c>
       <c r="G2" t="n">
-        <v>3.52</v>
+        <v>9.75</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -503,28 +503,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>13-10-2026</t>
+          <t>14-10-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2185</v>
+        <v>439</v>
       </c>
       <c r="D3" t="n">
-        <v>2174.83</v>
+        <v>419.9</v>
       </c>
       <c r="E3" t="n">
-        <v>2120.76</v>
+        <v>411.52</v>
       </c>
       <c r="F3" t="n">
-        <v>1989.09</v>
+        <v>399.56</v>
       </c>
       <c r="G3" t="n">
-        <v>9.85</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -532,43 +532,6 @@
         </is>
       </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>13-10-2026</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>KOTAKBANK</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>439</v>
-      </c>
-      <c r="D4" t="n">
-        <v>419.25</v>
-      </c>
-      <c r="E4" t="n">
-        <v>410.46</v>
-      </c>
-      <c r="F4" t="n">
-        <v>399.5</v>
-      </c>
-      <c r="G4" t="n">
-        <v>9.890000000000001</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,23 +471,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2185</v>
+        <v>291.05</v>
       </c>
       <c r="D2" t="n">
-        <v>2171.51</v>
+        <v>288.58</v>
       </c>
       <c r="E2" t="n">
-        <v>2127.66</v>
+        <v>287.31</v>
       </c>
       <c r="F2" t="n">
-        <v>1990.81</v>
+        <v>280.25</v>
       </c>
       <c r="G2" t="n">
-        <v>9.75</v>
+        <v>3.86</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -512,19 +512,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>439</v>
+        <v>443.2</v>
       </c>
       <c r="D3" t="n">
-        <v>419.9</v>
+        <v>420.7</v>
       </c>
       <c r="E3" t="n">
-        <v>411.52</v>
+        <v>412.44</v>
       </c>
       <c r="F3" t="n">
-        <v>399.56</v>
+        <v>399.63</v>
       </c>
       <c r="G3" t="n">
-        <v>9.869999999999999</v>
+        <v>10.9</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -532,6 +532,80 @@
         </is>
       </c>
       <c r="I3" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>14-10-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>5926</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5515.95</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5538.92</v>
+      </c>
+      <c r="F4" t="n">
+        <v>5335.77</v>
+      </c>
+      <c r="G4" t="n">
+        <v>11.06</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>14-10-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SOLARINDS</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>20231</v>
+      </c>
+      <c r="D5" t="n">
+        <v>20191.27</v>
+      </c>
+      <c r="E5" t="n">
+        <v>19943.36</v>
+      </c>
+      <c r="F5" t="n">
+        <v>16522.99</v>
+      </c>
+      <c r="G5" t="n">
+        <v>22.44</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>291.05</v>
+        <v>292.95</v>
       </c>
       <c r="D2" t="n">
-        <v>288.58</v>
+        <v>288.29</v>
       </c>
       <c r="E2" t="n">
-        <v>287.31</v>
+        <v>287.45</v>
       </c>
       <c r="F2" t="n">
-        <v>280.25</v>
+        <v>280.34</v>
       </c>
       <c r="G2" t="n">
-        <v>3.86</v>
+        <v>4.5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -512,19 +512,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>443.2</v>
+        <v>438.05</v>
       </c>
       <c r="D3" t="n">
-        <v>420.7</v>
+        <v>420.53</v>
       </c>
       <c r="E3" t="n">
-        <v>412.44</v>
+        <v>412.34</v>
       </c>
       <c r="F3" t="n">
-        <v>399.63</v>
+        <v>399.6</v>
       </c>
       <c r="G3" t="n">
-        <v>10.9</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -549,19 +549,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5926</v>
+        <v>5898</v>
       </c>
       <c r="D4" t="n">
-        <v>5515.95</v>
+        <v>5515.02</v>
       </c>
       <c r="E4" t="n">
-        <v>5538.92</v>
+        <v>5538.36</v>
       </c>
       <c r="F4" t="n">
-        <v>5335.77</v>
+        <v>5335.63</v>
       </c>
       <c r="G4" t="n">
-        <v>11.06</v>
+        <v>10.54</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -569,43 +569,6 @@
         </is>
       </c>
       <c r="I4" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>14-10-2026</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>SOLARINDS</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>20231</v>
-      </c>
-      <c r="D5" t="n">
-        <v>20191.27</v>
-      </c>
-      <c r="E5" t="n">
-        <v>19943.36</v>
-      </c>
-      <c r="F5" t="n">
-        <v>16522.99</v>
-      </c>
-      <c r="G5" t="n">
-        <v>22.44</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>14-10-2026</t>
+          <t>15-10-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,7 +503,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>14-10-2026</t>
+          <t>15-10-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -540,7 +540,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>14-10-2026</t>
+          <t>15-10-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,23 +471,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>292.95</v>
+        <v>116.75</v>
       </c>
       <c r="D2" t="n">
-        <v>288.29</v>
+        <v>115.64</v>
       </c>
       <c r="E2" t="n">
-        <v>287.45</v>
+        <v>115.77</v>
       </c>
       <c r="F2" t="n">
-        <v>280.34</v>
+        <v>112.42</v>
       </c>
       <c r="G2" t="n">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>438.05</v>
+        <v>2448.3</v>
       </c>
       <c r="D3" t="n">
-        <v>420.53</v>
+        <v>2321.87</v>
       </c>
       <c r="E3" t="n">
-        <v>412.34</v>
+        <v>2379.23</v>
       </c>
       <c r="F3" t="n">
-        <v>399.6</v>
+        <v>2345.78</v>
       </c>
       <c r="G3" t="n">
-        <v>9.619999999999999</v>
+        <v>4.37</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,30 +545,104 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>293.65</v>
+      </c>
+      <c r="D4" t="n">
+        <v>288.34</v>
+      </c>
+      <c r="E4" t="n">
+        <v>287.62</v>
+      </c>
+      <c r="F4" t="n">
+        <v>280.43</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>15-10-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>PERSISTENT</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>5898</v>
-      </c>
-      <c r="D4" t="n">
-        <v>5515.02</v>
-      </c>
-      <c r="E4" t="n">
-        <v>5538.36</v>
-      </c>
-      <c r="F4" t="n">
-        <v>5335.63</v>
-      </c>
-      <c r="G4" t="n">
-        <v>10.54</v>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="C5" t="n">
+        <v>5844</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5516.48</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5545.26</v>
+      </c>
+      <c r="F5" t="n">
+        <v>5332.64</v>
+      </c>
+      <c r="G5" t="n">
+        <v>9.59</v>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>15-10-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>444.65</v>
+      </c>
+      <c r="D6" t="n">
+        <v>421.18</v>
+      </c>
+      <c r="E6" t="n">
+        <v>413.27</v>
+      </c>
+      <c r="F6" t="n">
+        <v>399.67</v>
+      </c>
+      <c r="G6" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,23 +471,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>116.75</v>
+        <v>2453.2</v>
       </c>
       <c r="D2" t="n">
-        <v>115.64</v>
+        <v>2322.04</v>
       </c>
       <c r="E2" t="n">
-        <v>115.77</v>
+        <v>2379.33</v>
       </c>
       <c r="F2" t="n">
-        <v>112.42</v>
+        <v>2345.8</v>
       </c>
       <c r="G2" t="n">
-        <v>3.85</v>
+        <v>4.58</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2448.3</v>
+        <v>295.2</v>
       </c>
       <c r="D3" t="n">
-        <v>2321.87</v>
+        <v>288.39</v>
       </c>
       <c r="E3" t="n">
-        <v>2379.23</v>
+        <v>287.65</v>
       </c>
       <c r="F3" t="n">
-        <v>2345.78</v>
+        <v>280.43</v>
       </c>
       <c r="G3" t="n">
-        <v>4.37</v>
+        <v>5.27</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>293.65</v>
+        <v>5840</v>
       </c>
       <c r="D4" t="n">
-        <v>288.34</v>
+        <v>5516.35</v>
       </c>
       <c r="E4" t="n">
-        <v>287.62</v>
+        <v>5545.18</v>
       </c>
       <c r="F4" t="n">
-        <v>280.43</v>
+        <v>5332.62</v>
       </c>
       <c r="G4" t="n">
-        <v>4.72</v>
+        <v>9.51</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5844</v>
+        <v>447.95</v>
       </c>
       <c r="D5" t="n">
-        <v>5516.48</v>
+        <v>421.29</v>
       </c>
       <c r="E5" t="n">
-        <v>5545.26</v>
+        <v>413.33</v>
       </c>
       <c r="F5" t="n">
-        <v>5332.64</v>
+        <v>399.69</v>
       </c>
       <c r="G5" t="n">
-        <v>9.59</v>
+        <v>12.08</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -606,43 +606,6 @@
         </is>
       </c>
       <c r="I5" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>15-10-2026</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>KOTAKBANK</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>444.65</v>
-      </c>
-      <c r="D6" t="n">
-        <v>421.18</v>
-      </c>
-      <c r="E6" t="n">
-        <v>413.27</v>
-      </c>
-      <c r="F6" t="n">
-        <v>399.67</v>
-      </c>
-      <c r="G6" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,28 +466,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>15-10-2026</t>
+          <t>16-10-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2453.2</v>
+        <v>295.2</v>
       </c>
       <c r="D2" t="n">
-        <v>2322.04</v>
+        <v>288.39</v>
       </c>
       <c r="E2" t="n">
-        <v>2379.33</v>
+        <v>287.65</v>
       </c>
       <c r="F2" t="n">
-        <v>2345.8</v>
+        <v>280.43</v>
       </c>
       <c r="G2" t="n">
-        <v>4.58</v>
+        <v>5.27</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -503,28 +503,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>15-10-2026</t>
+          <t>16-10-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>295.2</v>
+        <v>5840</v>
       </c>
       <c r="D3" t="n">
-        <v>288.39</v>
+        <v>5516.35</v>
       </c>
       <c r="E3" t="n">
-        <v>287.65</v>
+        <v>5545.18</v>
       </c>
       <c r="F3" t="n">
-        <v>280.43</v>
+        <v>5332.62</v>
       </c>
       <c r="G3" t="n">
-        <v>5.27</v>
+        <v>9.51</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -540,28 +540,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>15-10-2026</t>
+          <t>16-10-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5840</v>
+        <v>447.95</v>
       </c>
       <c r="D4" t="n">
-        <v>5516.35</v>
+        <v>421.29</v>
       </c>
       <c r="E4" t="n">
-        <v>5545.18</v>
+        <v>413.33</v>
       </c>
       <c r="F4" t="n">
-        <v>5332.62</v>
+        <v>399.69</v>
       </c>
       <c r="G4" t="n">
-        <v>9.51</v>
+        <v>12.08</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -569,43 +569,6 @@
         </is>
       </c>
       <c r="I4" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>15-10-2026</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>KOTAKBANK</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>447.95</v>
-      </c>
-      <c r="D5" t="n">
-        <v>421.29</v>
-      </c>
-      <c r="E5" t="n">
-        <v>413.33</v>
-      </c>
-      <c r="F5" t="n">
-        <v>399.69</v>
-      </c>
-      <c r="G5" t="n">
-        <v>12.08</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>295.2</v>
+        <v>293.15</v>
       </c>
       <c r="D2" t="n">
-        <v>288.39</v>
+        <v>288.52</v>
       </c>
       <c r="E2" t="n">
-        <v>287.65</v>
+        <v>287.9</v>
       </c>
       <c r="F2" t="n">
-        <v>280.43</v>
+        <v>280.51</v>
       </c>
       <c r="G2" t="n">
-        <v>5.27</v>
+        <v>4.51</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5840</v>
+        <v>2486.2</v>
       </c>
       <c r="D3" t="n">
-        <v>5516.35</v>
+        <v>2323.14</v>
       </c>
       <c r="E3" t="n">
-        <v>5545.18</v>
+        <v>2379.99</v>
       </c>
       <c r="F3" t="n">
-        <v>5332.62</v>
+        <v>2345.97</v>
       </c>
       <c r="G3" t="n">
-        <v>9.51</v>
+        <v>5.98</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>447.95</v>
+        <v>5674.5</v>
       </c>
       <c r="D4" t="n">
-        <v>421.29</v>
+        <v>5515.83</v>
       </c>
       <c r="E4" t="n">
-        <v>413.33</v>
+        <v>5548.27</v>
       </c>
       <c r="F4" t="n">
-        <v>399.69</v>
+        <v>5329.45</v>
       </c>
       <c r="G4" t="n">
-        <v>12.08</v>
+        <v>6.47</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -569,6 +569,43 @@
         </is>
       </c>
       <c r="I4" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>16-10-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>325.05</v>
+      </c>
+      <c r="D5" t="n">
+        <v>324.97</v>
+      </c>
+      <c r="E5" t="n">
+        <v>323.88</v>
+      </c>
+      <c r="F5" t="n">
+        <v>278.57</v>
+      </c>
+      <c r="G5" t="n">
+        <v>16.68</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,23 +471,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>293.15</v>
+        <v>116.3</v>
       </c>
       <c r="D2" t="n">
-        <v>288.52</v>
+        <v>115.56</v>
       </c>
       <c r="E2" t="n">
-        <v>287.9</v>
+        <v>115.79</v>
       </c>
       <c r="F2" t="n">
-        <v>280.51</v>
+        <v>112.4</v>
       </c>
       <c r="G2" t="n">
-        <v>4.51</v>
+        <v>3.47</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2486.2</v>
+        <v>293</v>
       </c>
       <c r="D3" t="n">
-        <v>2323.14</v>
+        <v>288.51</v>
       </c>
       <c r="E3" t="n">
-        <v>2379.99</v>
+        <v>287.9</v>
       </c>
       <c r="F3" t="n">
-        <v>2345.97</v>
+        <v>280.51</v>
       </c>
       <c r="G3" t="n">
-        <v>5.98</v>
+        <v>4.45</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5674.5</v>
+        <v>2500</v>
       </c>
       <c r="D4" t="n">
-        <v>5515.83</v>
+        <v>2322.7</v>
       </c>
       <c r="E4" t="n">
-        <v>5548.27</v>
+        <v>2380.13</v>
       </c>
       <c r="F4" t="n">
-        <v>5329.45</v>
+        <v>2344.22</v>
       </c>
       <c r="G4" t="n">
-        <v>6.47</v>
+        <v>6.65</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,30 +582,67 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>5741</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5518.05</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5549.6</v>
+      </c>
+      <c r="F5" t="n">
+        <v>5329.78</v>
+      </c>
+      <c r="G5" t="n">
+        <v>7.72</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>16-10-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>ETERNAL</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>325.05</v>
-      </c>
-      <c r="D5" t="n">
-        <v>324.97</v>
-      </c>
-      <c r="E5" t="n">
+      <c r="C6" t="n">
+        <v>325.3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>324.98</v>
+      </c>
+      <c r="E6" t="n">
         <v>323.88</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F6" t="n">
         <v>278.57</v>
       </c>
-      <c r="G5" t="n">
-        <v>16.68</v>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="G6" t="n">
+        <v>16.77</v>
+      </c>
+      <c r="H6" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>16-10-2026</t>
+          <t>17-10-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,28 +503,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>16-10-2026</t>
+          <t>17-10-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>293</v>
+        <v>2500</v>
       </c>
       <c r="D3" t="n">
-        <v>288.51</v>
+        <v>2322.7</v>
       </c>
       <c r="E3" t="n">
-        <v>287.9</v>
+        <v>2380.13</v>
       </c>
       <c r="F3" t="n">
-        <v>280.51</v>
+        <v>2344.22</v>
       </c>
       <c r="G3" t="n">
-        <v>4.45</v>
+        <v>6.65</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -540,28 +540,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>16-10-2026</t>
+          <t>17-10-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2500</v>
+        <v>5741</v>
       </c>
       <c r="D4" t="n">
-        <v>2322.7</v>
+        <v>5518.05</v>
       </c>
       <c r="E4" t="n">
-        <v>2380.13</v>
+        <v>5549.6</v>
       </c>
       <c r="F4" t="n">
-        <v>2344.22</v>
+        <v>5329.78</v>
       </c>
       <c r="G4" t="n">
-        <v>6.65</v>
+        <v>7.72</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -577,28 +577,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>16-10-2026</t>
+          <t>17-10-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5741</v>
+        <v>325.3</v>
       </c>
       <c r="D5" t="n">
-        <v>5518.05</v>
+        <v>324.98</v>
       </c>
       <c r="E5" t="n">
-        <v>5549.6</v>
+        <v>323.88</v>
       </c>
       <c r="F5" t="n">
-        <v>5329.78</v>
+        <v>278.57</v>
       </c>
       <c r="G5" t="n">
-        <v>7.72</v>
+        <v>16.77</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -606,43 +606,6 @@
         </is>
       </c>
       <c r="I5" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>16-10-2026</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>ETERNAL</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>325.3</v>
-      </c>
-      <c r="D6" t="n">
-        <v>324.98</v>
-      </c>
-      <c r="E6" t="n">
-        <v>323.88</v>
-      </c>
-      <c r="F6" t="n">
-        <v>278.57</v>
-      </c>
-      <c r="G6" t="n">
-        <v>16.77</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2500</v>
+        <v>293</v>
       </c>
       <c r="D3" t="n">
-        <v>2322.7</v>
+        <v>288.51</v>
       </c>
       <c r="E3" t="n">
-        <v>2380.13</v>
+        <v>287.9</v>
       </c>
       <c r="F3" t="n">
-        <v>2344.22</v>
+        <v>280.51</v>
       </c>
       <c r="G3" t="n">
-        <v>6.65</v>
+        <v>4.45</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5741</v>
+        <v>2500</v>
       </c>
       <c r="D4" t="n">
-        <v>5518.05</v>
+        <v>2322.7</v>
       </c>
       <c r="E4" t="n">
-        <v>5549.6</v>
+        <v>2380.13</v>
       </c>
       <c r="F4" t="n">
-        <v>5329.78</v>
+        <v>2344.22</v>
       </c>
       <c r="G4" t="n">
-        <v>7.72</v>
+        <v>6.65</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,30 +582,67 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>5741</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5518.05</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5549.6</v>
+      </c>
+      <c r="F5" t="n">
+        <v>5329.78</v>
+      </c>
+      <c r="G5" t="n">
+        <v>7.72</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>17-10-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>ETERNAL</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C6" t="n">
         <v>325.3</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D6" t="n">
         <v>324.98</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E6" t="n">
         <v>323.88</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F6" t="n">
         <v>278.57</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G6" t="n">
         <v>16.77</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>17-10-2026</t>
+          <t>19-10-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,7 +503,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>17-10-2026</t>
+          <t>19-10-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -540,7 +540,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>17-10-2026</t>
+          <t>19-10-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -577,7 +577,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>17-10-2026</t>
+          <t>19-10-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -614,7 +614,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>17-10-2026</t>
+          <t>19-10-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -471,23 +471,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>116.3</v>
+        <v>294.15</v>
       </c>
       <c r="D2" t="n">
-        <v>115.56</v>
+        <v>288.67</v>
       </c>
       <c r="E2" t="n">
-        <v>115.79</v>
+        <v>288.24</v>
       </c>
       <c r="F2" t="n">
-        <v>112.4</v>
+        <v>280.59</v>
       </c>
       <c r="G2" t="n">
-        <v>3.47</v>
+        <v>4.83</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>293</v>
+        <v>2483.2</v>
       </c>
       <c r="D3" t="n">
-        <v>288.51</v>
+        <v>2323.11</v>
       </c>
       <c r="E3" t="n">
-        <v>287.9</v>
+        <v>2381.36</v>
       </c>
       <c r="F3" t="n">
-        <v>280.51</v>
+        <v>2342.76</v>
       </c>
       <c r="G3" t="n">
-        <v>4.45</v>
+        <v>5.99</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2500</v>
+        <v>5768</v>
       </c>
       <c r="D4" t="n">
-        <v>2322.7</v>
+        <v>5521.75</v>
       </c>
       <c r="E4" t="n">
-        <v>2380.13</v>
+        <v>5555.77</v>
       </c>
       <c r="F4" t="n">
-        <v>2344.22</v>
+        <v>5327.34</v>
       </c>
       <c r="G4" t="n">
-        <v>6.65</v>
+        <v>8.27</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5741</v>
+        <v>122.14</v>
       </c>
       <c r="D5" t="n">
-        <v>5518.05</v>
+        <v>115.76</v>
       </c>
       <c r="E5" t="n">
-        <v>5549.6</v>
+        <v>115.95</v>
       </c>
       <c r="F5" t="n">
-        <v>5329.78</v>
+        <v>112.43</v>
       </c>
       <c r="G5" t="n">
-        <v>7.72</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -623,19 +623,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>325.3</v>
+        <v>325.45</v>
       </c>
       <c r="D6" t="n">
-        <v>324.98</v>
+        <v>325</v>
       </c>
       <c r="E6" t="n">
-        <v>323.88</v>
+        <v>324.07</v>
       </c>
       <c r="F6" t="n">
-        <v>278.57</v>
+        <v>278.79</v>
       </c>
       <c r="G6" t="n">
-        <v>16.77</v>
+        <v>16.74</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>294.15</v>
+        <v>293.65</v>
       </c>
       <c r="D2" t="n">
-        <v>288.67</v>
+        <v>288.65</v>
       </c>
       <c r="E2" t="n">
-        <v>288.24</v>
+        <v>288.23</v>
       </c>
       <c r="F2" t="n">
         <v>280.59</v>
       </c>
       <c r="G2" t="n">
-        <v>4.83</v>
+        <v>4.66</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -512,19 +512,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2483.2</v>
+        <v>2500</v>
       </c>
       <c r="D3" t="n">
-        <v>2323.11</v>
+        <v>2323.67</v>
       </c>
       <c r="E3" t="n">
-        <v>2381.36</v>
+        <v>2381.69</v>
       </c>
       <c r="F3" t="n">
-        <v>2342.76</v>
+        <v>2342.84</v>
       </c>
       <c r="G3" t="n">
-        <v>5.99</v>
+        <v>6.71</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -549,19 +549,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5768</v>
+        <v>5690</v>
       </c>
       <c r="D4" t="n">
-        <v>5521.75</v>
+        <v>5519.15</v>
       </c>
       <c r="E4" t="n">
-        <v>5555.77</v>
+        <v>5554.21</v>
       </c>
       <c r="F4" t="n">
-        <v>5327.34</v>
+        <v>5326.95</v>
       </c>
       <c r="G4" t="n">
-        <v>8.27</v>
+        <v>6.82</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>122.14</v>
+        <v>121.9</v>
       </c>
       <c r="D5" t="n">
-        <v>115.76</v>
+        <v>115.75</v>
       </c>
       <c r="E5" t="n">
         <v>115.95</v>
@@ -598,7 +598,7 @@
         <v>112.43</v>
       </c>
       <c r="G5" t="n">
-        <v>8.640000000000001</v>
+        <v>8.43</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -606,43 +606,6 @@
         </is>
       </c>
       <c r="I5" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>19-10-2026</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>ETERNAL</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>325.45</v>
-      </c>
-      <c r="D6" t="n">
-        <v>325</v>
-      </c>
-      <c r="E6" t="n">
-        <v>324.07</v>
-      </c>
-      <c r="F6" t="n">
-        <v>278.79</v>
-      </c>
-      <c r="G6" t="n">
-        <v>16.74</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,28 +466,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>19-10-2026</t>
+          <t>20-10-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>293.65</v>
+        <v>5690</v>
       </c>
       <c r="D2" t="n">
-        <v>288.65</v>
+        <v>5519.15</v>
       </c>
       <c r="E2" t="n">
-        <v>288.23</v>
+        <v>5554.21</v>
       </c>
       <c r="F2" t="n">
-        <v>280.59</v>
+        <v>5326.95</v>
       </c>
       <c r="G2" t="n">
-        <v>4.66</v>
+        <v>6.82</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -503,28 +503,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>19-10-2026</t>
+          <t>20-10-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2500</v>
+        <v>121.9</v>
       </c>
       <c r="D3" t="n">
-        <v>2323.67</v>
+        <v>115.75</v>
       </c>
       <c r="E3" t="n">
-        <v>2381.69</v>
+        <v>115.95</v>
       </c>
       <c r="F3" t="n">
-        <v>2342.84</v>
+        <v>112.43</v>
       </c>
       <c r="G3" t="n">
-        <v>6.71</v>
+        <v>8.43</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -532,80 +532,6 @@
         </is>
       </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>19-10-2026</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>PERSISTENT</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>5690</v>
-      </c>
-      <c r="D4" t="n">
-        <v>5519.15</v>
-      </c>
-      <c r="E4" t="n">
-        <v>5554.21</v>
-      </c>
-      <c r="F4" t="n">
-        <v>5326.95</v>
-      </c>
-      <c r="G4" t="n">
-        <v>6.82</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>19-10-2026</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>PNB</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>121.9</v>
-      </c>
-      <c r="D5" t="n">
-        <v>115.75</v>
-      </c>
-      <c r="E5" t="n">
-        <v>115.95</v>
-      </c>
-      <c r="F5" t="n">
-        <v>112.43</v>
-      </c>
-      <c r="G5" t="n">
-        <v>8.43</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,23 +471,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5690</v>
+        <v>293.65</v>
       </c>
       <c r="D2" t="n">
-        <v>5519.15</v>
+        <v>288.65</v>
       </c>
       <c r="E2" t="n">
-        <v>5554.21</v>
+        <v>288.23</v>
       </c>
       <c r="F2" t="n">
-        <v>5326.95</v>
+        <v>280.59</v>
       </c>
       <c r="G2" t="n">
-        <v>6.82</v>
+        <v>4.66</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,30 +508,104 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>MPHASIS</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2500</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2323.67</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2381.69</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2342.84</v>
+      </c>
+      <c r="G3" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>20-10-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>5690</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5519.15</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5554.21</v>
+      </c>
+      <c r="F4" t="n">
+        <v>5326.95</v>
+      </c>
+      <c r="G4" t="n">
+        <v>6.82</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>20-10-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>PNB</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C5" t="n">
         <v>121.9</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D5" t="n">
         <v>115.75</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E5" t="n">
         <v>115.95</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F5" t="n">
         <v>112.43</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G5" t="n">
         <v>8.43</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20-10-2026</t>
+          <t>21-10-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,7 +503,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20-10-2026</t>
+          <t>21-10-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -540,7 +540,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20-10-2026</t>
+          <t>21-10-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -577,7 +577,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20-10-2026</t>
+          <t>21-10-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>293.65</v>
+        <v>297.75</v>
       </c>
       <c r="D2" t="n">
-        <v>288.65</v>
+        <v>288.97</v>
       </c>
       <c r="E2" t="n">
-        <v>288.23</v>
+        <v>288.57</v>
       </c>
       <c r="F2" t="n">
-        <v>280.59</v>
+        <v>280.7</v>
       </c>
       <c r="G2" t="n">
-        <v>4.66</v>
+        <v>6.07</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2500</v>
+        <v>5768.5</v>
       </c>
       <c r="D3" t="n">
-        <v>2323.67</v>
+        <v>5523.33</v>
       </c>
       <c r="E3" t="n">
-        <v>2381.69</v>
+        <v>5560.08</v>
       </c>
       <c r="F3" t="n">
-        <v>2342.84</v>
+        <v>5324.87</v>
       </c>
       <c r="G3" t="n">
-        <v>6.71</v>
+        <v>8.33</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5690</v>
+        <v>122.22</v>
       </c>
       <c r="D4" t="n">
-        <v>5519.15</v>
+        <v>115.92</v>
       </c>
       <c r="E4" t="n">
-        <v>5554.21</v>
+        <v>116.09</v>
       </c>
       <c r="F4" t="n">
-        <v>5326.95</v>
+        <v>112.45</v>
       </c>
       <c r="G4" t="n">
-        <v>6.82</v>
+        <v>8.69</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>121.9</v>
+        <v>2565.5</v>
       </c>
       <c r="D5" t="n">
-        <v>115.75</v>
+        <v>2328.45</v>
       </c>
       <c r="E5" t="n">
-        <v>115.95</v>
+        <v>2383.5</v>
       </c>
       <c r="F5" t="n">
-        <v>112.43</v>
+        <v>2341.97</v>
       </c>
       <c r="G5" t="n">
-        <v>8.43</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>297.75</v>
+        <v>295</v>
       </c>
       <c r="D2" t="n">
-        <v>288.97</v>
+        <v>288.88</v>
       </c>
       <c r="E2" t="n">
-        <v>288.57</v>
+        <v>288.52</v>
       </c>
       <c r="F2" t="n">
-        <v>280.7</v>
+        <v>280.68</v>
       </c>
       <c r="G2" t="n">
-        <v>6.07</v>
+        <v>5.1</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5768.5</v>
+        <v>122.5</v>
       </c>
       <c r="D3" t="n">
-        <v>5523.33</v>
+        <v>115.93</v>
       </c>
       <c r="E3" t="n">
-        <v>5560.08</v>
+        <v>116.1</v>
       </c>
       <c r="F3" t="n">
-        <v>5324.87</v>
+        <v>112.45</v>
       </c>
       <c r="G3" t="n">
-        <v>8.33</v>
+        <v>8.93</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>122.22</v>
+        <v>2575</v>
       </c>
       <c r="D4" t="n">
-        <v>115.92</v>
+        <v>2328.77</v>
       </c>
       <c r="E4" t="n">
-        <v>116.09</v>
+        <v>2383.69</v>
       </c>
       <c r="F4" t="n">
-        <v>112.45</v>
+        <v>2342.02</v>
       </c>
       <c r="G4" t="n">
-        <v>8.69</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2565.5</v>
+        <v>5858.5</v>
       </c>
       <c r="D5" t="n">
-        <v>2328.45</v>
+        <v>5526.33</v>
       </c>
       <c r="E5" t="n">
-        <v>2383.5</v>
+        <v>5561.88</v>
       </c>
       <c r="F5" t="n">
-        <v>2341.97</v>
+        <v>5325.32</v>
       </c>
       <c r="G5" t="n">
-        <v>9.539999999999999</v>
+        <v>10.01</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>21-10-2026</t>
+          <t>22-10-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,7 +503,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>21-10-2026</t>
+          <t>22-10-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -540,7 +540,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>21-10-2026</t>
+          <t>22-10-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -577,7 +577,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>21-10-2026</t>
+          <t>22-10-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>295</v>
+        <v>291.55</v>
       </c>
       <c r="D2" t="n">
-        <v>288.88</v>
+        <v>288.9</v>
       </c>
       <c r="E2" t="n">
-        <v>288.52</v>
+        <v>288.75</v>
       </c>
       <c r="F2" t="n">
-        <v>280.68</v>
+        <v>280.76</v>
       </c>
       <c r="G2" t="n">
-        <v>5.1</v>
+        <v>3.84</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>122.5</v>
+        <v>666.8</v>
       </c>
       <c r="D3" t="n">
-        <v>115.93</v>
+        <v>659.24</v>
       </c>
       <c r="E3" t="n">
-        <v>116.1</v>
+        <v>665.11</v>
       </c>
       <c r="F3" t="n">
-        <v>112.45</v>
+        <v>621.45</v>
       </c>
       <c r="G3" t="n">
-        <v>8.93</v>
+        <v>7.3</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2575</v>
+        <v>11317</v>
       </c>
       <c r="D4" t="n">
-        <v>2328.77</v>
+        <v>10951.39</v>
       </c>
       <c r="E4" t="n">
-        <v>2383.69</v>
+        <v>11081.32</v>
       </c>
       <c r="F4" t="n">
-        <v>2342.02</v>
+        <v>10536.81</v>
       </c>
       <c r="G4" t="n">
-        <v>9.949999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,30 +582,104 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>121.16</v>
+      </c>
+      <c r="D5" t="n">
+        <v>116.12</v>
+      </c>
+      <c r="E5" t="n">
+        <v>116.25</v>
+      </c>
+      <c r="F5" t="n">
+        <v>112.46</v>
+      </c>
+      <c r="G5" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>22-10-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>MPHASIS</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2553</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2334.9</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2384.59</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2341.17</v>
+      </c>
+      <c r="G6" t="n">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>22-10-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>PERSISTENT</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>5858.5</v>
-      </c>
-      <c r="D5" t="n">
-        <v>5526.33</v>
-      </c>
-      <c r="E5" t="n">
-        <v>5561.88</v>
-      </c>
-      <c r="F5" t="n">
-        <v>5325.32</v>
-      </c>
-      <c r="G5" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="C7" t="n">
+        <v>5847</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5536.57</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5569.34</v>
+      </c>
+      <c r="F7" t="n">
+        <v>5323.86</v>
+      </c>
+      <c r="G7" t="n">
+        <v>9.83</v>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>291.55</v>
+        <v>290.4</v>
       </c>
       <c r="D2" t="n">
-        <v>288.9</v>
+        <v>288.86</v>
       </c>
       <c r="E2" t="n">
-        <v>288.75</v>
+        <v>288.73</v>
       </c>
       <c r="F2" t="n">
-        <v>280.76</v>
+        <v>280.75</v>
       </c>
       <c r="G2" t="n">
-        <v>3.84</v>
+        <v>3.44</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>666.8</v>
+        <v>2499.5</v>
       </c>
       <c r="D3" t="n">
-        <v>659.24</v>
+        <v>2333.12</v>
       </c>
       <c r="E3" t="n">
-        <v>665.11</v>
+        <v>2383.52</v>
       </c>
       <c r="F3" t="n">
-        <v>621.45</v>
+        <v>2340.9</v>
       </c>
       <c r="G3" t="n">
-        <v>7.3</v>
+        <v>6.77</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -549,19 +549,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11317</v>
+        <v>11293</v>
       </c>
       <c r="D4" t="n">
-        <v>10951.39</v>
+        <v>10950.59</v>
       </c>
       <c r="E4" t="n">
-        <v>11081.32</v>
+        <v>11080.84</v>
       </c>
       <c r="F4" t="n">
-        <v>10536.81</v>
+        <v>10536.69</v>
       </c>
       <c r="G4" t="n">
-        <v>7.4</v>
+        <v>7.18</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>121.16</v>
+        <v>5740.5</v>
       </c>
       <c r="D5" t="n">
-        <v>116.12</v>
+        <v>5533.02</v>
       </c>
       <c r="E5" t="n">
-        <v>116.25</v>
+        <v>5567.21</v>
       </c>
       <c r="F5" t="n">
-        <v>112.46</v>
+        <v>5323.32</v>
       </c>
       <c r="G5" t="n">
-        <v>7.73</v>
+        <v>7.84</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2553</v>
+        <v>122.5</v>
       </c>
       <c r="D6" t="n">
-        <v>2334.9</v>
+        <v>116.16</v>
       </c>
       <c r="E6" t="n">
-        <v>2384.59</v>
+        <v>116.28</v>
       </c>
       <c r="F6" t="n">
-        <v>2341.17</v>
+        <v>112.47</v>
       </c>
       <c r="G6" t="n">
-        <v>9.050000000000001</v>
+        <v>8.92</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -643,43 +643,6 @@
         </is>
       </c>
       <c r="I6" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>22-10-2026</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>PERSISTENT</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>5847</v>
-      </c>
-      <c r="D7" t="n">
-        <v>5536.57</v>
-      </c>
-      <c r="E7" t="n">
-        <v>5569.34</v>
-      </c>
-      <c r="F7" t="n">
-        <v>5323.86</v>
-      </c>
-      <c r="G7" t="n">
-        <v>9.83</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,28 +466,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>22-10-2026</t>
+          <t>23-10-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>290.4</v>
+        <v>122.5</v>
       </c>
       <c r="D2" t="n">
-        <v>288.86</v>
+        <v>116.16</v>
       </c>
       <c r="E2" t="n">
-        <v>288.73</v>
+        <v>116.28</v>
       </c>
       <c r="F2" t="n">
-        <v>280.75</v>
+        <v>112.47</v>
       </c>
       <c r="G2" t="n">
-        <v>3.44</v>
+        <v>8.92</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -495,154 +495,6 @@
         </is>
       </c>
       <c r="I2" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>22-10-2026</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>MPHASIS</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>2499.5</v>
-      </c>
-      <c r="D3" t="n">
-        <v>2333.12</v>
-      </c>
-      <c r="E3" t="n">
-        <v>2383.52</v>
-      </c>
-      <c r="F3" t="n">
-        <v>2340.9</v>
-      </c>
-      <c r="G3" t="n">
-        <v>6.77</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>22-10-2026</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>BAJAJHLDNG</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>11293</v>
-      </c>
-      <c r="D4" t="n">
-        <v>10950.59</v>
-      </c>
-      <c r="E4" t="n">
-        <v>11080.84</v>
-      </c>
-      <c r="F4" t="n">
-        <v>10536.69</v>
-      </c>
-      <c r="G4" t="n">
-        <v>7.18</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>22-10-2026</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>PERSISTENT</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>5740.5</v>
-      </c>
-      <c r="D5" t="n">
-        <v>5533.02</v>
-      </c>
-      <c r="E5" t="n">
-        <v>5567.21</v>
-      </c>
-      <c r="F5" t="n">
-        <v>5323.32</v>
-      </c>
-      <c r="G5" t="n">
-        <v>7.84</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>22-10-2026</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>PNB</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>122.5</v>
-      </c>
-      <c r="D6" t="n">
-        <v>116.16</v>
-      </c>
-      <c r="E6" t="n">
-        <v>116.28</v>
-      </c>
-      <c r="F6" t="n">
-        <v>112.47</v>
-      </c>
-      <c r="G6" t="n">
-        <v>8.92</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>122.5</v>
+        <v>119.5</v>
       </c>
       <c r="D2" t="n">
-        <v>116.16</v>
+        <v>116.28</v>
       </c>
       <c r="E2" t="n">
-        <v>116.28</v>
+        <v>116.39</v>
       </c>
       <c r="F2" t="n">
         <v>112.47</v>
       </c>
       <c r="G2" t="n">
-        <v>8.92</v>
+        <v>6.25</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -495,6 +495,80 @@
         </is>
       </c>
       <c r="I2" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>23-10-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>MPHASIS</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2506</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2333.33</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2383.65</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2340.94</v>
+      </c>
+      <c r="G3" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>23-10-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>5790</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5534.67</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5568.2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>5323.57</v>
+      </c>
+      <c r="G4" t="n">
+        <v>8.76</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,23 +471,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>119.5</v>
+        <v>2480</v>
       </c>
       <c r="D2" t="n">
-        <v>116.28</v>
+        <v>2337.28</v>
       </c>
       <c r="E2" t="n">
-        <v>116.39</v>
+        <v>2382.52</v>
       </c>
       <c r="F2" t="n">
-        <v>112.47</v>
+        <v>2339.71</v>
       </c>
       <c r="G2" t="n">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2506</v>
+        <v>11175</v>
       </c>
       <c r="D3" t="n">
-        <v>2333.33</v>
+        <v>10957.01</v>
       </c>
       <c r="E3" t="n">
-        <v>2383.65</v>
+        <v>11074.67</v>
       </c>
       <c r="F3" t="n">
-        <v>2340.94</v>
+        <v>10536.94</v>
       </c>
       <c r="G3" t="n">
-        <v>7.05</v>
+        <v>6.06</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,30 +545,67 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>120.37</v>
+      </c>
+      <c r="D4" t="n">
+        <v>116.31</v>
+      </c>
+      <c r="E4" t="n">
+        <v>116.41</v>
+      </c>
+      <c r="F4" t="n">
+        <v>112.47</v>
+      </c>
+      <c r="G4" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>23-10-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>PERSISTENT</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>5790</v>
-      </c>
-      <c r="D4" t="n">
-        <v>5534.67</v>
-      </c>
-      <c r="E4" t="n">
-        <v>5568.2</v>
-      </c>
-      <c r="F4" t="n">
-        <v>5323.57</v>
-      </c>
-      <c r="G4" t="n">
-        <v>8.76</v>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="C5" t="n">
+        <v>5727.5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5538.6</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5571.04</v>
+      </c>
+      <c r="F5" t="n">
+        <v>5320.82</v>
+      </c>
+      <c r="G5" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>23-10-2026</t>
+          <t>24-10-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,7 +503,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>23-10-2026</t>
+          <t>24-10-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -540,28 +540,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>23-10-2026</t>
+          <t>24-10-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>120.37</v>
+        <v>5727.5</v>
       </c>
       <c r="D4" t="n">
-        <v>116.31</v>
+        <v>5538.6</v>
       </c>
       <c r="E4" t="n">
-        <v>116.41</v>
+        <v>5571.04</v>
       </c>
       <c r="F4" t="n">
-        <v>112.47</v>
+        <v>5320.82</v>
       </c>
       <c r="G4" t="n">
-        <v>7.02</v>
+        <v>7.64</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -569,43 +569,6 @@
         </is>
       </c>
       <c r="I4" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>23-10-2026</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>PERSISTENT</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>5727.5</v>
-      </c>
-      <c r="D5" t="n">
-        <v>5538.6</v>
-      </c>
-      <c r="E5" t="n">
-        <v>5571.04</v>
-      </c>
-      <c r="F5" t="n">
-        <v>5320.82</v>
-      </c>
-      <c r="G5" t="n">
-        <v>7.64</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -545,30 +545,67 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>120.37</v>
+      </c>
+      <c r="D4" t="n">
+        <v>116.31</v>
+      </c>
+      <c r="E4" t="n">
+        <v>116.41</v>
+      </c>
+      <c r="F4" t="n">
+        <v>112.47</v>
+      </c>
+      <c r="G4" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>24-10-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>PERSISTENT</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C5" t="n">
         <v>5727.5</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D5" t="n">
         <v>5538.6</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E5" t="n">
         <v>5571.04</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F5" t="n">
         <v>5320.82</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G5" t="n">
         <v>7.64</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>24-10-2026</t>
+          <t>26-10-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,7 +503,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>24-10-2026</t>
+          <t>26-10-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -540,7 +540,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>24-10-2026</t>
+          <t>26-10-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -577,7 +577,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>24-10-2026</t>
+          <t>26-10-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,23 +471,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2480</v>
+        <v>1280.5</v>
       </c>
       <c r="D2" t="n">
-        <v>2337.28</v>
+        <v>1208.42</v>
       </c>
       <c r="E2" t="n">
-        <v>2382.52</v>
+        <v>1194.05</v>
       </c>
       <c r="F2" t="n">
-        <v>2339.71</v>
+        <v>1238.42</v>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>3.4</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11175</v>
+        <v>118.86</v>
       </c>
       <c r="D3" t="n">
-        <v>10957.01</v>
+        <v>116.42</v>
       </c>
       <c r="E3" t="n">
-        <v>11074.67</v>
+        <v>116.4</v>
       </c>
       <c r="F3" t="n">
-        <v>10536.94</v>
+        <v>112.46</v>
       </c>
       <c r="G3" t="n">
-        <v>6.06</v>
+        <v>5.69</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>120.37</v>
+        <v>11160</v>
       </c>
       <c r="D4" t="n">
-        <v>116.31</v>
+        <v>10961.87</v>
       </c>
       <c r="E4" t="n">
-        <v>116.41</v>
+        <v>11067.62</v>
       </c>
       <c r="F4" t="n">
-        <v>112.47</v>
+        <v>10537.05</v>
       </c>
       <c r="G4" t="n">
-        <v>7.02</v>
+        <v>5.91</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,30 +582,141 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>MPHASIS</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2514.3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2344.18</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2382.06</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2338.51</v>
+      </c>
+      <c r="G5" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>26-10-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>PERSISTENT</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>5727.5</v>
-      </c>
-      <c r="D5" t="n">
-        <v>5538.6</v>
-      </c>
-      <c r="E5" t="n">
-        <v>5571.04</v>
-      </c>
-      <c r="F5" t="n">
-        <v>5320.82</v>
-      </c>
-      <c r="G5" t="n">
-        <v>7.64</v>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="C6" t="n">
+        <v>5757.5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5549.88</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5576.71</v>
+      </c>
+      <c r="F6" t="n">
+        <v>5318.42</v>
+      </c>
+      <c r="G6" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="H6" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>26-10-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>HCLTECH</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1418.4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1269.61</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1281.74</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1298.85</v>
+      </c>
+      <c r="G7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>26-10-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1940.4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1843.89</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1866.01</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1530.74</v>
+      </c>
+      <c r="G8" t="n">
+        <v>26.76</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,23 +471,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1280.5</v>
+        <v>291.75</v>
       </c>
       <c r="D2" t="n">
-        <v>1208.42</v>
+        <v>289.08</v>
       </c>
       <c r="E2" t="n">
-        <v>1194.05</v>
+        <v>289.15</v>
       </c>
       <c r="F2" t="n">
-        <v>1238.42</v>
+        <v>280.82</v>
       </c>
       <c r="G2" t="n">
-        <v>3.4</v>
+        <v>3.89</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>118.86</v>
+        <v>1310.9</v>
       </c>
       <c r="D3" t="n">
-        <v>116.42</v>
+        <v>1209.43</v>
       </c>
       <c r="E3" t="n">
-        <v>116.4</v>
+        <v>1194.66</v>
       </c>
       <c r="F3" t="n">
-        <v>112.46</v>
+        <v>1238.58</v>
       </c>
       <c r="G3" t="n">
-        <v>5.69</v>
+        <v>5.84</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11160</v>
+        <v>120.89</v>
       </c>
       <c r="D4" t="n">
-        <v>10961.87</v>
+        <v>116.48</v>
       </c>
       <c r="E4" t="n">
-        <v>11067.62</v>
+        <v>116.44</v>
       </c>
       <c r="F4" t="n">
-        <v>10537.05</v>
+        <v>112.47</v>
       </c>
       <c r="G4" t="n">
-        <v>5.91</v>
+        <v>7.48</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2514.3</v>
+        <v>1417</v>
       </c>
       <c r="D5" t="n">
-        <v>2344.18</v>
+        <v>1269.56</v>
       </c>
       <c r="E5" t="n">
-        <v>2382.06</v>
+        <v>1281.71</v>
       </c>
       <c r="F5" t="n">
-        <v>2338.51</v>
+        <v>1298.84</v>
       </c>
       <c r="G5" t="n">
-        <v>7.52</v>
+        <v>9.1</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5757.5</v>
+        <v>2557.6</v>
       </c>
       <c r="D6" t="n">
-        <v>5549.88</v>
+        <v>2345.62</v>
       </c>
       <c r="E6" t="n">
-        <v>5576.71</v>
+        <v>2382.92</v>
       </c>
       <c r="F6" t="n">
-        <v>5318.42</v>
+        <v>2338.73</v>
       </c>
       <c r="G6" t="n">
-        <v>8.26</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -656,23 +656,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1418.4</v>
+        <v>5850</v>
       </c>
       <c r="D7" t="n">
-        <v>1269.61</v>
+        <v>5552.97</v>
       </c>
       <c r="E7" t="n">
-        <v>1281.74</v>
+        <v>5578.56</v>
       </c>
       <c r="F7" t="n">
-        <v>1298.85</v>
+        <v>5318.88</v>
       </c>
       <c r="G7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.99</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -693,30 +693,67 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>325.55</v>
+      </c>
+      <c r="D8" t="n">
+        <v>323.96</v>
+      </c>
+      <c r="E8" t="n">
+        <v>324.01</v>
+      </c>
+      <c r="F8" t="n">
+        <v>279.46</v>
+      </c>
+      <c r="G8" t="n">
+        <v>16.49</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>26-10-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>COFORGE</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>1940.4</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1843.89</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1866.01</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1530.74</v>
-      </c>
-      <c r="G8" t="n">
-        <v>26.76</v>
-      </c>
-      <c r="H8" t="inlineStr">
+      <c r="C9" t="n">
+        <v>1993</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1845.65</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1867.06</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1531</v>
+      </c>
+      <c r="G9" t="n">
+        <v>30.18</v>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,28 +466,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>26-10-2026</t>
+          <t>27-10-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>291.75</v>
+        <v>1310.9</v>
       </c>
       <c r="D2" t="n">
-        <v>289.08</v>
+        <v>1209.43</v>
       </c>
       <c r="E2" t="n">
-        <v>289.15</v>
+        <v>1194.66</v>
       </c>
       <c r="F2" t="n">
-        <v>280.82</v>
+        <v>1238.58</v>
       </c>
       <c r="G2" t="n">
-        <v>3.89</v>
+        <v>5.84</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -503,28 +503,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>26-10-2026</t>
+          <t>27-10-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1310.9</v>
+        <v>120.89</v>
       </c>
       <c r="D3" t="n">
-        <v>1209.43</v>
+        <v>116.48</v>
       </c>
       <c r="E3" t="n">
-        <v>1194.66</v>
+        <v>116.44</v>
       </c>
       <c r="F3" t="n">
-        <v>1238.58</v>
+        <v>112.47</v>
       </c>
       <c r="G3" t="n">
-        <v>5.84</v>
+        <v>7.48</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -540,28 +540,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>26-10-2026</t>
+          <t>27-10-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>120.89</v>
+        <v>2557.6</v>
       </c>
       <c r="D4" t="n">
-        <v>116.48</v>
+        <v>2345.62</v>
       </c>
       <c r="E4" t="n">
-        <v>116.44</v>
+        <v>2382.92</v>
       </c>
       <c r="F4" t="n">
-        <v>112.47</v>
+        <v>2338.73</v>
       </c>
       <c r="G4" t="n">
-        <v>7.48</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -577,28 +577,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>26-10-2026</t>
+          <t>27-10-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1417</v>
+        <v>5850</v>
       </c>
       <c r="D5" t="n">
-        <v>1269.56</v>
+        <v>5552.97</v>
       </c>
       <c r="E5" t="n">
-        <v>1281.71</v>
+        <v>5578.56</v>
       </c>
       <c r="F5" t="n">
-        <v>1298.84</v>
+        <v>5318.88</v>
       </c>
       <c r="G5" t="n">
-        <v>9.1</v>
+        <v>9.99</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -614,28 +614,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>26-10-2026</t>
+          <t>27-10-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2557.6</v>
+        <v>325.55</v>
       </c>
       <c r="D6" t="n">
-        <v>2345.62</v>
+        <v>323.96</v>
       </c>
       <c r="E6" t="n">
-        <v>2382.92</v>
+        <v>324.01</v>
       </c>
       <c r="F6" t="n">
-        <v>2338.73</v>
+        <v>279.46</v>
       </c>
       <c r="G6" t="n">
-        <v>9.359999999999999</v>
+        <v>16.49</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -651,28 +651,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>26-10-2026</t>
+          <t>27-10-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5850</v>
+        <v>1993</v>
       </c>
       <c r="D7" t="n">
-        <v>5552.97</v>
+        <v>1845.65</v>
       </c>
       <c r="E7" t="n">
-        <v>5578.56</v>
+        <v>1867.06</v>
       </c>
       <c r="F7" t="n">
-        <v>5318.88</v>
+        <v>1531</v>
       </c>
       <c r="G7" t="n">
-        <v>9.99</v>
+        <v>30.18</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -680,80 +680,6 @@
         </is>
       </c>
       <c r="I7" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>26-10-2026</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>ETERNAL</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>325.55</v>
-      </c>
-      <c r="D8" t="n">
-        <v>323.96</v>
-      </c>
-      <c r="E8" t="n">
-        <v>324.01</v>
-      </c>
-      <c r="F8" t="n">
-        <v>279.46</v>
-      </c>
-      <c r="G8" t="n">
-        <v>16.49</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>26-10-2026</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>COFORGE</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>1993</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1845.65</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1867.06</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1531</v>
-      </c>
-      <c r="G9" t="n">
-        <v>30.18</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,23 +471,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1310.9</v>
+        <v>292.75</v>
       </c>
       <c r="D2" t="n">
-        <v>1209.43</v>
+        <v>289.11</v>
       </c>
       <c r="E2" t="n">
-        <v>1194.66</v>
+        <v>289.17</v>
       </c>
       <c r="F2" t="n">
-        <v>1238.58</v>
+        <v>280.82</v>
       </c>
       <c r="G2" t="n">
-        <v>5.84</v>
+        <v>4.25</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>120.89</v>
+        <v>1313.5</v>
       </c>
       <c r="D3" t="n">
-        <v>116.48</v>
+        <v>1215.11</v>
       </c>
       <c r="E3" t="n">
-        <v>116.44</v>
+        <v>1196.81</v>
       </c>
       <c r="F3" t="n">
-        <v>112.47</v>
+        <v>1238.9</v>
       </c>
       <c r="G3" t="n">
-        <v>7.48</v>
+        <v>6.02</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2557.6</v>
+        <v>121.04</v>
       </c>
       <c r="D4" t="n">
-        <v>2345.62</v>
+        <v>116.62</v>
       </c>
       <c r="E4" t="n">
-        <v>2382.92</v>
+        <v>116.51</v>
       </c>
       <c r="F4" t="n">
-        <v>2338.73</v>
+        <v>112.47</v>
       </c>
       <c r="G4" t="n">
-        <v>9.359999999999999</v>
+        <v>7.62</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5850</v>
+        <v>670.25</v>
       </c>
       <c r="D5" t="n">
-        <v>5552.97</v>
+        <v>659.24</v>
       </c>
       <c r="E5" t="n">
-        <v>5578.56</v>
+        <v>665.3099999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>5318.88</v>
+        <v>621.13</v>
       </c>
       <c r="G5" t="n">
-        <v>9.99</v>
+        <v>7.91</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>325.55</v>
+        <v>2526.6</v>
       </c>
       <c r="D6" t="n">
-        <v>323.96</v>
+        <v>2353.45</v>
       </c>
       <c r="E6" t="n">
-        <v>324.01</v>
+        <v>2382.63</v>
       </c>
       <c r="F6" t="n">
-        <v>279.46</v>
+        <v>2337.69</v>
       </c>
       <c r="G6" t="n">
-        <v>16.49</v>
+        <v>8.08</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -656,30 +656,178 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>HCLTECH</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1404.3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1269.14</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1281.46</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1298.78</v>
+      </c>
+      <c r="G7" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>27-10-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>5778.5</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5561.93</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5583.67</v>
+      </c>
+      <c r="F8" t="n">
+        <v>5316.55</v>
+      </c>
+      <c r="G8" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>27-10-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2177.6</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2145.38</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2152.74</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2000.84</v>
+      </c>
+      <c r="G9" t="n">
+        <v>8.83</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>27-10-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>328.1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>324.16</v>
+      </c>
+      <c r="E10" t="n">
+        <v>324.21</v>
+      </c>
+      <c r="F10" t="n">
+        <v>279.68</v>
+      </c>
+      <c r="G10" t="n">
+        <v>17.31</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>27-10-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>COFORGE</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>1993</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1845.65</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1867.06</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1531</v>
-      </c>
-      <c r="G7" t="n">
-        <v>30.18</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="C11" t="n">
+        <v>1958</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1849.81</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1869.64</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1532.58</v>
+      </c>
+      <c r="G11" t="n">
+        <v>27.76</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>292.75</v>
+        <v>296</v>
       </c>
       <c r="D2" t="n">
-        <v>289.11</v>
+        <v>289.32</v>
       </c>
       <c r="E2" t="n">
-        <v>289.17</v>
+        <v>289.48</v>
       </c>
       <c r="F2" t="n">
-        <v>280.82</v>
+        <v>280.86</v>
       </c>
       <c r="G2" t="n">
-        <v>4.25</v>
+        <v>5.39</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -512,19 +512,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1313.5</v>
+        <v>1310</v>
       </c>
       <c r="D3" t="n">
-        <v>1215.11</v>
+        <v>1215</v>
       </c>
       <c r="E3" t="n">
-        <v>1196.81</v>
+        <v>1196.74</v>
       </c>
       <c r="F3" t="n">
-        <v>1238.9</v>
+        <v>1238.88</v>
       </c>
       <c r="G3" t="n">
-        <v>6.02</v>
+        <v>5.74</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -549,19 +549,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>121.04</v>
+        <v>121.27</v>
       </c>
       <c r="D4" t="n">
-        <v>116.62</v>
+        <v>116.63</v>
       </c>
       <c r="E4" t="n">
-        <v>116.51</v>
+        <v>116.52</v>
       </c>
       <c r="F4" t="n">
         <v>112.47</v>
       </c>
       <c r="G4" t="n">
-        <v>7.62</v>
+        <v>7.82</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -586,19 +586,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>670.25</v>
+        <v>671</v>
       </c>
       <c r="D5" t="n">
-        <v>659.24</v>
+        <v>659.26</v>
       </c>
       <c r="E5" t="n">
-        <v>665.3099999999999</v>
+        <v>665.3200000000001</v>
       </c>
       <c r="F5" t="n">
         <v>621.13</v>
       </c>
       <c r="G5" t="n">
-        <v>7.91</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2526.6</v>
+        <v>1420</v>
       </c>
       <c r="D6" t="n">
-        <v>2353.45</v>
+        <v>1277.02</v>
       </c>
       <c r="E6" t="n">
-        <v>2382.63</v>
+        <v>1282.95</v>
       </c>
       <c r="F6" t="n">
-        <v>2337.69</v>
+        <v>1298.11</v>
       </c>
       <c r="G6" t="n">
-        <v>8.08</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -656,23 +656,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1404.3</v>
+        <v>5832.5</v>
       </c>
       <c r="D7" t="n">
-        <v>1269.14</v>
+        <v>5563.73</v>
       </c>
       <c r="E7" t="n">
-        <v>1281.46</v>
+        <v>5584.75</v>
       </c>
       <c r="F7" t="n">
-        <v>1298.78</v>
+        <v>5316.82</v>
       </c>
       <c r="G7" t="n">
-        <v>8.119999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -693,23 +693,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5778.5</v>
+        <v>2213.9</v>
       </c>
       <c r="D8" t="n">
-        <v>5561.93</v>
+        <v>2146.59</v>
       </c>
       <c r="E8" t="n">
-        <v>5583.67</v>
+        <v>2153.46</v>
       </c>
       <c r="F8" t="n">
-        <v>5316.55</v>
+        <v>2001.03</v>
       </c>
       <c r="G8" t="n">
-        <v>8.69</v>
+        <v>10.64</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -730,23 +730,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2177.6</v>
+        <v>2618.4</v>
       </c>
       <c r="D9" t="n">
-        <v>2145.38</v>
+        <v>2356.51</v>
       </c>
       <c r="E9" t="n">
-        <v>2152.74</v>
+        <v>2384.47</v>
       </c>
       <c r="F9" t="n">
-        <v>2000.84</v>
+        <v>2338.15</v>
       </c>
       <c r="G9" t="n">
-        <v>8.83</v>
+        <v>11.99</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -771,19 +771,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>328.1</v>
+        <v>331</v>
       </c>
       <c r="D10" t="n">
-        <v>324.16</v>
+        <v>324.26</v>
       </c>
       <c r="E10" t="n">
-        <v>324.21</v>
+        <v>324.27</v>
       </c>
       <c r="F10" t="n">
-        <v>279.68</v>
+        <v>279.69</v>
       </c>
       <c r="G10" t="n">
-        <v>17.31</v>
+        <v>18.34</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -808,19 +808,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1958</v>
+        <v>1997</v>
       </c>
       <c r="D11" t="n">
-        <v>1849.81</v>
+        <v>1851.11</v>
       </c>
       <c r="E11" t="n">
-        <v>1869.64</v>
+        <v>1870.42</v>
       </c>
       <c r="F11" t="n">
-        <v>1532.58</v>
+        <v>1532.77</v>
       </c>
       <c r="G11" t="n">
-        <v>27.76</v>
+        <v>30.29</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>27-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,7 +503,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>27-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -540,7 +540,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>27-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -577,7 +577,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>27-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -614,7 +614,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>27-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -651,28 +651,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>27-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5832.5</v>
+        <v>2213.9</v>
       </c>
       <c r="D7" t="n">
-        <v>5563.73</v>
+        <v>2146.59</v>
       </c>
       <c r="E7" t="n">
-        <v>5584.75</v>
+        <v>2153.46</v>
       </c>
       <c r="F7" t="n">
-        <v>5316.82</v>
+        <v>2001.03</v>
       </c>
       <c r="G7" t="n">
-        <v>9.699999999999999</v>
+        <v>10.64</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -688,28 +688,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>27-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2213.9</v>
+        <v>2618.4</v>
       </c>
       <c r="D8" t="n">
-        <v>2146.59</v>
+        <v>2356.51</v>
       </c>
       <c r="E8" t="n">
-        <v>2153.46</v>
+        <v>2384.47</v>
       </c>
       <c r="F8" t="n">
-        <v>2001.03</v>
+        <v>2338.15</v>
       </c>
       <c r="G8" t="n">
-        <v>10.64</v>
+        <v>11.99</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -725,28 +725,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>27-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2618.4</v>
+        <v>331</v>
       </c>
       <c r="D9" t="n">
-        <v>2356.51</v>
+        <v>324.26</v>
       </c>
       <c r="E9" t="n">
-        <v>2384.47</v>
+        <v>324.27</v>
       </c>
       <c r="F9" t="n">
-        <v>2338.15</v>
+        <v>279.69</v>
       </c>
       <c r="G9" t="n">
-        <v>11.99</v>
+        <v>18.34</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -762,28 +762,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>27-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>331</v>
+        <v>1997</v>
       </c>
       <c r="D10" t="n">
-        <v>324.26</v>
+        <v>1851.11</v>
       </c>
       <c r="E10" t="n">
-        <v>324.27</v>
+        <v>1870.42</v>
       </c>
       <c r="F10" t="n">
-        <v>279.69</v>
+        <v>1532.77</v>
       </c>
       <c r="G10" t="n">
-        <v>18.34</v>
+        <v>30.29</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -791,43 +791,6 @@
         </is>
       </c>
       <c r="I10" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>27-10-2026</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>COFORGE</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>1997</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1851.11</v>
-      </c>
-      <c r="E11" t="n">
-        <v>1870.42</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1532.77</v>
-      </c>
-      <c r="G11" t="n">
-        <v>30.29</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -471,23 +471,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>296</v>
+        <v>2434.3</v>
       </c>
       <c r="D2" t="n">
-        <v>289.32</v>
+        <v>2225.52</v>
       </c>
       <c r="E2" t="n">
-        <v>289.48</v>
+        <v>2246.5</v>
       </c>
       <c r="F2" t="n">
-        <v>280.86</v>
+        <v>2400.04</v>
       </c>
       <c r="G2" t="n">
-        <v>5.39</v>
+        <v>1.43</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -512,19 +512,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1310</v>
+        <v>1322.9</v>
       </c>
       <c r="D3" t="n">
-        <v>1215</v>
+        <v>1220.24</v>
       </c>
       <c r="E3" t="n">
-        <v>1196.74</v>
+        <v>1199.2</v>
       </c>
       <c r="F3" t="n">
-        <v>1238.88</v>
+        <v>1239.29</v>
       </c>
       <c r="G3" t="n">
-        <v>5.74</v>
+        <v>6.75</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>121.27</v>
+        <v>2495.2</v>
       </c>
       <c r="D4" t="n">
-        <v>116.63</v>
+        <v>2363.18</v>
       </c>
       <c r="E4" t="n">
-        <v>116.52</v>
+        <v>2383.47</v>
       </c>
       <c r="F4" t="n">
-        <v>112.47</v>
+        <v>2336.98</v>
       </c>
       <c r="G4" t="n">
-        <v>7.82</v>
+        <v>6.77</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>671</v>
+        <v>1388.5</v>
       </c>
       <c r="D5" t="n">
-        <v>659.26</v>
+        <v>1283.45</v>
       </c>
       <c r="E5" t="n">
-        <v>665.3200000000001</v>
+        <v>1283.76</v>
       </c>
       <c r="F5" t="n">
-        <v>621.13</v>
+        <v>1297.37</v>
       </c>
       <c r="G5" t="n">
-        <v>8.029999999999999</v>
+        <v>7.02</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1420</v>
+        <v>120.36</v>
       </c>
       <c r="D6" t="n">
-        <v>1277.02</v>
+        <v>116.75</v>
       </c>
       <c r="E6" t="n">
-        <v>1282.95</v>
+        <v>116.57</v>
       </c>
       <c r="F6" t="n">
-        <v>1298.11</v>
+        <v>112.47</v>
       </c>
       <c r="G6" t="n">
-        <v>9.390000000000001</v>
+        <v>7.02</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -656,23 +656,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2213.9</v>
+        <v>666.9</v>
       </c>
       <c r="D7" t="n">
-        <v>2146.59</v>
+        <v>660.01</v>
       </c>
       <c r="E7" t="n">
-        <v>2153.46</v>
+        <v>665.36</v>
       </c>
       <c r="F7" t="n">
-        <v>2001.03</v>
+        <v>620.95</v>
       </c>
       <c r="G7" t="n">
-        <v>10.64</v>
+        <v>7.4</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -693,23 +693,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2618.4</v>
+        <v>2177</v>
       </c>
       <c r="D8" t="n">
-        <v>2356.51</v>
+        <v>2147.37</v>
       </c>
       <c r="E8" t="n">
-        <v>2384.47</v>
+        <v>2155.5</v>
       </c>
       <c r="F8" t="n">
-        <v>2338.15</v>
+        <v>2002.12</v>
       </c>
       <c r="G8" t="n">
-        <v>11.99</v>
+        <v>8.73</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -730,23 +730,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>331</v>
+        <v>5817.5</v>
       </c>
       <c r="D9" t="n">
-        <v>324.26</v>
+        <v>5563.23</v>
       </c>
       <c r="E9" t="n">
-        <v>324.27</v>
+        <v>5584.45</v>
       </c>
       <c r="F9" t="n">
-        <v>279.69</v>
+        <v>5316.74</v>
       </c>
       <c r="G9" t="n">
-        <v>18.34</v>
+        <v>9.42</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -771,19 +771,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1997</v>
+        <v>1956.8</v>
       </c>
       <c r="D10" t="n">
-        <v>1851.11</v>
+        <v>1854.79</v>
       </c>
       <c r="E10" t="n">
-        <v>1870.42</v>
+        <v>1873.31</v>
       </c>
       <c r="F10" t="n">
-        <v>1532.77</v>
+        <v>1534.39</v>
       </c>
       <c r="G10" t="n">
-        <v>30.29</v>
+        <v>27.53</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2434.3</v>
+        <v>2460</v>
       </c>
       <c r="D2" t="n">
-        <v>2225.52</v>
+        <v>2226.38</v>
       </c>
       <c r="E2" t="n">
-        <v>2246.5</v>
+        <v>2247.02</v>
       </c>
       <c r="F2" t="n">
-        <v>2400.04</v>
+        <v>2400.17</v>
       </c>
       <c r="G2" t="n">
-        <v>1.43</v>
+        <v>2.49</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1322.9</v>
+        <v>120.31</v>
       </c>
       <c r="D3" t="n">
-        <v>1220.24</v>
+        <v>116.75</v>
       </c>
       <c r="E3" t="n">
-        <v>1199.2</v>
+        <v>116.56</v>
       </c>
       <c r="F3" t="n">
-        <v>1239.29</v>
+        <v>112.47</v>
       </c>
       <c r="G3" t="n">
-        <v>6.75</v>
+        <v>6.97</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2495.2</v>
+        <v>666.3</v>
       </c>
       <c r="D4" t="n">
-        <v>2363.18</v>
+        <v>659.99</v>
       </c>
       <c r="E4" t="n">
-        <v>2383.47</v>
+        <v>665.35</v>
       </c>
       <c r="F4" t="n">
-        <v>2336.98</v>
+        <v>620.95</v>
       </c>
       <c r="G4" t="n">
-        <v>6.77</v>
+        <v>7.3</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1388.5</v>
+        <v>2518</v>
       </c>
       <c r="D5" t="n">
-        <v>1283.45</v>
+        <v>2363.94</v>
       </c>
       <c r="E5" t="n">
-        <v>1283.76</v>
+        <v>2383.93</v>
       </c>
       <c r="F5" t="n">
-        <v>1297.37</v>
+        <v>2337.1</v>
       </c>
       <c r="G5" t="n">
-        <v>7.02</v>
+        <v>7.74</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>120.36</v>
+        <v>1335.4</v>
       </c>
       <c r="D6" t="n">
-        <v>116.75</v>
+        <v>1220.66</v>
       </c>
       <c r="E6" t="n">
-        <v>116.57</v>
+        <v>1199.45</v>
       </c>
       <c r="F6" t="n">
-        <v>112.47</v>
+        <v>1239.35</v>
       </c>
       <c r="G6" t="n">
-        <v>7.02</v>
+        <v>7.75</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -656,23 +656,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>666.9</v>
+        <v>1400.5</v>
       </c>
       <c r="D7" t="n">
-        <v>660.01</v>
+        <v>1283.85</v>
       </c>
       <c r="E7" t="n">
-        <v>665.36</v>
+        <v>1284</v>
       </c>
       <c r="F7" t="n">
-        <v>620.95</v>
+        <v>1297.43</v>
       </c>
       <c r="G7" t="n">
-        <v>7.4</v>
+        <v>7.94</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -697,19 +697,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2177</v>
+        <v>2165.3</v>
       </c>
       <c r="D8" t="n">
-        <v>2147.37</v>
+        <v>2146.98</v>
       </c>
       <c r="E8" t="n">
-        <v>2155.5</v>
+        <v>2155.26</v>
       </c>
       <c r="F8" t="n">
-        <v>2002.12</v>
+        <v>2002.06</v>
       </c>
       <c r="G8" t="n">
-        <v>8.73</v>
+        <v>8.15</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5817.5</v>
+        <v>5848</v>
       </c>
       <c r="D9" t="n">
-        <v>5563.23</v>
+        <v>5574.8</v>
       </c>
       <c r="E9" t="n">
-        <v>5584.45</v>
+        <v>5590.11</v>
       </c>
       <c r="F9" t="n">
-        <v>5316.74</v>
+        <v>5315.25</v>
       </c>
       <c r="G9" t="n">
-        <v>9.42</v>
+        <v>10.02</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -771,19 +771,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1956.8</v>
+        <v>1961.9</v>
       </c>
       <c r="D10" t="n">
-        <v>1854.79</v>
+        <v>1854.96</v>
       </c>
       <c r="E10" t="n">
-        <v>1873.31</v>
+        <v>1873.42</v>
       </c>
       <c r="F10" t="n">
-        <v>1534.39</v>
+        <v>1534.41</v>
       </c>
       <c r="G10" t="n">
-        <v>27.53</v>
+        <v>27.86</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>28-10-2026</t>
+          <t>29-10-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,7 +503,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>28-10-2026</t>
+          <t>29-10-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -540,7 +540,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>28-10-2026</t>
+          <t>29-10-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -577,28 +577,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>28-10-2026</t>
+          <t>29-10-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2518</v>
+        <v>1335.4</v>
       </c>
       <c r="D5" t="n">
-        <v>2363.94</v>
+        <v>1220.66</v>
       </c>
       <c r="E5" t="n">
-        <v>2383.93</v>
+        <v>1199.45</v>
       </c>
       <c r="F5" t="n">
-        <v>2337.1</v>
+        <v>1239.35</v>
       </c>
       <c r="G5" t="n">
-        <v>7.74</v>
+        <v>7.75</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -614,28 +614,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>28-10-2026</t>
+          <t>29-10-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1335.4</v>
+        <v>1400.5</v>
       </c>
       <c r="D6" t="n">
-        <v>1220.66</v>
+        <v>1283.85</v>
       </c>
       <c r="E6" t="n">
-        <v>1199.45</v>
+        <v>1284</v>
       </c>
       <c r="F6" t="n">
-        <v>1239.35</v>
+        <v>1297.43</v>
       </c>
       <c r="G6" t="n">
-        <v>7.75</v>
+        <v>7.94</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -651,28 +651,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>28-10-2026</t>
+          <t>29-10-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1400.5</v>
+        <v>2165.3</v>
       </c>
       <c r="D7" t="n">
-        <v>1283.85</v>
+        <v>2146.98</v>
       </c>
       <c r="E7" t="n">
-        <v>1284</v>
+        <v>2155.26</v>
       </c>
       <c r="F7" t="n">
-        <v>1297.43</v>
+        <v>2002.06</v>
       </c>
       <c r="G7" t="n">
-        <v>7.94</v>
+        <v>8.15</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -688,28 +688,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>28-10-2026</t>
+          <t>29-10-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2165.3</v>
+        <v>1961.9</v>
       </c>
       <c r="D8" t="n">
-        <v>2146.98</v>
+        <v>1854.96</v>
       </c>
       <c r="E8" t="n">
-        <v>2155.26</v>
+        <v>1873.42</v>
       </c>
       <c r="F8" t="n">
-        <v>2002.06</v>
+        <v>1534.41</v>
       </c>
       <c r="G8" t="n">
-        <v>8.15</v>
+        <v>27.86</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -717,80 +717,6 @@
         </is>
       </c>
       <c r="I8" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>28-10-2026</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>PERSISTENT</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>5848</v>
-      </c>
-      <c r="D9" t="n">
-        <v>5574.8</v>
-      </c>
-      <c r="E9" t="n">
-        <v>5590.11</v>
-      </c>
-      <c r="F9" t="n">
-        <v>5315.25</v>
-      </c>
-      <c r="G9" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>28-10-2026</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>COFORGE</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>1961.9</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1854.96</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1873.42</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1534.41</v>
-      </c>
-      <c r="G10" t="n">
-        <v>27.86</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2460</v>
+        <v>2473.8</v>
       </c>
       <c r="D2" t="n">
-        <v>2226.38</v>
+        <v>2234.2</v>
       </c>
       <c r="E2" t="n">
-        <v>2247.02</v>
+        <v>2250.47</v>
       </c>
       <c r="F2" t="n">
-        <v>2400.17</v>
+        <v>2396.93</v>
       </c>
       <c r="G2" t="n">
-        <v>2.49</v>
+        <v>3.21</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>120.31</v>
+        <v>1400.8</v>
       </c>
       <c r="D3" t="n">
-        <v>116.75</v>
+        <v>1289.12</v>
       </c>
       <c r="E3" t="n">
-        <v>116.56</v>
+        <v>1285.75</v>
       </c>
       <c r="F3" t="n">
-        <v>112.47</v>
+        <v>1296.71</v>
       </c>
       <c r="G3" t="n">
-        <v>6.97</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -549,19 +549,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>666.3</v>
+        <v>673.45</v>
       </c>
       <c r="D4" t="n">
-        <v>659.99</v>
+        <v>661.74</v>
       </c>
       <c r="E4" t="n">
-        <v>665.35</v>
+        <v>665.4</v>
       </c>
       <c r="F4" t="n">
-        <v>620.95</v>
+        <v>620.83</v>
       </c>
       <c r="G4" t="n">
-        <v>7.3</v>
+        <v>8.48</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1335.4</v>
+        <v>2536.2</v>
       </c>
       <c r="D5" t="n">
-        <v>1220.66</v>
+        <v>2364.55</v>
       </c>
       <c r="E5" t="n">
-        <v>1199.45</v>
+        <v>2384.29</v>
       </c>
       <c r="F5" t="n">
-        <v>1239.35</v>
+        <v>2337.19</v>
       </c>
       <c r="G5" t="n">
-        <v>7.75</v>
+        <v>8.52</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1400.5</v>
+        <v>1348.2</v>
       </c>
       <c r="D6" t="n">
-        <v>1283.85</v>
+        <v>1227.43</v>
       </c>
       <c r="E6" t="n">
-        <v>1284</v>
+        <v>1202.57</v>
       </c>
       <c r="F6" t="n">
-        <v>1297.43</v>
+        <v>1239.85</v>
       </c>
       <c r="G6" t="n">
-        <v>7.94</v>
+        <v>8.74</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -656,23 +656,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2165.3</v>
+        <v>122.32</v>
       </c>
       <c r="D7" t="n">
-        <v>2146.98</v>
+        <v>117</v>
       </c>
       <c r="E7" t="n">
-        <v>2155.26</v>
+        <v>116.66</v>
       </c>
       <c r="F7" t="n">
-        <v>2002.06</v>
+        <v>112.47</v>
       </c>
       <c r="G7" t="n">
-        <v>8.15</v>
+        <v>8.76</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -693,30 +693,104 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>5873.5</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5575.65</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5590.62</v>
+      </c>
+      <c r="F8" t="n">
+        <v>5315.38</v>
+      </c>
+      <c r="G8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>29-10-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2213.7</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2150.13</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2158.07</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2003.42</v>
+      </c>
+      <c r="G9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>29-10-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>COFORGE</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>1961.9</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1854.96</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1873.42</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1534.41</v>
-      </c>
-      <c r="G8" t="n">
-        <v>27.86</v>
-      </c>
-      <c r="H8" t="inlineStr">
+      <c r="C10" t="n">
+        <v>1951.9</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1860.84</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1876.33</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1535.92</v>
+      </c>
+      <c r="G10" t="n">
+        <v>27.08</v>
+      </c>
+      <c r="H10" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2473.8</v>
+        <v>2478</v>
       </c>
       <c r="D2" t="n">
-        <v>2234.2</v>
+        <v>2234.34</v>
       </c>
       <c r="E2" t="n">
-        <v>2250.47</v>
+        <v>2250.56</v>
       </c>
       <c r="F2" t="n">
-        <v>2396.93</v>
+        <v>2396.95</v>
       </c>
       <c r="G2" t="n">
-        <v>3.21</v>
+        <v>3.38</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -512,19 +512,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1400.8</v>
+        <v>1403.9</v>
       </c>
       <c r="D3" t="n">
-        <v>1289.12</v>
+        <v>1289.23</v>
       </c>
       <c r="E3" t="n">
-        <v>1285.75</v>
+        <v>1285.82</v>
       </c>
       <c r="F3" t="n">
-        <v>1296.71</v>
+        <v>1296.72</v>
       </c>
       <c r="G3" t="n">
-        <v>8.029999999999999</v>
+        <v>8.27</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,20 +545,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>673.45</v>
+        <v>1345</v>
       </c>
       <c r="D4" t="n">
-        <v>661.74</v>
+        <v>1227.33</v>
       </c>
       <c r="E4" t="n">
-        <v>665.4</v>
+        <v>1202.51</v>
       </c>
       <c r="F4" t="n">
-        <v>620.83</v>
+        <v>1239.83</v>
       </c>
       <c r="G4" t="n">
         <v>8.48</v>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2536.2</v>
+        <v>2195</v>
       </c>
       <c r="D5" t="n">
-        <v>2364.55</v>
+        <v>2149.51</v>
       </c>
       <c r="E5" t="n">
-        <v>2384.29</v>
+        <v>2157.7</v>
       </c>
       <c r="F5" t="n">
-        <v>2337.19</v>
+        <v>2003.33</v>
       </c>
       <c r="G5" t="n">
-        <v>8.52</v>
+        <v>9.57</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1348.2</v>
+        <v>2561.3</v>
       </c>
       <c r="D6" t="n">
-        <v>1227.43</v>
+        <v>2370.05</v>
       </c>
       <c r="E6" t="n">
-        <v>1202.57</v>
+        <v>2384.96</v>
       </c>
       <c r="F6" t="n">
-        <v>1239.85</v>
+        <v>2336.19</v>
       </c>
       <c r="G6" t="n">
-        <v>8.74</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -660,19 +660,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>122.32</v>
+        <v>123.9</v>
       </c>
       <c r="D7" t="n">
-        <v>117</v>
+        <v>117.06</v>
       </c>
       <c r="E7" t="n">
-        <v>116.66</v>
+        <v>116.7</v>
       </c>
       <c r="F7" t="n">
-        <v>112.47</v>
+        <v>112.48</v>
       </c>
       <c r="G7" t="n">
-        <v>8.76</v>
+        <v>10.16</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -697,19 +697,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5873.5</v>
+        <v>5880</v>
       </c>
       <c r="D8" t="n">
-        <v>5575.65</v>
+        <v>5588.22</v>
       </c>
       <c r="E8" t="n">
-        <v>5590.62</v>
+        <v>5596.31</v>
       </c>
       <c r="F8" t="n">
-        <v>5315.38</v>
+        <v>5313.63</v>
       </c>
       <c r="G8" t="n">
-        <v>10.5</v>
+        <v>10.66</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -730,23 +730,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2213.7</v>
+        <v>694.35</v>
       </c>
       <c r="D9" t="n">
-        <v>2150.13</v>
+        <v>662.4400000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>2158.07</v>
+        <v>665.8200000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>2003.42</v>
+        <v>620.9299999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>10.5</v>
+        <v>11.82</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -771,19 +771,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1951.9</v>
+        <v>1962</v>
       </c>
       <c r="D10" t="n">
-        <v>1860.84</v>
+        <v>1861.17</v>
       </c>
       <c r="E10" t="n">
-        <v>1876.33</v>
+        <v>1876.54</v>
       </c>
       <c r="F10" t="n">
-        <v>1535.92</v>
+        <v>1535.97</v>
       </c>
       <c r="G10" t="n">
-        <v>27.08</v>
+        <v>27.74</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>29-10-2026</t>
+          <t>30-10-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,7 +503,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>29-10-2026</t>
+          <t>30-10-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -540,7 +540,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>29-10-2026</t>
+          <t>30-10-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -577,28 +577,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>29-10-2026</t>
+          <t>30-10-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2195</v>
+        <v>2561.3</v>
       </c>
       <c r="D5" t="n">
-        <v>2149.51</v>
+        <v>2370.05</v>
       </c>
       <c r="E5" t="n">
-        <v>2157.7</v>
+        <v>2384.96</v>
       </c>
       <c r="F5" t="n">
-        <v>2003.33</v>
+        <v>2336.19</v>
       </c>
       <c r="G5" t="n">
-        <v>9.57</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -614,28 +614,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>29-10-2026</t>
+          <t>30-10-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2561.3</v>
+        <v>123.9</v>
       </c>
       <c r="D6" t="n">
-        <v>2370.05</v>
+        <v>117.06</v>
       </c>
       <c r="E6" t="n">
-        <v>2384.96</v>
+        <v>116.7</v>
       </c>
       <c r="F6" t="n">
-        <v>2336.19</v>
+        <v>112.48</v>
       </c>
       <c r="G6" t="n">
-        <v>9.640000000000001</v>
+        <v>10.16</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -651,28 +651,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>29-10-2026</t>
+          <t>30-10-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>123.9</v>
+        <v>694.35</v>
       </c>
       <c r="D7" t="n">
-        <v>117.06</v>
+        <v>662.4400000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>116.7</v>
+        <v>665.8200000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>112.48</v>
+        <v>620.9299999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>10.16</v>
+        <v>11.82</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -688,28 +688,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>29-10-2026</t>
+          <t>30-10-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5880</v>
+        <v>1962</v>
       </c>
       <c r="D8" t="n">
-        <v>5588.22</v>
+        <v>1861.17</v>
       </c>
       <c r="E8" t="n">
-        <v>5596.31</v>
+        <v>1876.54</v>
       </c>
       <c r="F8" t="n">
-        <v>5313.63</v>
+        <v>1535.97</v>
       </c>
       <c r="G8" t="n">
-        <v>10.66</v>
+        <v>27.74</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -717,80 +717,6 @@
         </is>
       </c>
       <c r="I8" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>29-10-2026</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>DLF</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>694.35</v>
-      </c>
-      <c r="D9" t="n">
-        <v>662.4400000000001</v>
-      </c>
-      <c r="E9" t="n">
-        <v>665.8200000000001</v>
-      </c>
-      <c r="F9" t="n">
-        <v>620.9299999999999</v>
-      </c>
-      <c r="G9" t="n">
-        <v>11.82</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>29-10-2026</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>COFORGE</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>1962</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1861.17</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1876.54</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1535.97</v>
-      </c>
-      <c r="G10" t="n">
-        <v>27.74</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2478</v>
+        <v>2511.4</v>
       </c>
       <c r="D2" t="n">
-        <v>2234.34</v>
+        <v>2245.48</v>
       </c>
       <c r="E2" t="n">
-        <v>2250.56</v>
+        <v>2255.43</v>
       </c>
       <c r="F2" t="n">
-        <v>2396.95</v>
+        <v>2393.71</v>
       </c>
       <c r="G2" t="n">
-        <v>3.38</v>
+        <v>4.92</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1403.9</v>
+        <v>187</v>
       </c>
       <c r="D3" t="n">
-        <v>1289.23</v>
+        <v>176.32</v>
       </c>
       <c r="E3" t="n">
-        <v>1285.82</v>
+        <v>179.47</v>
       </c>
       <c r="F3" t="n">
-        <v>1296.72</v>
+        <v>173.35</v>
       </c>
       <c r="G3" t="n">
-        <v>8.27</v>
+        <v>7.87</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1345</v>
+        <v>2547.6</v>
       </c>
       <c r="D4" t="n">
-        <v>1227.33</v>
+        <v>2377.75</v>
       </c>
       <c r="E4" t="n">
-        <v>1202.51</v>
+        <v>2387.27</v>
       </c>
       <c r="F4" t="n">
-        <v>1239.83</v>
+        <v>2334.93</v>
       </c>
       <c r="G4" t="n">
-        <v>8.48</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2561.3</v>
+        <v>2193.4</v>
       </c>
       <c r="D5" t="n">
-        <v>2370.05</v>
+        <v>2149.45</v>
       </c>
       <c r="E5" t="n">
-        <v>2384.96</v>
+        <v>2157.66</v>
       </c>
       <c r="F5" t="n">
-        <v>2336.19</v>
+        <v>2003.32</v>
       </c>
       <c r="G5" t="n">
-        <v>9.640000000000001</v>
+        <v>9.49</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>123.9</v>
+        <v>1359.3</v>
       </c>
       <c r="D6" t="n">
-        <v>117.06</v>
+        <v>1234.64</v>
       </c>
       <c r="E6" t="n">
-        <v>116.7</v>
+        <v>1206.12</v>
       </c>
       <c r="F6" t="n">
-        <v>112.48</v>
+        <v>1240.46</v>
       </c>
       <c r="G6" t="n">
-        <v>10.16</v>
+        <v>9.58</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -656,23 +656,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>694.35</v>
+        <v>123.93</v>
       </c>
       <c r="D7" t="n">
-        <v>662.4400000000001</v>
+        <v>117.29</v>
       </c>
       <c r="E7" t="n">
-        <v>665.8200000000001</v>
+        <v>116.84</v>
       </c>
       <c r="F7" t="n">
-        <v>620.9299999999999</v>
+        <v>112.48</v>
       </c>
       <c r="G7" t="n">
-        <v>11.82</v>
+        <v>10.17</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -693,23 +693,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1962</v>
+        <v>1442.4</v>
       </c>
       <c r="D8" t="n">
-        <v>1861.17</v>
+        <v>1295.91</v>
       </c>
       <c r="E8" t="n">
-        <v>1876.54</v>
+        <v>1288.93</v>
       </c>
       <c r="F8" t="n">
-        <v>1535.97</v>
+        <v>1296.06</v>
       </c>
       <c r="G8" t="n">
-        <v>27.74</v>
+        <v>11.29</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -717,6 +717,80 @@
         </is>
       </c>
       <c r="I8" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>30-10-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>692.7</v>
+      </c>
+      <c r="D9" t="n">
+        <v>664.77</v>
+      </c>
+      <c r="E9" t="n">
+        <v>666.36</v>
+      </c>
+      <c r="F9" t="n">
+        <v>620.92</v>
+      </c>
+      <c r="G9" t="n">
+        <v>11.56</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>30-10-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>6000</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5592.22</v>
+      </c>
+      <c r="E10" t="n">
+        <v>5598.71</v>
+      </c>
+      <c r="F10" t="n">
+        <v>5314.23</v>
+      </c>
+      <c r="G10" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2511.4</v>
+        <v>2502.6</v>
       </c>
       <c r="D2" t="n">
-        <v>2245.48</v>
+        <v>2245.19</v>
       </c>
       <c r="E2" t="n">
-        <v>2255.43</v>
+        <v>2255.25</v>
       </c>
       <c r="F2" t="n">
-        <v>2393.71</v>
+        <v>2393.67</v>
       </c>
       <c r="G2" t="n">
-        <v>4.92</v>
+        <v>4.55</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -512,19 +512,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D3" t="n">
-        <v>176.32</v>
+        <v>176.28</v>
       </c>
       <c r="E3" t="n">
-        <v>179.47</v>
+        <v>179.45</v>
       </c>
       <c r="F3" t="n">
         <v>173.35</v>
       </c>
       <c r="G3" t="n">
-        <v>7.87</v>
+        <v>7.3</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2547.6</v>
+        <v>2165.1</v>
       </c>
       <c r="D4" t="n">
-        <v>2377.75</v>
+        <v>2151.01</v>
       </c>
       <c r="E4" t="n">
-        <v>2387.27</v>
+        <v>2158.86</v>
       </c>
       <c r="F4" t="n">
-        <v>2334.93</v>
+        <v>2004.45</v>
       </c>
       <c r="G4" t="n">
-        <v>9.109999999999999</v>
+        <v>8.01</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2193.4</v>
+        <v>2525.6</v>
       </c>
       <c r="D5" t="n">
-        <v>2149.45</v>
+        <v>2377.02</v>
       </c>
       <c r="E5" t="n">
-        <v>2157.66</v>
+        <v>2386.83</v>
       </c>
       <c r="F5" t="n">
-        <v>2003.32</v>
+        <v>2334.82</v>
       </c>
       <c r="G5" t="n">
-        <v>9.49</v>
+        <v>8.17</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -623,19 +623,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1359.3</v>
+        <v>1352</v>
       </c>
       <c r="D6" t="n">
-        <v>1234.64</v>
+        <v>1234.39</v>
       </c>
       <c r="E6" t="n">
-        <v>1206.12</v>
+        <v>1205.97</v>
       </c>
       <c r="F6" t="n">
-        <v>1240.46</v>
+        <v>1240.42</v>
       </c>
       <c r="G6" t="n">
-        <v>9.58</v>
+        <v>9</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -660,19 +660,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>123.93</v>
+        <v>122.85</v>
       </c>
       <c r="D7" t="n">
-        <v>117.29</v>
+        <v>117.26</v>
       </c>
       <c r="E7" t="n">
-        <v>116.84</v>
+        <v>116.82</v>
       </c>
       <c r="F7" t="n">
         <v>112.48</v>
       </c>
       <c r="G7" t="n">
-        <v>10.17</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -697,19 +697,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1442.4</v>
+        <v>1428.1</v>
       </c>
       <c r="D8" t="n">
-        <v>1295.91</v>
+        <v>1295.43</v>
       </c>
       <c r="E8" t="n">
-        <v>1288.93</v>
+        <v>1288.65</v>
       </c>
       <c r="F8" t="n">
-        <v>1296.06</v>
+        <v>1295.99</v>
       </c>
       <c r="G8" t="n">
-        <v>11.29</v>
+        <v>10.19</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>692.7</v>
+        <v>691.55</v>
       </c>
       <c r="D9" t="n">
-        <v>664.77</v>
+        <v>664.73</v>
       </c>
       <c r="E9" t="n">
-        <v>666.36</v>
+        <v>666.33</v>
       </c>
       <c r="F9" t="n">
         <v>620.92</v>
       </c>
       <c r="G9" t="n">
-        <v>11.56</v>
+        <v>11.38</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -771,19 +771,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6000</v>
+        <v>6048</v>
       </c>
       <c r="D10" t="n">
-        <v>5592.22</v>
+        <v>5608.48</v>
       </c>
       <c r="E10" t="n">
-        <v>5598.71</v>
+        <v>5608.42</v>
       </c>
       <c r="F10" t="n">
-        <v>5314.23</v>
+        <v>5311.53</v>
       </c>
       <c r="G10" t="n">
-        <v>12.9</v>
+        <v>13.87</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>30-10-2026</t>
+          <t>31-10-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,7 +503,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>30-10-2026</t>
+          <t>31-10-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -540,28 +540,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>30-10-2026</t>
+          <t>31-10-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2165.1</v>
+        <v>1352</v>
       </c>
       <c r="D4" t="n">
-        <v>2151.01</v>
+        <v>1234.39</v>
       </c>
       <c r="E4" t="n">
-        <v>2158.86</v>
+        <v>1205.97</v>
       </c>
       <c r="F4" t="n">
-        <v>2004.45</v>
+        <v>1240.42</v>
       </c>
       <c r="G4" t="n">
-        <v>8.01</v>
+        <v>9</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -577,28 +577,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>30-10-2026</t>
+          <t>31-10-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2525.6</v>
+        <v>122.85</v>
       </c>
       <c r="D5" t="n">
-        <v>2377.02</v>
+        <v>117.26</v>
       </c>
       <c r="E5" t="n">
-        <v>2386.83</v>
+        <v>116.82</v>
       </c>
       <c r="F5" t="n">
-        <v>2334.82</v>
+        <v>112.48</v>
       </c>
       <c r="G5" t="n">
-        <v>8.17</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -614,28 +614,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>30-10-2026</t>
+          <t>31-10-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1352</v>
+        <v>1428.1</v>
       </c>
       <c r="D6" t="n">
-        <v>1234.39</v>
+        <v>1295.43</v>
       </c>
       <c r="E6" t="n">
-        <v>1205.97</v>
+        <v>1288.65</v>
       </c>
       <c r="F6" t="n">
-        <v>1240.42</v>
+        <v>1295.99</v>
       </c>
       <c r="G6" t="n">
-        <v>9</v>
+        <v>10.19</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -651,28 +651,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>30-10-2026</t>
+          <t>31-10-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>122.85</v>
+        <v>691.55</v>
       </c>
       <c r="D7" t="n">
-        <v>117.26</v>
+        <v>664.73</v>
       </c>
       <c r="E7" t="n">
-        <v>116.82</v>
+        <v>666.33</v>
       </c>
       <c r="F7" t="n">
-        <v>112.48</v>
+        <v>620.92</v>
       </c>
       <c r="G7" t="n">
-        <v>9.220000000000001</v>
+        <v>11.38</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -688,28 +688,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>30-10-2026</t>
+          <t>31-10-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1428.1</v>
+        <v>6048</v>
       </c>
       <c r="D8" t="n">
-        <v>1295.43</v>
+        <v>5608.48</v>
       </c>
       <c r="E8" t="n">
-        <v>1288.65</v>
+        <v>5608.42</v>
       </c>
       <c r="F8" t="n">
-        <v>1295.99</v>
+        <v>5311.53</v>
       </c>
       <c r="G8" t="n">
-        <v>10.19</v>
+        <v>13.87</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -717,80 +717,6 @@
         </is>
       </c>
       <c r="I8" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>30-10-2026</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>DLF</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>691.55</v>
-      </c>
-      <c r="D9" t="n">
-        <v>664.73</v>
-      </c>
-      <c r="E9" t="n">
-        <v>666.33</v>
-      </c>
-      <c r="F9" t="n">
-        <v>620.92</v>
-      </c>
-      <c r="G9" t="n">
-        <v>11.38</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>30-10-2026</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>PERSISTENT</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>6048</v>
-      </c>
-      <c r="D10" t="n">
-        <v>5608.48</v>
-      </c>
-      <c r="E10" t="n">
-        <v>5608.42</v>
-      </c>
-      <c r="F10" t="n">
-        <v>5311.53</v>
-      </c>
-      <c r="G10" t="n">
-        <v>13.87</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1352</v>
+        <v>2165.1</v>
       </c>
       <c r="D4" t="n">
-        <v>1234.39</v>
+        <v>2151.01</v>
       </c>
       <c r="E4" t="n">
-        <v>1205.97</v>
+        <v>2158.86</v>
       </c>
       <c r="F4" t="n">
-        <v>1240.42</v>
+        <v>2004.45</v>
       </c>
       <c r="G4" t="n">
-        <v>9</v>
+        <v>8.01</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>122.85</v>
+        <v>2525.6</v>
       </c>
       <c r="D5" t="n">
-        <v>117.26</v>
+        <v>2377.02</v>
       </c>
       <c r="E5" t="n">
-        <v>116.82</v>
+        <v>2386.83</v>
       </c>
       <c r="F5" t="n">
-        <v>112.48</v>
+        <v>2334.82</v>
       </c>
       <c r="G5" t="n">
-        <v>9.220000000000001</v>
+        <v>8.17</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1428.1</v>
+        <v>1352</v>
       </c>
       <c r="D6" t="n">
-        <v>1295.43</v>
+        <v>1234.39</v>
       </c>
       <c r="E6" t="n">
-        <v>1288.65</v>
+        <v>1205.97</v>
       </c>
       <c r="F6" t="n">
-        <v>1295.99</v>
+        <v>1240.42</v>
       </c>
       <c r="G6" t="n">
-        <v>10.19</v>
+        <v>9</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -656,23 +656,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>691.55</v>
+        <v>122.85</v>
       </c>
       <c r="D7" t="n">
-        <v>664.73</v>
+        <v>117.26</v>
       </c>
       <c r="E7" t="n">
-        <v>666.33</v>
+        <v>116.82</v>
       </c>
       <c r="F7" t="n">
-        <v>620.92</v>
+        <v>112.48</v>
       </c>
       <c r="G7" t="n">
-        <v>11.38</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -693,30 +693,104 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>HCLTECH</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1428.1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1295.43</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1288.65</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1295.99</v>
+      </c>
+      <c r="G8" t="n">
+        <v>10.19</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>31-10-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>691.55</v>
+      </c>
+      <c r="D9" t="n">
+        <v>664.73</v>
+      </c>
+      <c r="E9" t="n">
+        <v>666.33</v>
+      </c>
+      <c r="F9" t="n">
+        <v>620.92</v>
+      </c>
+      <c r="G9" t="n">
+        <v>11.38</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>31-10-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>PERSISTENT</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C10" t="n">
         <v>6048</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D10" t="n">
         <v>5608.48</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E10" t="n">
         <v>5608.42</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F10" t="n">
         <v>5311.53</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G10" t="n">
         <v>13.87</v>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>
